--- a/Professional_Report.xlsx
+++ b/Professional_Report.xlsx
@@ -7,15 +7,15 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Весь Склад" sheetId="1" r:id="rId1"/>
-    <sheet name="Аналитика" sheetId="2" r:id="rId2"/>
+    <sheet name="Warehouse" sheetId="1" r:id="rId1"/>
+    <sheet name="Analytics" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="515">
   <si>
     <t>Артикул</t>
   </si>
@@ -1556,24 +1556,21 @@
     <t>Платье</t>
   </si>
   <si>
-    <t>ОБЩИЙ ИТОГ:</t>
-  </si>
-  <si>
-    <t>СОВЕТ ОТ GEMINI 3:</t>
-  </si>
-  <si>
-    <t>AI сейчас отдыхает, но данные в порядке! 😴</t>
+    <t>Рекомендация AI</t>
+  </si>
+  <si>
+    <t>Анализируя текущие остатки, **Юбка** имеет наименьшее количество (3801).
+**Рекомендация:** Рассмотрите приоритетную закупку **Юбок**, а также проведите сверку всех позиций с планом продаж и минимальными остатками для более точной оценки.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00 &quot;₴&quot;"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1581,36 +1578,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7E4BC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1618,30 +1595,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1936,40 +1896,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H502"/>
+  <dimension ref="A1:H501"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="8" width="16.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1986,7 +1938,7 @@
       <c r="D2">
         <v>32.32</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>45658</v>
       </c>
       <c r="F2">
@@ -2012,17 +1964,17 @@
       <c r="D3">
         <v>149.73</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>45659</v>
       </c>
       <c r="F3">
         <v>6737.849999999999</v>
       </c>
       <c r="G3">
-        <v>471649.5</v>
+        <v>471649.4999999999</v>
       </c>
       <c r="H3">
-        <v>94329.90000000001</v>
+        <v>94329.89999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2038,7 +1990,7 @@
       <c r="D4">
         <v>127.09</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>45660</v>
       </c>
       <c r="F4">
@@ -2064,7 +2016,7 @@
       <c r="D5">
         <v>59.14</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>45661</v>
       </c>
       <c r="F5">
@@ -2090,7 +2042,7 @@
       <c r="D6">
         <v>27.71</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>45662</v>
       </c>
       <c r="F6">
@@ -2116,7 +2068,7 @@
       <c r="D7">
         <v>86.05</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>45663</v>
       </c>
       <c r="F7">
@@ -2142,7 +2094,7 @@
       <c r="D8">
         <v>55.78</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>45664</v>
       </c>
       <c r="F8">
@@ -2168,7 +2120,7 @@
       <c r="D9">
         <v>57.98</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>45665</v>
       </c>
       <c r="F9">
@@ -2194,7 +2146,7 @@
       <c r="D10">
         <v>92.66</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>45666</v>
       </c>
       <c r="F10">
@@ -2220,7 +2172,7 @@
       <c r="D11">
         <v>79.91</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>45667</v>
       </c>
       <c r="F11">
@@ -2246,7 +2198,7 @@
       <c r="D12">
         <v>125.64</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>45668</v>
       </c>
       <c r="F12">
@@ -2272,7 +2224,7 @@
       <c r="D13">
         <v>7.19</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>45669</v>
       </c>
       <c r="F13">
@@ -2298,7 +2250,7 @@
       <c r="D14">
         <v>96.13</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>45670</v>
       </c>
       <c r="F14">
@@ -2324,7 +2276,7 @@
       <c r="D15">
         <v>113.11</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>45671</v>
       </c>
       <c r="F15">
@@ -2350,7 +2302,7 @@
       <c r="D16">
         <v>74.73999999999999</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="1">
         <v>45672</v>
       </c>
       <c r="F16">
@@ -2376,7 +2328,7 @@
       <c r="D17">
         <v>34.61</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="1">
         <v>45673</v>
       </c>
       <c r="F17">
@@ -2402,7 +2354,7 @@
       <c r="D18">
         <v>32.98</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="1">
         <v>45674</v>
       </c>
       <c r="F18">
@@ -2428,7 +2380,7 @@
       <c r="D19">
         <v>106.48</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="1">
         <v>45675</v>
       </c>
       <c r="F19">
@@ -2454,7 +2406,7 @@
       <c r="D20">
         <v>38.7</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="1">
         <v>45676</v>
       </c>
       <c r="F20">
@@ -2480,7 +2432,7 @@
       <c r="D21">
         <v>136.08</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="1">
         <v>45677</v>
       </c>
       <c r="F21">
@@ -2506,7 +2458,7 @@
       <c r="D22">
         <v>120.1</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="1">
         <v>45678</v>
       </c>
       <c r="F22">
@@ -2532,7 +2484,7 @@
       <c r="D23">
         <v>40.06</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="1">
         <v>45679</v>
       </c>
       <c r="F23">
@@ -2558,7 +2510,7 @@
       <c r="D24">
         <v>49.92</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="1">
         <v>45680</v>
       </c>
       <c r="F24">
@@ -2568,7 +2520,7 @@
         <v>31449.6</v>
       </c>
       <c r="H24">
-        <v>6289.92</v>
+        <v>6289.920000000001</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2584,7 +2536,7 @@
       <c r="D25">
         <v>27.6</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="1">
         <v>45681</v>
       </c>
       <c r="F25">
@@ -2610,7 +2562,7 @@
       <c r="D26">
         <v>7.16</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="1">
         <v>45682</v>
       </c>
       <c r="F26">
@@ -2636,7 +2588,7 @@
       <c r="D27">
         <v>96.3</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="1">
         <v>45683</v>
       </c>
       <c r="F27">
@@ -2662,7 +2614,7 @@
       <c r="D28">
         <v>77.65000000000001</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="1">
         <v>45684</v>
       </c>
       <c r="F28">
@@ -2672,7 +2624,7 @@
         <v>223632</v>
       </c>
       <c r="H28">
-        <v>44726.4</v>
+        <v>44726.40000000001</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2688,7 +2640,7 @@
       <c r="D29">
         <v>125.31</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="1">
         <v>45685</v>
       </c>
       <c r="F29">
@@ -2714,7 +2666,7 @@
       <c r="D30">
         <v>76.5</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="1">
         <v>45686</v>
       </c>
       <c r="F30">
@@ -2740,7 +2692,7 @@
       <c r="D31">
         <v>20.2</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="1">
         <v>45687</v>
       </c>
       <c r="F31">
@@ -2766,7 +2718,7 @@
       <c r="D32">
         <v>115.28</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="1">
         <v>45688</v>
       </c>
       <c r="F32">
@@ -2792,7 +2744,7 @@
       <c r="D33">
         <v>127.99</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" s="1">
         <v>45689</v>
       </c>
       <c r="F33">
@@ -2818,7 +2770,7 @@
       <c r="D34">
         <v>103.03</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E34" s="1">
         <v>45690</v>
       </c>
       <c r="F34">
@@ -2844,7 +2796,7 @@
       <c r="D35">
         <v>86.45</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E35" s="1">
         <v>45691</v>
       </c>
       <c r="F35">
@@ -2870,7 +2822,7 @@
       <c r="D36">
         <v>88.72</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="1">
         <v>45692</v>
       </c>
       <c r="F36">
@@ -2896,7 +2848,7 @@
       <c r="D37">
         <v>62.13</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="1">
         <v>45693</v>
       </c>
       <c r="F37">
@@ -2922,14 +2874,14 @@
       <c r="D38">
         <v>77.18000000000001</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="1">
         <v>45694</v>
       </c>
       <c r="F38">
         <v>3473.1</v>
       </c>
       <c r="G38">
-        <v>329944.5</v>
+        <v>329944.5000000001</v>
       </c>
       <c r="H38">
         <v>65988.90000000001</v>
@@ -2948,7 +2900,7 @@
       <c r="D39">
         <v>101.59</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="1">
         <v>45695</v>
       </c>
       <c r="F39">
@@ -2974,7 +2926,7 @@
       <c r="D40">
         <v>121.05</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E40" s="1">
         <v>45696</v>
       </c>
       <c r="F40">
@@ -3000,7 +2952,7 @@
       <c r="D41">
         <v>22.8</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E41" s="1">
         <v>45697</v>
       </c>
       <c r="F41">
@@ -3026,7 +2978,7 @@
       <c r="D42">
         <v>64.28</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="1">
         <v>45698</v>
       </c>
       <c r="F42">
@@ -3052,7 +3004,7 @@
       <c r="D43">
         <v>13.9</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E43" s="1">
         <v>45699</v>
       </c>
       <c r="F43">
@@ -3078,7 +3030,7 @@
       <c r="D44">
         <v>130.25</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="1">
         <v>45700</v>
       </c>
       <c r="F44">
@@ -3104,7 +3056,7 @@
       <c r="D45">
         <v>149.54</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E45" s="1">
         <v>45701</v>
       </c>
       <c r="F45">
@@ -3130,7 +3082,7 @@
       <c r="D46">
         <v>115.93</v>
       </c>
-      <c r="E46" s="2">
+      <c r="E46" s="1">
         <v>45702</v>
       </c>
       <c r="F46">
@@ -3140,7 +3092,7 @@
         <v>485167.05</v>
       </c>
       <c r="H46">
-        <v>97033.41</v>
+        <v>97033.41000000002</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -3156,7 +3108,7 @@
       <c r="D47">
         <v>60.1</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47" s="1">
         <v>45703</v>
       </c>
       <c r="F47">
@@ -3182,7 +3134,7 @@
       <c r="D48">
         <v>131.66</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E48" s="1">
         <v>45704</v>
       </c>
       <c r="F48">
@@ -3208,7 +3160,7 @@
       <c r="D49">
         <v>97.65000000000001</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="1">
         <v>45705</v>
       </c>
       <c r="F49">
@@ -3234,7 +3186,7 @@
       <c r="D50">
         <v>142.56</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E50" s="1">
         <v>45706</v>
       </c>
       <c r="F50">
@@ -3260,7 +3212,7 @@
       <c r="D51">
         <v>118.46</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E51" s="1">
         <v>45707</v>
       </c>
       <c r="F51">
@@ -3286,7 +3238,7 @@
       <c r="D52">
         <v>84.45999999999999</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52" s="1">
         <v>45708</v>
       </c>
       <c r="F52">
@@ -3312,7 +3264,7 @@
       <c r="D53">
         <v>21.28</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53" s="1">
         <v>45709</v>
       </c>
       <c r="F53">
@@ -3338,7 +3290,7 @@
       <c r="D54">
         <v>112.69</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54" s="1">
         <v>45710</v>
       </c>
       <c r="F54">
@@ -3364,7 +3316,7 @@
       <c r="D55">
         <v>47.3</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="1">
         <v>45711</v>
       </c>
       <c r="F55">
@@ -3390,7 +3342,7 @@
       <c r="D56">
         <v>118.7</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E56" s="1">
         <v>45712</v>
       </c>
       <c r="F56">
@@ -3416,7 +3368,7 @@
       <c r="D57">
         <v>60.75</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E57" s="1">
         <v>45713</v>
       </c>
       <c r="F57">
@@ -3442,7 +3394,7 @@
       <c r="D58">
         <v>125.34</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="1">
         <v>45714</v>
       </c>
       <c r="F58">
@@ -3468,7 +3420,7 @@
       <c r="D59">
         <v>13.42</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E59" s="1">
         <v>45715</v>
       </c>
       <c r="F59">
@@ -3494,7 +3446,7 @@
       <c r="D60">
         <v>53.96</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60" s="1">
         <v>45716</v>
       </c>
       <c r="F60">
@@ -3520,7 +3472,7 @@
       <c r="D61">
         <v>91.37</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61" s="1">
         <v>45717</v>
       </c>
       <c r="F61">
@@ -3546,7 +3498,7 @@
       <c r="D62">
         <v>14.34</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E62" s="1">
         <v>45718</v>
       </c>
       <c r="F62">
@@ -3572,7 +3524,7 @@
       <c r="D63">
         <v>137.14</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E63" s="1">
         <v>45719</v>
       </c>
       <c r="F63">
@@ -3598,7 +3550,7 @@
       <c r="D64">
         <v>100.77</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E64" s="1">
         <v>45720</v>
       </c>
       <c r="F64">
@@ -3624,7 +3576,7 @@
       <c r="D65">
         <v>16.41</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E65" s="1">
         <v>45721</v>
       </c>
       <c r="F65">
@@ -3634,7 +3586,7 @@
         <v>37660.95</v>
       </c>
       <c r="H65">
-        <v>7532.19</v>
+        <v>7532.190000000001</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -3650,7 +3602,7 @@
       <c r="D66">
         <v>48.35</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E66" s="1">
         <v>45722</v>
       </c>
       <c r="F66">
@@ -3676,7 +3628,7 @@
       <c r="D67">
         <v>145.23</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="1">
         <v>45723</v>
       </c>
       <c r="F67">
@@ -3686,7 +3638,7 @@
         <v>209131.2</v>
       </c>
       <c r="H67">
-        <v>41826.24000000001</v>
+        <v>41826.24</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -3702,7 +3654,7 @@
       <c r="D68">
         <v>5.78</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="1">
         <v>45724</v>
       </c>
       <c r="F68">
@@ -3728,7 +3680,7 @@
       <c r="D69">
         <v>87.38</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69" s="1">
         <v>45725</v>
       </c>
       <c r="F69">
@@ -3754,7 +3706,7 @@
       <c r="D70">
         <v>144.18</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E70" s="1">
         <v>45726</v>
       </c>
       <c r="F70">
@@ -3780,7 +3732,7 @@
       <c r="D71">
         <v>111.26</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="1">
         <v>45727</v>
       </c>
       <c r="F71">
@@ -3806,7 +3758,7 @@
       <c r="D72">
         <v>21.22</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E72" s="1">
         <v>45728</v>
       </c>
       <c r="F72">
@@ -3832,7 +3784,7 @@
       <c r="D73">
         <v>37.02</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E73" s="1">
         <v>45729</v>
       </c>
       <c r="F73">
@@ -3842,7 +3794,7 @@
         <v>46645.2</v>
       </c>
       <c r="H73">
-        <v>9329.039999999999</v>
+        <v>9329.040000000001</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -3858,7 +3810,7 @@
       <c r="D74">
         <v>122.36</v>
       </c>
-      <c r="E74" s="2">
+      <c r="E74" s="1">
         <v>45730</v>
       </c>
       <c r="F74">
@@ -3884,7 +3836,7 @@
       <c r="D75">
         <v>132.18</v>
       </c>
-      <c r="E75" s="2">
+      <c r="E75" s="1">
         <v>45731</v>
       </c>
       <c r="F75">
@@ -3910,7 +3862,7 @@
       <c r="D76">
         <v>120.18</v>
       </c>
-      <c r="E76" s="2">
+      <c r="E76" s="1">
         <v>45732</v>
       </c>
       <c r="F76">
@@ -3936,7 +3888,7 @@
       <c r="D77">
         <v>16.33</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E77" s="1">
         <v>45733</v>
       </c>
       <c r="F77">
@@ -3962,7 +3914,7 @@
       <c r="D78">
         <v>62.08</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E78" s="1">
         <v>45734</v>
       </c>
       <c r="F78">
@@ -3988,7 +3940,7 @@
       <c r="D79">
         <v>40.37</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E79" s="1">
         <v>45735</v>
       </c>
       <c r="F79">
@@ -4014,7 +3966,7 @@
       <c r="D80">
         <v>33.12</v>
       </c>
-      <c r="E80" s="2">
+      <c r="E80" s="1">
         <v>45736</v>
       </c>
       <c r="F80">
@@ -4040,7 +3992,7 @@
       <c r="D81">
         <v>91.70999999999999</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E81" s="1">
         <v>45737</v>
       </c>
       <c r="F81">
@@ -4066,7 +4018,7 @@
       <c r="D82">
         <v>145.25</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E82" s="1">
         <v>45738</v>
       </c>
       <c r="F82">
@@ -4092,17 +4044,17 @@
       <c r="D83">
         <v>27.83</v>
       </c>
-      <c r="E83" s="2">
+      <c r="E83" s="1">
         <v>45739</v>
       </c>
       <c r="F83">
         <v>1252.35</v>
       </c>
       <c r="G83">
-        <v>42579.9</v>
+        <v>42579.89999999999</v>
       </c>
       <c r="H83">
-        <v>8515.980000000001</v>
+        <v>8515.98</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -4118,7 +4070,7 @@
       <c r="D84">
         <v>88.89</v>
       </c>
-      <c r="E84" s="2">
+      <c r="E84" s="1">
         <v>45740</v>
       </c>
       <c r="F84">
@@ -4144,7 +4096,7 @@
       <c r="D85">
         <v>64.8</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E85" s="1">
         <v>45741</v>
       </c>
       <c r="F85">
@@ -4170,7 +4122,7 @@
       <c r="D86">
         <v>73.88</v>
       </c>
-      <c r="E86" s="2">
+      <c r="E86" s="1">
         <v>45742</v>
       </c>
       <c r="F86">
@@ -4196,7 +4148,7 @@
       <c r="D87">
         <v>64.66</v>
       </c>
-      <c r="E87" s="2">
+      <c r="E87" s="1">
         <v>45743</v>
       </c>
       <c r="F87">
@@ -4222,7 +4174,7 @@
       <c r="D88">
         <v>45.23</v>
       </c>
-      <c r="E88" s="2">
+      <c r="E88" s="1">
         <v>45744</v>
       </c>
       <c r="F88">
@@ -4248,7 +4200,7 @@
       <c r="D89">
         <v>136.53</v>
       </c>
-      <c r="E89" s="2">
+      <c r="E89" s="1">
         <v>45745</v>
       </c>
       <c r="F89">
@@ -4258,7 +4210,7 @@
         <v>313336.35</v>
       </c>
       <c r="H89">
-        <v>62667.27</v>
+        <v>62667.27000000001</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -4274,7 +4226,7 @@
       <c r="D90">
         <v>73.45999999999999</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E90" s="1">
         <v>45746</v>
       </c>
       <c r="F90">
@@ -4300,7 +4252,7 @@
       <c r="D91">
         <v>91.5</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="1">
         <v>45747</v>
       </c>
       <c r="F91">
@@ -4326,7 +4278,7 @@
       <c r="D92">
         <v>63.76</v>
       </c>
-      <c r="E92" s="2">
+      <c r="E92" s="1">
         <v>45748</v>
       </c>
       <c r="F92">
@@ -4352,7 +4304,7 @@
       <c r="D93">
         <v>125.94</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E93" s="1">
         <v>45749</v>
       </c>
       <c r="F93">
@@ -4378,7 +4330,7 @@
       <c r="D94">
         <v>52.65</v>
       </c>
-      <c r="E94" s="2">
+      <c r="E94" s="1">
         <v>45750</v>
       </c>
       <c r="F94">
@@ -4404,7 +4356,7 @@
       <c r="D95">
         <v>112.3</v>
       </c>
-      <c r="E95" s="2">
+      <c r="E95" s="1">
         <v>45751</v>
       </c>
       <c r="F95">
@@ -4430,7 +4382,7 @@
       <c r="D96">
         <v>128.85</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E96" s="1">
         <v>45752</v>
       </c>
       <c r="F96">
@@ -4456,7 +4408,7 @@
       <c r="D97">
         <v>92.63</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E97" s="1">
         <v>45753</v>
       </c>
       <c r="F97">
@@ -4482,7 +4434,7 @@
       <c r="D98">
         <v>123.1</v>
       </c>
-      <c r="E98" s="2">
+      <c r="E98" s="1">
         <v>45754</v>
       </c>
       <c r="F98">
@@ -4508,7 +4460,7 @@
       <c r="D99">
         <v>36.15</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E99" s="1">
         <v>45755</v>
       </c>
       <c r="F99">
@@ -4534,7 +4486,7 @@
       <c r="D100">
         <v>24.99</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E100" s="1">
         <v>45756</v>
       </c>
       <c r="F100">
@@ -4560,7 +4512,7 @@
       <c r="D101">
         <v>53.9</v>
       </c>
-      <c r="E101" s="2">
+      <c r="E101" s="1">
         <v>45757</v>
       </c>
       <c r="F101">
@@ -4586,7 +4538,7 @@
       <c r="D102">
         <v>13.18</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E102" s="1">
         <v>45758</v>
       </c>
       <c r="F102">
@@ -4612,7 +4564,7 @@
       <c r="D103">
         <v>40.17</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E103" s="1">
         <v>45759</v>
       </c>
       <c r="F103">
@@ -4622,7 +4574,7 @@
         <v>21691.8</v>
       </c>
       <c r="H103">
-        <v>4338.36</v>
+        <v>4338.360000000001</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -4638,7 +4590,7 @@
       <c r="D104">
         <v>80.94</v>
       </c>
-      <c r="E104" s="2">
+      <c r="E104" s="1">
         <v>45760</v>
       </c>
       <c r="F104">
@@ -4664,7 +4616,7 @@
       <c r="D105">
         <v>105.2</v>
       </c>
-      <c r="E105" s="2">
+      <c r="E105" s="1">
         <v>45761</v>
       </c>
       <c r="F105">
@@ -4690,7 +4642,7 @@
       <c r="D106">
         <v>40.74</v>
       </c>
-      <c r="E106" s="2">
+      <c r="E106" s="1">
         <v>45762</v>
       </c>
       <c r="F106">
@@ -4716,7 +4668,7 @@
       <c r="D107">
         <v>118.81</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E107" s="1">
         <v>45763</v>
       </c>
       <c r="F107">
@@ -4726,7 +4678,7 @@
         <v>278015.4</v>
       </c>
       <c r="H107">
-        <v>55603.08000000001</v>
+        <v>55603.07999999999</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -4742,7 +4694,7 @@
       <c r="D108">
         <v>95.27</v>
       </c>
-      <c r="E108" s="2">
+      <c r="E108" s="1">
         <v>45764</v>
       </c>
       <c r="F108">
@@ -4768,7 +4720,7 @@
       <c r="D109">
         <v>87.56</v>
       </c>
-      <c r="E109" s="2">
+      <c r="E109" s="1">
         <v>45765</v>
       </c>
       <c r="F109">
@@ -4794,7 +4746,7 @@
       <c r="D110">
         <v>69.87</v>
       </c>
-      <c r="E110" s="2">
+      <c r="E110" s="1">
         <v>45766</v>
       </c>
       <c r="F110">
@@ -4820,7 +4772,7 @@
       <c r="D111">
         <v>93.78</v>
       </c>
-      <c r="E111" s="2">
+      <c r="E111" s="1">
         <v>45767</v>
       </c>
       <c r="F111">
@@ -4846,7 +4798,7 @@
       <c r="D112">
         <v>39.01</v>
       </c>
-      <c r="E112" s="2">
+      <c r="E112" s="1">
         <v>45768</v>
       </c>
       <c r="F112">
@@ -4872,7 +4824,7 @@
       <c r="D113">
         <v>107.45</v>
       </c>
-      <c r="E113" s="2">
+      <c r="E113" s="1">
         <v>45769</v>
       </c>
       <c r="F113">
@@ -4898,7 +4850,7 @@
       <c r="D114">
         <v>62.41</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E114" s="1">
         <v>45770</v>
       </c>
       <c r="F114">
@@ -4924,7 +4876,7 @@
       <c r="D115">
         <v>85.19</v>
       </c>
-      <c r="E115" s="2">
+      <c r="E115" s="1">
         <v>45771</v>
       </c>
       <c r="F115">
@@ -4950,7 +4902,7 @@
       <c r="D116">
         <v>104.52</v>
       </c>
-      <c r="E116" s="2">
+      <c r="E116" s="1">
         <v>45772</v>
       </c>
       <c r="F116">
@@ -4976,7 +4928,7 @@
       <c r="D117">
         <v>45.93</v>
       </c>
-      <c r="E117" s="2">
+      <c r="E117" s="1">
         <v>45773</v>
       </c>
       <c r="F117">
@@ -5002,7 +4954,7 @@
       <c r="D118">
         <v>131.84</v>
       </c>
-      <c r="E118" s="2">
+      <c r="E118" s="1">
         <v>45774</v>
       </c>
       <c r="F118">
@@ -5028,7 +4980,7 @@
       <c r="D119">
         <v>136.94</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E119" s="1">
         <v>45775</v>
       </c>
       <c r="F119">
@@ -5054,7 +5006,7 @@
       <c r="D120">
         <v>92.28</v>
       </c>
-      <c r="E120" s="2">
+      <c r="E120" s="1">
         <v>45776</v>
       </c>
       <c r="F120">
@@ -5080,7 +5032,7 @@
       <c r="D121">
         <v>13.11</v>
       </c>
-      <c r="E121" s="2">
+      <c r="E121" s="1">
         <v>45777</v>
       </c>
       <c r="F121">
@@ -5090,7 +5042,7 @@
         <v>24187.95</v>
       </c>
       <c r="H121">
-        <v>4837.59</v>
+        <v>4837.589999999999</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -5106,7 +5058,7 @@
       <c r="D122">
         <v>88.02</v>
       </c>
-      <c r="E122" s="2">
+      <c r="E122" s="1">
         <v>45778</v>
       </c>
       <c r="F122">
@@ -5132,7 +5084,7 @@
       <c r="D123">
         <v>137.36</v>
       </c>
-      <c r="E123" s="2">
+      <c r="E123" s="1">
         <v>45779</v>
       </c>
       <c r="F123">
@@ -5142,7 +5094,7 @@
         <v>302878.8</v>
       </c>
       <c r="H123">
-        <v>60575.76</v>
+        <v>60575.76000000001</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -5158,7 +5110,7 @@
       <c r="D124">
         <v>21.7</v>
       </c>
-      <c r="E124" s="2">
+      <c r="E124" s="1">
         <v>45780</v>
       </c>
       <c r="F124">
@@ -5184,7 +5136,7 @@
       <c r="D125">
         <v>103.09</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="1">
         <v>45781</v>
       </c>
       <c r="F125">
@@ -5210,17 +5162,17 @@
       <c r="D126">
         <v>77.65000000000001</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E126" s="1">
         <v>45782</v>
       </c>
       <c r="F126">
         <v>3494.25</v>
       </c>
       <c r="G126">
-        <v>83862</v>
+        <v>83862.00000000001</v>
       </c>
       <c r="H126">
-        <v>16772.4</v>
+        <v>16772.40000000001</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -5236,14 +5188,14 @@
       <c r="D127">
         <v>35.2</v>
       </c>
-      <c r="E127" s="2">
+      <c r="E127" s="1">
         <v>45783</v>
       </c>
       <c r="F127">
         <v>1584</v>
       </c>
       <c r="G127">
-        <v>64944</v>
+        <v>64944.00000000001</v>
       </c>
       <c r="H127">
         <v>12988.8</v>
@@ -5262,7 +5214,7 @@
       <c r="D128">
         <v>11.97</v>
       </c>
-      <c r="E128" s="2">
+      <c r="E128" s="1">
         <v>45784</v>
       </c>
       <c r="F128">
@@ -5288,7 +5240,7 @@
       <c r="D129">
         <v>94.09</v>
       </c>
-      <c r="E129" s="2">
+      <c r="E129" s="1">
         <v>45785</v>
       </c>
       <c r="F129">
@@ -5314,7 +5266,7 @@
       <c r="D130">
         <v>48.18</v>
       </c>
-      <c r="E130" s="2">
+      <c r="E130" s="1">
         <v>45786</v>
       </c>
       <c r="F130">
@@ -5340,7 +5292,7 @@
       <c r="D131">
         <v>116.4</v>
       </c>
-      <c r="E131" s="2">
+      <c r="E131" s="1">
         <v>45787</v>
       </c>
       <c r="F131">
@@ -5366,7 +5318,7 @@
       <c r="D132">
         <v>28.73</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E132" s="1">
         <v>45788</v>
       </c>
       <c r="F132">
@@ -5392,7 +5344,7 @@
       <c r="D133">
         <v>131.79</v>
       </c>
-      <c r="E133" s="2">
+      <c r="E133" s="1">
         <v>45789</v>
       </c>
       <c r="F133">
@@ -5418,7 +5370,7 @@
       <c r="D134">
         <v>47.63</v>
       </c>
-      <c r="E134" s="2">
+      <c r="E134" s="1">
         <v>45790</v>
       </c>
       <c r="F134">
@@ -5444,7 +5396,7 @@
       <c r="D135">
         <v>133.25</v>
       </c>
-      <c r="E135" s="2">
+      <c r="E135" s="1">
         <v>45791</v>
       </c>
       <c r="F135">
@@ -5470,7 +5422,7 @@
       <c r="D136">
         <v>85.52</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E136" s="1">
         <v>45792</v>
       </c>
       <c r="F136">
@@ -5496,7 +5448,7 @@
       <c r="D137">
         <v>102.45</v>
       </c>
-      <c r="E137" s="2">
+      <c r="E137" s="1">
         <v>45793</v>
       </c>
       <c r="F137">
@@ -5522,7 +5474,7 @@
       <c r="D138">
         <v>67.69</v>
       </c>
-      <c r="E138" s="2">
+      <c r="E138" s="1">
         <v>45794</v>
       </c>
       <c r="F138">
@@ -5548,7 +5500,7 @@
       <c r="D139">
         <v>107.01</v>
       </c>
-      <c r="E139" s="2">
+      <c r="E139" s="1">
         <v>45795</v>
       </c>
       <c r="F139">
@@ -5574,7 +5526,7 @@
       <c r="D140">
         <v>16.41</v>
       </c>
-      <c r="E140" s="2">
+      <c r="E140" s="1">
         <v>45796</v>
       </c>
       <c r="F140">
@@ -5600,7 +5552,7 @@
       <c r="D141">
         <v>17.27</v>
       </c>
-      <c r="E141" s="2">
+      <c r="E141" s="1">
         <v>45797</v>
       </c>
       <c r="F141">
@@ -5626,7 +5578,7 @@
       <c r="D142">
         <v>103.05</v>
       </c>
-      <c r="E142" s="2">
+      <c r="E142" s="1">
         <v>45798</v>
       </c>
       <c r="F142">
@@ -5652,7 +5604,7 @@
       <c r="D143">
         <v>6.39</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="1">
         <v>45799</v>
       </c>
       <c r="F143">
@@ -5678,7 +5630,7 @@
       <c r="D144">
         <v>50.57</v>
       </c>
-      <c r="E144" s="2">
+      <c r="E144" s="1">
         <v>45800</v>
       </c>
       <c r="F144">
@@ -5704,7 +5656,7 @@
       <c r="D145">
         <v>117.22</v>
       </c>
-      <c r="E145" s="2">
+      <c r="E145" s="1">
         <v>45801</v>
       </c>
       <c r="F145">
@@ -5730,7 +5682,7 @@
       <c r="D146">
         <v>149.35</v>
       </c>
-      <c r="E146" s="2">
+      <c r="E146" s="1">
         <v>45802</v>
       </c>
       <c r="F146">
@@ -5756,7 +5708,7 @@
       <c r="D147">
         <v>104.14</v>
       </c>
-      <c r="E147" s="2">
+      <c r="E147" s="1">
         <v>45803</v>
       </c>
       <c r="F147">
@@ -5782,7 +5734,7 @@
       <c r="D148">
         <v>87.65000000000001</v>
       </c>
-      <c r="E148" s="2">
+      <c r="E148" s="1">
         <v>45804</v>
       </c>
       <c r="F148">
@@ -5792,7 +5744,7 @@
         <v>114383.25</v>
       </c>
       <c r="H148">
-        <v>22876.65</v>
+        <v>22876.65000000001</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -5808,7 +5760,7 @@
       <c r="D149">
         <v>45.32</v>
       </c>
-      <c r="E149" s="2">
+      <c r="E149" s="1">
         <v>45805</v>
       </c>
       <c r="F149">
@@ -5834,7 +5786,7 @@
       <c r="D150">
         <v>92.05</v>
       </c>
-      <c r="E150" s="2">
+      <c r="E150" s="1">
         <v>45806</v>
       </c>
       <c r="F150">
@@ -5860,7 +5812,7 @@
       <c r="D151">
         <v>148.34</v>
       </c>
-      <c r="E151" s="2">
+      <c r="E151" s="1">
         <v>45807</v>
       </c>
       <c r="F151">
@@ -5886,7 +5838,7 @@
       <c r="D152">
         <v>122.03</v>
       </c>
-      <c r="E152" s="2">
+      <c r="E152" s="1">
         <v>45808</v>
       </c>
       <c r="F152">
@@ -5912,7 +5864,7 @@
       <c r="D153">
         <v>5.59</v>
       </c>
-      <c r="E153" s="2">
+      <c r="E153" s="1">
         <v>45809</v>
       </c>
       <c r="F153">
@@ -5922,7 +5874,7 @@
         <v>12325.95</v>
       </c>
       <c r="H153">
-        <v>2465.190000000001</v>
+        <v>2465.19</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -5938,7 +5890,7 @@
       <c r="D154">
         <v>111.48</v>
       </c>
-      <c r="E154" s="2">
+      <c r="E154" s="1">
         <v>45810</v>
       </c>
       <c r="F154">
@@ -5948,7 +5900,7 @@
         <v>381261.6</v>
       </c>
       <c r="H154">
-        <v>76252.31999999999</v>
+        <v>76252.32000000001</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -5964,7 +5916,7 @@
       <c r="D155">
         <v>121.62</v>
       </c>
-      <c r="E155" s="2">
+      <c r="E155" s="1">
         <v>45811</v>
       </c>
       <c r="F155">
@@ -5990,7 +5942,7 @@
       <c r="D156">
         <v>80.2</v>
       </c>
-      <c r="E156" s="2">
+      <c r="E156" s="1">
         <v>45812</v>
       </c>
       <c r="F156">
@@ -6016,7 +5968,7 @@
       <c r="D157">
         <v>20.83</v>
       </c>
-      <c r="E157" s="2">
+      <c r="E157" s="1">
         <v>45813</v>
       </c>
       <c r="F157">
@@ -6026,7 +5978,7 @@
         <v>30932.55</v>
       </c>
       <c r="H157">
-        <v>6186.51</v>
+        <v>6186.509999999999</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -6042,7 +5994,7 @@
       <c r="D158">
         <v>129.4</v>
       </c>
-      <c r="E158" s="2">
+      <c r="E158" s="1">
         <v>45814</v>
       </c>
       <c r="F158">
@@ -6068,7 +6020,7 @@
       <c r="D159">
         <v>108.7</v>
       </c>
-      <c r="E159" s="2">
+      <c r="E159" s="1">
         <v>45815</v>
       </c>
       <c r="F159">
@@ -6094,7 +6046,7 @@
       <c r="D160">
         <v>114.18</v>
       </c>
-      <c r="E160" s="2">
+      <c r="E160" s="1">
         <v>45816</v>
       </c>
       <c r="F160">
@@ -6104,7 +6056,7 @@
         <v>493257.6</v>
       </c>
       <c r="H160">
-        <v>98651.52</v>
+        <v>98651.52000000002</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -6120,7 +6072,7 @@
       <c r="D161">
         <v>25.26</v>
       </c>
-      <c r="E161" s="2">
+      <c r="E161" s="1">
         <v>45817</v>
       </c>
       <c r="F161">
@@ -6146,7 +6098,7 @@
       <c r="D162">
         <v>130.06</v>
       </c>
-      <c r="E162" s="2">
+      <c r="E162" s="1">
         <v>45818</v>
       </c>
       <c r="F162">
@@ -6172,7 +6124,7 @@
       <c r="D163">
         <v>18.57</v>
       </c>
-      <c r="E163" s="2">
+      <c r="E163" s="1">
         <v>45819</v>
       </c>
       <c r="F163">
@@ -6198,7 +6150,7 @@
       <c r="D164">
         <v>144.33</v>
       </c>
-      <c r="E164" s="2">
+      <c r="E164" s="1">
         <v>45820</v>
       </c>
       <c r="F164">
@@ -6208,7 +6160,7 @@
         <v>409175.55</v>
       </c>
       <c r="H164">
-        <v>81835.11</v>
+        <v>81835.11000000002</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -6224,7 +6176,7 @@
       <c r="D165">
         <v>99.65000000000001</v>
       </c>
-      <c r="E165" s="2">
+      <c r="E165" s="1">
         <v>45821</v>
       </c>
       <c r="F165">
@@ -6250,7 +6202,7 @@
       <c r="D166">
         <v>71.63</v>
       </c>
-      <c r="E166" s="2">
+      <c r="E166" s="1">
         <v>45822</v>
       </c>
       <c r="F166">
@@ -6276,7 +6228,7 @@
       <c r="D167">
         <v>32.67</v>
       </c>
-      <c r="E167" s="2">
+      <c r="E167" s="1">
         <v>45823</v>
       </c>
       <c r="F167">
@@ -6302,7 +6254,7 @@
       <c r="D168">
         <v>13.52</v>
       </c>
-      <c r="E168" s="2">
+      <c r="E168" s="1">
         <v>45824</v>
       </c>
       <c r="F168">
@@ -6312,7 +6264,7 @@
         <v>37720.8</v>
       </c>
       <c r="H168">
-        <v>7544.160000000001</v>
+        <v>7544.16</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -6328,7 +6280,7 @@
       <c r="D169">
         <v>12.34</v>
       </c>
-      <c r="E169" s="2">
+      <c r="E169" s="1">
         <v>45825</v>
       </c>
       <c r="F169">
@@ -6354,17 +6306,17 @@
       <c r="D170">
         <v>12.04</v>
       </c>
-      <c r="E170" s="2">
+      <c r="E170" s="1">
         <v>45826</v>
       </c>
       <c r="F170">
         <v>541.8</v>
       </c>
       <c r="G170">
-        <v>39551.4</v>
+        <v>39551.39999999999</v>
       </c>
       <c r="H170">
-        <v>7910.280000000001</v>
+        <v>7910.279999999999</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -6380,17 +6332,17 @@
       <c r="D171">
         <v>130.87</v>
       </c>
-      <c r="E171" s="2">
+      <c r="E171" s="1">
         <v>45827</v>
       </c>
       <c r="F171">
         <v>5889.150000000001</v>
       </c>
       <c r="G171">
-        <v>323903.25</v>
+        <v>323903.2500000001</v>
       </c>
       <c r="H171">
-        <v>64780.65</v>
+        <v>64780.65000000002</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -6406,7 +6358,7 @@
       <c r="D172">
         <v>54.01</v>
       </c>
-      <c r="E172" s="2">
+      <c r="E172" s="1">
         <v>45828</v>
       </c>
       <c r="F172">
@@ -6432,7 +6384,7 @@
       <c r="D173">
         <v>71.75</v>
       </c>
-      <c r="E173" s="2">
+      <c r="E173" s="1">
         <v>45829</v>
       </c>
       <c r="F173">
@@ -6458,7 +6410,7 @@
       <c r="D174">
         <v>60.44</v>
       </c>
-      <c r="E174" s="2">
+      <c r="E174" s="1">
         <v>45830</v>
       </c>
       <c r="F174">
@@ -6484,7 +6436,7 @@
       <c r="D175">
         <v>85.94</v>
       </c>
-      <c r="E175" s="2">
+      <c r="E175" s="1">
         <v>45831</v>
       </c>
       <c r="F175">
@@ -6510,17 +6462,17 @@
       <c r="D176">
         <v>132.71</v>
       </c>
-      <c r="E176" s="2">
+      <c r="E176" s="1">
         <v>45832</v>
       </c>
       <c r="F176">
         <v>5971.950000000001</v>
       </c>
       <c r="G176">
-        <v>424008.45</v>
+        <v>424008.4500000001</v>
       </c>
       <c r="H176">
-        <v>84801.69</v>
+        <v>84801.69000000002</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -6536,7 +6488,7 @@
       <c r="D177">
         <v>5.42</v>
       </c>
-      <c r="E177" s="2">
+      <c r="E177" s="1">
         <v>45833</v>
       </c>
       <c r="F177">
@@ -6546,7 +6498,7 @@
         <v>21707.1</v>
       </c>
       <c r="H177">
-        <v>4341.42</v>
+        <v>4341.420000000001</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -6562,7 +6514,7 @@
       <c r="D178">
         <v>55.66</v>
       </c>
-      <c r="E178" s="2">
+      <c r="E178" s="1">
         <v>45834</v>
       </c>
       <c r="F178">
@@ -6588,7 +6540,7 @@
       <c r="D179">
         <v>30.1</v>
       </c>
-      <c r="E179" s="2">
+      <c r="E179" s="1">
         <v>45835</v>
       </c>
       <c r="F179">
@@ -6614,7 +6566,7 @@
       <c r="D180">
         <v>120.86</v>
       </c>
-      <c r="E180" s="2">
+      <c r="E180" s="1">
         <v>45836</v>
       </c>
       <c r="F180">
@@ -6640,14 +6592,14 @@
       <c r="D181">
         <v>21.35</v>
       </c>
-      <c r="E181" s="2">
+      <c r="E181" s="1">
         <v>45837</v>
       </c>
       <c r="F181">
         <v>960.7500000000001</v>
       </c>
       <c r="G181">
-        <v>9607.5</v>
+        <v>9607.500000000002</v>
       </c>
       <c r="H181">
         <v>1921.5</v>
@@ -6666,7 +6618,7 @@
       <c r="D182">
         <v>105.99</v>
       </c>
-      <c r="E182" s="2">
+      <c r="E182" s="1">
         <v>45838</v>
       </c>
       <c r="F182">
@@ -6692,14 +6644,14 @@
       <c r="D183">
         <v>5.89</v>
       </c>
-      <c r="E183" s="2">
+      <c r="E183" s="1">
         <v>45839</v>
       </c>
       <c r="F183">
         <v>265.05</v>
       </c>
       <c r="G183">
-        <v>7686.45</v>
+        <v>7686.450000000001</v>
       </c>
       <c r="H183">
         <v>1537.29</v>
@@ -6718,7 +6670,7 @@
       <c r="D184">
         <v>8.51</v>
       </c>
-      <c r="E184" s="2">
+      <c r="E184" s="1">
         <v>45840</v>
       </c>
       <c r="F184">
@@ -6744,7 +6696,7 @@
       <c r="D185">
         <v>123.09</v>
       </c>
-      <c r="E185" s="2">
+      <c r="E185" s="1">
         <v>45841</v>
       </c>
       <c r="F185">
@@ -6770,7 +6722,7 @@
       <c r="D186">
         <v>97.53</v>
       </c>
-      <c r="E186" s="2">
+      <c r="E186" s="1">
         <v>45842</v>
       </c>
       <c r="F186">
@@ -6796,7 +6748,7 @@
       <c r="D187">
         <v>137.59</v>
       </c>
-      <c r="E187" s="2">
+      <c r="E187" s="1">
         <v>45843</v>
       </c>
       <c r="F187">
@@ -6822,7 +6774,7 @@
       <c r="D188">
         <v>120.15</v>
       </c>
-      <c r="E188" s="2">
+      <c r="E188" s="1">
         <v>45844</v>
       </c>
       <c r="F188">
@@ -6848,17 +6800,17 @@
       <c r="D189">
         <v>82.15000000000001</v>
       </c>
-      <c r="E189" s="2">
+      <c r="E189" s="1">
         <v>45845</v>
       </c>
       <c r="F189">
         <v>3696.75</v>
       </c>
       <c r="G189">
-        <v>351191.25</v>
+        <v>351191.2500000001</v>
       </c>
       <c r="H189">
-        <v>70238.25</v>
+        <v>70238.25000000001</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -6874,7 +6826,7 @@
       <c r="D190">
         <v>42.92</v>
       </c>
-      <c r="E190" s="2">
+      <c r="E190" s="1">
         <v>45846</v>
       </c>
       <c r="F190">
@@ -6900,7 +6852,7 @@
       <c r="D191">
         <v>142.71</v>
       </c>
-      <c r="E191" s="2">
+      <c r="E191" s="1">
         <v>45847</v>
       </c>
       <c r="F191">
@@ -6910,7 +6862,7 @@
         <v>308253.6</v>
       </c>
       <c r="H191">
-        <v>61650.72</v>
+        <v>61650.72000000001</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -6926,7 +6878,7 @@
       <c r="D192">
         <v>22.85</v>
       </c>
-      <c r="E192" s="2">
+      <c r="E192" s="1">
         <v>45848</v>
       </c>
       <c r="F192">
@@ -6952,7 +6904,7 @@
       <c r="D193">
         <v>7.4</v>
       </c>
-      <c r="E193" s="2">
+      <c r="E193" s="1">
         <v>45849</v>
       </c>
       <c r="F193">
@@ -6978,7 +6930,7 @@
       <c r="D194">
         <v>44.58</v>
       </c>
-      <c r="E194" s="2">
+      <c r="E194" s="1">
         <v>45850</v>
       </c>
       <c r="F194">
@@ -7004,7 +6956,7 @@
       <c r="D195">
         <v>18.97</v>
       </c>
-      <c r="E195" s="2">
+      <c r="E195" s="1">
         <v>45851</v>
       </c>
       <c r="F195">
@@ -7030,17 +6982,17 @@
       <c r="D196">
         <v>108.13</v>
       </c>
-      <c r="E196" s="2">
+      <c r="E196" s="1">
         <v>45852</v>
       </c>
       <c r="F196">
         <v>4865.849999999999</v>
       </c>
       <c r="G196">
-        <v>403865.55</v>
+        <v>403865.5499999999</v>
       </c>
       <c r="H196">
-        <v>80773.11</v>
+        <v>80773.10999999999</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -7056,7 +7008,7 @@
       <c r="D197">
         <v>34.04</v>
       </c>
-      <c r="E197" s="2">
+      <c r="E197" s="1">
         <v>45853</v>
       </c>
       <c r="F197">
@@ -7082,7 +7034,7 @@
       <c r="D198">
         <v>106.69</v>
       </c>
-      <c r="E198" s="2">
+      <c r="E198" s="1">
         <v>45854</v>
       </c>
       <c r="F198">
@@ -7108,7 +7060,7 @@
       <c r="D199">
         <v>14.62</v>
       </c>
-      <c r="E199" s="2">
+      <c r="E199" s="1">
         <v>45855</v>
       </c>
       <c r="F199">
@@ -7134,7 +7086,7 @@
       <c r="D200">
         <v>8.039999999999999</v>
       </c>
-      <c r="E200" s="2">
+      <c r="E200" s="1">
         <v>45856</v>
       </c>
       <c r="F200">
@@ -7144,7 +7096,7 @@
         <v>27496.8</v>
       </c>
       <c r="H200">
-        <v>5499.360000000001</v>
+        <v>5499.36</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -7160,7 +7112,7 @@
       <c r="D201">
         <v>15.83</v>
       </c>
-      <c r="E201" s="2">
+      <c r="E201" s="1">
         <v>45857</v>
       </c>
       <c r="F201">
@@ -7186,7 +7138,7 @@
       <c r="D202">
         <v>24.09</v>
       </c>
-      <c r="E202" s="2">
+      <c r="E202" s="1">
         <v>45858</v>
       </c>
       <c r="F202">
@@ -7212,7 +7164,7 @@
       <c r="D203">
         <v>95.58</v>
       </c>
-      <c r="E203" s="2">
+      <c r="E203" s="1">
         <v>45859</v>
       </c>
       <c r="F203">
@@ -7238,7 +7190,7 @@
       <c r="D204">
         <v>20.76</v>
       </c>
-      <c r="E204" s="2">
+      <c r="E204" s="1">
         <v>45860</v>
       </c>
       <c r="F204">
@@ -7264,7 +7216,7 @@
       <c r="D205">
         <v>122.98</v>
       </c>
-      <c r="E205" s="2">
+      <c r="E205" s="1">
         <v>45861</v>
       </c>
       <c r="F205">
@@ -7290,7 +7242,7 @@
       <c r="D206">
         <v>136.82</v>
       </c>
-      <c r="E206" s="2">
+      <c r="E206" s="1">
         <v>45862</v>
       </c>
       <c r="F206">
@@ -7316,14 +7268,14 @@
       <c r="D207">
         <v>140.93</v>
       </c>
-      <c r="E207" s="2">
+      <c r="E207" s="1">
         <v>45863</v>
       </c>
       <c r="F207">
         <v>6341.85</v>
       </c>
       <c r="G207">
-        <v>615159.45</v>
+        <v>615159.4500000001</v>
       </c>
       <c r="H207">
         <v>123031.89</v>
@@ -7342,7 +7294,7 @@
       <c r="D208">
         <v>47.13</v>
       </c>
-      <c r="E208" s="2">
+      <c r="E208" s="1">
         <v>45864</v>
       </c>
       <c r="F208">
@@ -7368,7 +7320,7 @@
       <c r="D209">
         <v>74.62</v>
       </c>
-      <c r="E209" s="2">
+      <c r="E209" s="1">
         <v>45865</v>
       </c>
       <c r="F209">
@@ -7394,7 +7346,7 @@
       <c r="D210">
         <v>56.91</v>
       </c>
-      <c r="E210" s="2">
+      <c r="E210" s="1">
         <v>45866</v>
       </c>
       <c r="F210">
@@ -7404,7 +7356,7 @@
         <v>217680.75</v>
       </c>
       <c r="H210">
-        <v>43536.15</v>
+        <v>43536.14999999999</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -7420,14 +7372,14 @@
       <c r="D211">
         <v>33.34</v>
       </c>
-      <c r="E211" s="2">
+      <c r="E211" s="1">
         <v>45867</v>
       </c>
       <c r="F211">
         <v>1500.3</v>
       </c>
       <c r="G211">
-        <v>57011.4</v>
+        <v>57011.40000000001</v>
       </c>
       <c r="H211">
         <v>11402.28</v>
@@ -7446,7 +7398,7 @@
       <c r="D212">
         <v>77.8</v>
       </c>
-      <c r="E212" s="2">
+      <c r="E212" s="1">
         <v>45868</v>
       </c>
       <c r="F212">
@@ -7472,7 +7424,7 @@
       <c r="D213">
         <v>110.41</v>
       </c>
-      <c r="E213" s="2">
+      <c r="E213" s="1">
         <v>45869</v>
       </c>
       <c r="F213">
@@ -7498,14 +7450,14 @@
       <c r="D214">
         <v>142.95</v>
       </c>
-      <c r="E214" s="2">
+      <c r="E214" s="1">
         <v>45870</v>
       </c>
       <c r="F214">
         <v>6432.749999999999</v>
       </c>
       <c r="G214">
-        <v>598245.75</v>
+        <v>598245.7499999999</v>
       </c>
       <c r="H214">
         <v>119649.15</v>
@@ -7524,7 +7476,7 @@
       <c r="D215">
         <v>116.3</v>
       </c>
-      <c r="E215" s="2">
+      <c r="E215" s="1">
         <v>45871</v>
       </c>
       <c r="F215">
@@ -7550,7 +7502,7 @@
       <c r="D216">
         <v>115.65</v>
       </c>
-      <c r="E216" s="2">
+      <c r="E216" s="1">
         <v>45872</v>
       </c>
       <c r="F216">
@@ -7576,7 +7528,7 @@
       <c r="D217">
         <v>45.25</v>
       </c>
-      <c r="E217" s="2">
+      <c r="E217" s="1">
         <v>45873</v>
       </c>
       <c r="F217">
@@ -7602,7 +7554,7 @@
       <c r="D218">
         <v>31.62</v>
       </c>
-      <c r="E218" s="2">
+      <c r="E218" s="1">
         <v>45874</v>
       </c>
       <c r="F218">
@@ -7628,7 +7580,7 @@
       <c r="D219">
         <v>8.18</v>
       </c>
-      <c r="E219" s="2">
+      <c r="E219" s="1">
         <v>45875</v>
       </c>
       <c r="F219">
@@ -7654,7 +7606,7 @@
       <c r="D220">
         <v>39.04</v>
       </c>
-      <c r="E220" s="2">
+      <c r="E220" s="1">
         <v>45876</v>
       </c>
       <c r="F220">
@@ -7680,14 +7632,14 @@
       <c r="D221">
         <v>78.77</v>
       </c>
-      <c r="E221" s="2">
+      <c r="E221" s="1">
         <v>45877</v>
       </c>
       <c r="F221">
         <v>3544.65</v>
       </c>
       <c r="G221">
-        <v>38991.15</v>
+        <v>38991.14999999999</v>
       </c>
       <c r="H221">
         <v>7798.23</v>
@@ -7706,7 +7658,7 @@
       <c r="D222">
         <v>130.43</v>
       </c>
-      <c r="E222" s="2">
+      <c r="E222" s="1">
         <v>45878</v>
       </c>
       <c r="F222">
@@ -7732,7 +7684,7 @@
       <c r="D223">
         <v>39.59</v>
       </c>
-      <c r="E223" s="2">
+      <c r="E223" s="1">
         <v>45879</v>
       </c>
       <c r="F223">
@@ -7758,7 +7710,7 @@
       <c r="D224">
         <v>7</v>
       </c>
-      <c r="E224" s="2">
+      <c r="E224" s="1">
         <v>45880</v>
       </c>
       <c r="F224">
@@ -7784,7 +7736,7 @@
       <c r="D225">
         <v>125.94</v>
       </c>
-      <c r="E225" s="2">
+      <c r="E225" s="1">
         <v>45881</v>
       </c>
       <c r="F225">
@@ -7810,7 +7762,7 @@
       <c r="D226">
         <v>124.2</v>
       </c>
-      <c r="E226" s="2">
+      <c r="E226" s="1">
         <v>45882</v>
       </c>
       <c r="F226">
@@ -7836,7 +7788,7 @@
       <c r="D227">
         <v>111.05</v>
       </c>
-      <c r="E227" s="2">
+      <c r="E227" s="1">
         <v>45883</v>
       </c>
       <c r="F227">
@@ -7862,14 +7814,14 @@
       <c r="D228">
         <v>51.27</v>
       </c>
-      <c r="E228" s="2">
+      <c r="E228" s="1">
         <v>45884</v>
       </c>
       <c r="F228">
         <v>2307.15</v>
       </c>
       <c r="G228">
-        <v>83057.39999999999</v>
+        <v>83057.40000000001</v>
       </c>
       <c r="H228">
         <v>16611.48</v>
@@ -7888,14 +7840,14 @@
       <c r="D229">
         <v>138.84</v>
       </c>
-      <c r="E229" s="2">
+      <c r="E229" s="1">
         <v>45885</v>
       </c>
       <c r="F229">
         <v>6247.8</v>
       </c>
       <c r="G229">
-        <v>81221.39999999999</v>
+        <v>81221.40000000001</v>
       </c>
       <c r="H229">
         <v>16244.28</v>
@@ -7914,7 +7866,7 @@
       <c r="D230">
         <v>32.93</v>
       </c>
-      <c r="E230" s="2">
+      <c r="E230" s="1">
         <v>45886</v>
       </c>
       <c r="F230">
@@ -7940,7 +7892,7 @@
       <c r="D231">
         <v>21.87</v>
       </c>
-      <c r="E231" s="2">
+      <c r="E231" s="1">
         <v>45887</v>
       </c>
       <c r="F231">
@@ -7966,7 +7918,7 @@
       <c r="D232">
         <v>26.86</v>
       </c>
-      <c r="E232" s="2">
+      <c r="E232" s="1">
         <v>45888</v>
       </c>
       <c r="F232">
@@ -7992,7 +7944,7 @@
       <c r="D233">
         <v>55.67</v>
       </c>
-      <c r="E233" s="2">
+      <c r="E233" s="1">
         <v>45889</v>
       </c>
       <c r="F233">
@@ -8018,7 +7970,7 @@
       <c r="D234">
         <v>103.15</v>
       </c>
-      <c r="E234" s="2">
+      <c r="E234" s="1">
         <v>45890</v>
       </c>
       <c r="F234">
@@ -8044,7 +7996,7 @@
       <c r="D235">
         <v>99.12</v>
       </c>
-      <c r="E235" s="2">
+      <c r="E235" s="1">
         <v>45891</v>
       </c>
       <c r="F235">
@@ -8070,7 +8022,7 @@
       <c r="D236">
         <v>34.49</v>
       </c>
-      <c r="E236" s="2">
+      <c r="E236" s="1">
         <v>45892</v>
       </c>
       <c r="F236">
@@ -8096,7 +8048,7 @@
       <c r="D237">
         <v>61.01</v>
       </c>
-      <c r="E237" s="2">
+      <c r="E237" s="1">
         <v>45893</v>
       </c>
       <c r="F237">
@@ -8122,7 +8074,7 @@
       <c r="D238">
         <v>58.8</v>
       </c>
-      <c r="E238" s="2">
+      <c r="E238" s="1">
         <v>45894</v>
       </c>
       <c r="F238">
@@ -8148,7 +8100,7 @@
       <c r="D239">
         <v>11.46</v>
       </c>
-      <c r="E239" s="2">
+      <c r="E239" s="1">
         <v>45895</v>
       </c>
       <c r="F239">
@@ -8174,7 +8126,7 @@
       <c r="D240">
         <v>141.47</v>
       </c>
-      <c r="E240" s="2">
+      <c r="E240" s="1">
         <v>45896</v>
       </c>
       <c r="F240">
@@ -8200,7 +8152,7 @@
       <c r="D241">
         <v>27</v>
       </c>
-      <c r="E241" s="2">
+      <c r="E241" s="1">
         <v>45897</v>
       </c>
       <c r="F241">
@@ -8226,7 +8178,7 @@
       <c r="D242">
         <v>8.890000000000001</v>
       </c>
-      <c r="E242" s="2">
+      <c r="E242" s="1">
         <v>45898</v>
       </c>
       <c r="F242">
@@ -8252,7 +8204,7 @@
       <c r="D243">
         <v>123.98</v>
       </c>
-      <c r="E243" s="2">
+      <c r="E243" s="1">
         <v>45899</v>
       </c>
       <c r="F243">
@@ -8262,7 +8214,7 @@
         <v>133898.4</v>
       </c>
       <c r="H243">
-        <v>26779.68</v>
+        <v>26779.68000000001</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -8278,14 +8230,14 @@
       <c r="D244">
         <v>6.98</v>
       </c>
-      <c r="E244" s="2">
+      <c r="E244" s="1">
         <v>45900</v>
       </c>
       <c r="F244">
         <v>314.1</v>
       </c>
       <c r="G244">
-        <v>9108.9</v>
+        <v>9108.900000000001</v>
       </c>
       <c r="H244">
         <v>1821.78</v>
@@ -8304,7 +8256,7 @@
       <c r="D245">
         <v>12.06</v>
       </c>
-      <c r="E245" s="2">
+      <c r="E245" s="1">
         <v>45901</v>
       </c>
       <c r="F245">
@@ -8330,7 +8282,7 @@
       <c r="D246">
         <v>37.31</v>
       </c>
-      <c r="E246" s="2">
+      <c r="E246" s="1">
         <v>45902</v>
       </c>
       <c r="F246">
@@ -8356,7 +8308,7 @@
       <c r="D247">
         <v>11.1</v>
       </c>
-      <c r="E247" s="2">
+      <c r="E247" s="1">
         <v>45903</v>
       </c>
       <c r="F247">
@@ -8382,7 +8334,7 @@
       <c r="D248">
         <v>21.3</v>
       </c>
-      <c r="E248" s="2">
+      <c r="E248" s="1">
         <v>45904</v>
       </c>
       <c r="F248">
@@ -8408,7 +8360,7 @@
       <c r="D249">
         <v>58.54</v>
       </c>
-      <c r="E249" s="2">
+      <c r="E249" s="1">
         <v>45905</v>
       </c>
       <c r="F249">
@@ -8434,7 +8386,7 @@
       <c r="D250">
         <v>113.57</v>
       </c>
-      <c r="E250" s="2">
+      <c r="E250" s="1">
         <v>45906</v>
       </c>
       <c r="F250">
@@ -8444,7 +8396,7 @@
         <v>373077.45</v>
       </c>
       <c r="H250">
-        <v>74615.49000000001</v>
+        <v>74615.48999999999</v>
       </c>
     </row>
     <row r="251" spans="1:8">
@@ -8460,7 +8412,7 @@
       <c r="D251">
         <v>141.75</v>
       </c>
-      <c r="E251" s="2">
+      <c r="E251" s="1">
         <v>45907</v>
       </c>
       <c r="F251">
@@ -8486,7 +8438,7 @@
       <c r="D252">
         <v>129.75</v>
       </c>
-      <c r="E252" s="2">
+      <c r="E252" s="1">
         <v>45908</v>
       </c>
       <c r="F252">
@@ -8512,17 +8464,17 @@
       <c r="D253">
         <v>131.7</v>
       </c>
-      <c r="E253" s="2">
+      <c r="E253" s="1">
         <v>45909</v>
       </c>
       <c r="F253">
         <v>5926.499999999999</v>
       </c>
       <c r="G253">
-        <v>325957.5</v>
+        <v>325957.4999999999</v>
       </c>
       <c r="H253">
-        <v>65191.5</v>
+        <v>65191.49999999999</v>
       </c>
     </row>
     <row r="254" spans="1:8">
@@ -8538,7 +8490,7 @@
       <c r="D254">
         <v>79.08</v>
       </c>
-      <c r="E254" s="2">
+      <c r="E254" s="1">
         <v>45910</v>
       </c>
       <c r="F254">
@@ -8564,7 +8516,7 @@
       <c r="D255">
         <v>134.12</v>
       </c>
-      <c r="E255" s="2">
+      <c r="E255" s="1">
         <v>45911</v>
       </c>
       <c r="F255">
@@ -8590,7 +8542,7 @@
       <c r="D256">
         <v>63.35</v>
       </c>
-      <c r="E256" s="2">
+      <c r="E256" s="1">
         <v>45912</v>
       </c>
       <c r="F256">
@@ -8616,7 +8568,7 @@
       <c r="D257">
         <v>78.19</v>
       </c>
-      <c r="E257" s="2">
+      <c r="E257" s="1">
         <v>45913</v>
       </c>
       <c r="F257">
@@ -8642,7 +8594,7 @@
       <c r="D258">
         <v>119.83</v>
       </c>
-      <c r="E258" s="2">
+      <c r="E258" s="1">
         <v>45914</v>
       </c>
       <c r="F258">
@@ -8668,7 +8620,7 @@
       <c r="D259">
         <v>126.17</v>
       </c>
-      <c r="E259" s="2">
+      <c r="E259" s="1">
         <v>45915</v>
       </c>
       <c r="F259">
@@ -8678,7 +8630,7 @@
         <v>39743.55</v>
       </c>
       <c r="H259">
-        <v>7948.710000000001</v>
+        <v>7948.709999999999</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -8694,7 +8646,7 @@
       <c r="D260">
         <v>96.25</v>
       </c>
-      <c r="E260" s="2">
+      <c r="E260" s="1">
         <v>45916</v>
       </c>
       <c r="F260">
@@ -8720,7 +8672,7 @@
       <c r="D261">
         <v>53.02</v>
       </c>
-      <c r="E261" s="2">
+      <c r="E261" s="1">
         <v>45917</v>
       </c>
       <c r="F261">
@@ -8746,7 +8698,7 @@
       <c r="D262">
         <v>6.74</v>
       </c>
-      <c r="E262" s="2">
+      <c r="E262" s="1">
         <v>45918</v>
       </c>
       <c r="F262">
@@ -8772,7 +8724,7 @@
       <c r="D263">
         <v>64.38</v>
       </c>
-      <c r="E263" s="2">
+      <c r="E263" s="1">
         <v>45919</v>
       </c>
       <c r="F263">
@@ -8798,7 +8750,7 @@
       <c r="D264">
         <v>86.38</v>
       </c>
-      <c r="E264" s="2">
+      <c r="E264" s="1">
         <v>45920</v>
       </c>
       <c r="F264">
@@ -8824,7 +8776,7 @@
       <c r="D265">
         <v>89</v>
       </c>
-      <c r="E265" s="2">
+      <c r="E265" s="1">
         <v>45921</v>
       </c>
       <c r="F265">
@@ -8850,7 +8802,7 @@
       <c r="D266">
         <v>74.84</v>
       </c>
-      <c r="E266" s="2">
+      <c r="E266" s="1">
         <v>45922</v>
       </c>
       <c r="F266">
@@ -8860,7 +8812,7 @@
         <v>188596.8</v>
       </c>
       <c r="H266">
-        <v>37719.36</v>
+        <v>37719.36000000001</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -8876,7 +8828,7 @@
       <c r="D267">
         <v>13.81</v>
       </c>
-      <c r="E267" s="2">
+      <c r="E267" s="1">
         <v>45923</v>
       </c>
       <c r="F267">
@@ -8902,7 +8854,7 @@
       <c r="D268">
         <v>118.99</v>
       </c>
-      <c r="E268" s="2">
+      <c r="E268" s="1">
         <v>45924</v>
       </c>
       <c r="F268">
@@ -8928,14 +8880,14 @@
       <c r="D269">
         <v>94.86</v>
       </c>
-      <c r="E269" s="2">
+      <c r="E269" s="1">
         <v>45925</v>
       </c>
       <c r="F269">
         <v>4268.7</v>
       </c>
       <c r="G269">
-        <v>98180.10000000001</v>
+        <v>98180.09999999999</v>
       </c>
       <c r="H269">
         <v>19636.02</v>
@@ -8954,7 +8906,7 @@
       <c r="D270">
         <v>79.33</v>
       </c>
-      <c r="E270" s="2">
+      <c r="E270" s="1">
         <v>45926</v>
       </c>
       <c r="F270">
@@ -8964,7 +8916,7 @@
         <v>239179.95</v>
       </c>
       <c r="H270">
-        <v>47835.99000000001</v>
+        <v>47835.99</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -8980,7 +8932,7 @@
       <c r="D271">
         <v>42.67</v>
       </c>
-      <c r="E271" s="2">
+      <c r="E271" s="1">
         <v>45927</v>
       </c>
       <c r="F271">
@@ -9006,7 +8958,7 @@
       <c r="D272">
         <v>123.08</v>
       </c>
-      <c r="E272" s="2">
+      <c r="E272" s="1">
         <v>45928</v>
       </c>
       <c r="F272">
@@ -9032,7 +8984,7 @@
       <c r="D273">
         <v>47.97</v>
       </c>
-      <c r="E273" s="2">
+      <c r="E273" s="1">
         <v>45929</v>
       </c>
       <c r="F273">
@@ -9058,7 +9010,7 @@
       <c r="D274">
         <v>73.75</v>
       </c>
-      <c r="E274" s="2">
+      <c r="E274" s="1">
         <v>45930</v>
       </c>
       <c r="F274">
@@ -9084,7 +9036,7 @@
       <c r="D275">
         <v>142.17</v>
       </c>
-      <c r="E275" s="2">
+      <c r="E275" s="1">
         <v>45931</v>
       </c>
       <c r="F275">
@@ -9110,7 +9062,7 @@
       <c r="D276">
         <v>9.279999999999999</v>
       </c>
-      <c r="E276" s="2">
+      <c r="E276" s="1">
         <v>45932</v>
       </c>
       <c r="F276">
@@ -9136,7 +9088,7 @@
       <c r="D277">
         <v>128.14</v>
       </c>
-      <c r="E277" s="2">
+      <c r="E277" s="1">
         <v>45933</v>
       </c>
       <c r="F277">
@@ -9162,7 +9114,7 @@
       <c r="D278">
         <v>131.42</v>
       </c>
-      <c r="E278" s="2">
+      <c r="E278" s="1">
         <v>45934</v>
       </c>
       <c r="F278">
@@ -9188,7 +9140,7 @@
       <c r="D279">
         <v>106.67</v>
       </c>
-      <c r="E279" s="2">
+      <c r="E279" s="1">
         <v>45935</v>
       </c>
       <c r="F279">
@@ -9198,7 +9150,7 @@
         <v>206406.45</v>
       </c>
       <c r="H279">
-        <v>41281.29000000001</v>
+        <v>41281.29</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -9214,7 +9166,7 @@
       <c r="D280">
         <v>139.78</v>
       </c>
-      <c r="E280" s="2">
+      <c r="E280" s="1">
         <v>45936</v>
       </c>
       <c r="F280">
@@ -9240,14 +9192,14 @@
       <c r="D281">
         <v>67.98</v>
       </c>
-      <c r="E281" s="2">
+      <c r="E281" s="1">
         <v>45937</v>
       </c>
       <c r="F281">
         <v>3059.1</v>
       </c>
       <c r="G281">
-        <v>6118.2</v>
+        <v>6118.200000000001</v>
       </c>
       <c r="H281">
         <v>1223.64</v>
@@ -9266,7 +9218,7 @@
       <c r="D282">
         <v>95.36</v>
       </c>
-      <c r="E282" s="2">
+      <c r="E282" s="1">
         <v>45938</v>
       </c>
       <c r="F282">
@@ -9292,7 +9244,7 @@
       <c r="D283">
         <v>7.54</v>
       </c>
-      <c r="E283" s="2">
+      <c r="E283" s="1">
         <v>45939</v>
       </c>
       <c r="F283">
@@ -9302,7 +9254,7 @@
         <v>26126.1</v>
       </c>
       <c r="H283">
-        <v>5225.22</v>
+        <v>5225.220000000001</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -9318,7 +9270,7 @@
       <c r="D284">
         <v>55.2</v>
       </c>
-      <c r="E284" s="2">
+      <c r="E284" s="1">
         <v>45940</v>
       </c>
       <c r="F284">
@@ -9344,7 +9296,7 @@
       <c r="D285">
         <v>11.6</v>
       </c>
-      <c r="E285" s="2">
+      <c r="E285" s="1">
         <v>45941</v>
       </c>
       <c r="F285">
@@ -9370,7 +9322,7 @@
       <c r="D286">
         <v>59.09</v>
       </c>
-      <c r="E286" s="2">
+      <c r="E286" s="1">
         <v>45942</v>
       </c>
       <c r="F286">
@@ -9380,7 +9332,7 @@
         <v>255268.8</v>
       </c>
       <c r="H286">
-        <v>51053.76</v>
+        <v>51053.76000000001</v>
       </c>
     </row>
     <row r="287" spans="1:8">
@@ -9396,7 +9348,7 @@
       <c r="D287">
         <v>11.84</v>
       </c>
-      <c r="E287" s="2">
+      <c r="E287" s="1">
         <v>45943</v>
       </c>
       <c r="F287">
@@ -9406,7 +9358,7 @@
         <v>35164.8</v>
       </c>
       <c r="H287">
-        <v>7032.960000000001</v>
+        <v>7032.959999999999</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -9422,7 +9374,7 @@
       <c r="D288">
         <v>132.16</v>
       </c>
-      <c r="E288" s="2">
+      <c r="E288" s="1">
         <v>45944</v>
       </c>
       <c r="F288">
@@ -9448,7 +9400,7 @@
       <c r="D289">
         <v>17.72</v>
       </c>
-      <c r="E289" s="2">
+      <c r="E289" s="1">
         <v>45945</v>
       </c>
       <c r="F289">
@@ -9474,7 +9426,7 @@
       <c r="D290">
         <v>145.18</v>
       </c>
-      <c r="E290" s="2">
+      <c r="E290" s="1">
         <v>45946</v>
       </c>
       <c r="F290">
@@ -9500,7 +9452,7 @@
       <c r="D291">
         <v>12.34</v>
       </c>
-      <c r="E291" s="2">
+      <c r="E291" s="1">
         <v>45947</v>
       </c>
       <c r="F291">
@@ -9526,7 +9478,7 @@
       <c r="D292">
         <v>66.09999999999999</v>
       </c>
-      <c r="E292" s="2">
+      <c r="E292" s="1">
         <v>45948</v>
       </c>
       <c r="F292">
@@ -9552,7 +9504,7 @@
       <c r="D293">
         <v>29.03</v>
       </c>
-      <c r="E293" s="2">
+      <c r="E293" s="1">
         <v>45949</v>
       </c>
       <c r="F293">
@@ -9578,7 +9530,7 @@
       <c r="D294">
         <v>19.39</v>
       </c>
-      <c r="E294" s="2">
+      <c r="E294" s="1">
         <v>45950</v>
       </c>
       <c r="F294">
@@ -9588,7 +9540,7 @@
         <v>34029.45</v>
       </c>
       <c r="H294">
-        <v>6805.889999999999</v>
+        <v>6805.890000000001</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -9604,7 +9556,7 @@
       <c r="D295">
         <v>145.16</v>
       </c>
-      <c r="E295" s="2">
+      <c r="E295" s="1">
         <v>45951</v>
       </c>
       <c r="F295">
@@ -9630,7 +9582,7 @@
       <c r="D296">
         <v>112.56</v>
       </c>
-      <c r="E296" s="2">
+      <c r="E296" s="1">
         <v>45952</v>
       </c>
       <c r="F296">
@@ -9656,7 +9608,7 @@
       <c r="D297">
         <v>12.34</v>
       </c>
-      <c r="E297" s="2">
+      <c r="E297" s="1">
         <v>45953</v>
       </c>
       <c r="F297">
@@ -9682,7 +9634,7 @@
       <c r="D298">
         <v>70.56999999999999</v>
       </c>
-      <c r="E298" s="2">
+      <c r="E298" s="1">
         <v>45954</v>
       </c>
       <c r="F298">
@@ -9692,7 +9644,7 @@
         <v>22229.55</v>
       </c>
       <c r="H298">
-        <v>4445.91</v>
+        <v>4445.909999999999</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -9708,7 +9660,7 @@
       <c r="D299">
         <v>87.34999999999999</v>
       </c>
-      <c r="E299" s="2">
+      <c r="E299" s="1">
         <v>45955</v>
       </c>
       <c r="F299">
@@ -9718,7 +9670,7 @@
         <v>196537.5</v>
       </c>
       <c r="H299">
-        <v>39307.5</v>
+        <v>39307.49999999999</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -9734,7 +9686,7 @@
       <c r="D300">
         <v>128.63</v>
       </c>
-      <c r="E300" s="2">
+      <c r="E300" s="1">
         <v>45956</v>
       </c>
       <c r="F300">
@@ -9760,7 +9712,7 @@
       <c r="D301">
         <v>16.94</v>
       </c>
-      <c r="E301" s="2">
+      <c r="E301" s="1">
         <v>45957</v>
       </c>
       <c r="F301">
@@ -9786,7 +9738,7 @@
       <c r="D302">
         <v>5.54</v>
       </c>
-      <c r="E302" s="2">
+      <c r="E302" s="1">
         <v>45958</v>
       </c>
       <c r="F302">
@@ -9812,7 +9764,7 @@
       <c r="D303">
         <v>94.11</v>
       </c>
-      <c r="E303" s="2">
+      <c r="E303" s="1">
         <v>45959</v>
       </c>
       <c r="F303">
@@ -9838,7 +9790,7 @@
       <c r="D304">
         <v>99.05</v>
       </c>
-      <c r="E304" s="2">
+      <c r="E304" s="1">
         <v>45960</v>
       </c>
       <c r="F304">
@@ -9864,7 +9816,7 @@
       <c r="D305">
         <v>113.73</v>
       </c>
-      <c r="E305" s="2">
+      <c r="E305" s="1">
         <v>45961</v>
       </c>
       <c r="F305">
@@ -9890,7 +9842,7 @@
       <c r="D306">
         <v>136.84</v>
       </c>
-      <c r="E306" s="2">
+      <c r="E306" s="1">
         <v>45962</v>
       </c>
       <c r="F306">
@@ -9916,7 +9868,7 @@
       <c r="D307">
         <v>78.98</v>
       </c>
-      <c r="E307" s="2">
+      <c r="E307" s="1">
         <v>45963</v>
       </c>
       <c r="F307">
@@ -9942,7 +9894,7 @@
       <c r="D308">
         <v>134.93</v>
       </c>
-      <c r="E308" s="2">
+      <c r="E308" s="1">
         <v>45964</v>
       </c>
       <c r="F308">
@@ -9968,7 +9920,7 @@
       <c r="D309">
         <v>129.62</v>
       </c>
-      <c r="E309" s="2">
+      <c r="E309" s="1">
         <v>45965</v>
       </c>
       <c r="F309">
@@ -9994,17 +9946,17 @@
       <c r="D310">
         <v>146.3</v>
       </c>
-      <c r="E310" s="2">
+      <c r="E310" s="1">
         <v>45966</v>
       </c>
       <c r="F310">
         <v>6583.500000000001</v>
       </c>
       <c r="G310">
-        <v>322591.5</v>
+        <v>322591.5000000001</v>
       </c>
       <c r="H310">
-        <v>64518.3</v>
+        <v>64518.30000000002</v>
       </c>
     </row>
     <row r="311" spans="1:8">
@@ -10020,7 +9972,7 @@
       <c r="D311">
         <v>91.01000000000001</v>
       </c>
-      <c r="E311" s="2">
+      <c r="E311" s="1">
         <v>45967</v>
       </c>
       <c r="F311">
@@ -10046,7 +9998,7 @@
       <c r="D312">
         <v>6.18</v>
       </c>
-      <c r="E312" s="2">
+      <c r="E312" s="1">
         <v>45968</v>
       </c>
       <c r="F312">
@@ -10072,7 +10024,7 @@
       <c r="D313">
         <v>128.59</v>
       </c>
-      <c r="E313" s="2">
+      <c r="E313" s="1">
         <v>45969</v>
       </c>
       <c r="F313">
@@ -10082,7 +10034,7 @@
         <v>474497.1</v>
       </c>
       <c r="H313">
-        <v>94899.42</v>
+        <v>94899.42000000001</v>
       </c>
     </row>
     <row r="314" spans="1:8">
@@ -10098,7 +10050,7 @@
       <c r="D314">
         <v>40.72</v>
       </c>
-      <c r="E314" s="2">
+      <c r="E314" s="1">
         <v>45970</v>
       </c>
       <c r="F314">
@@ -10124,7 +10076,7 @@
       <c r="D315">
         <v>86.3</v>
       </c>
-      <c r="E315" s="2">
+      <c r="E315" s="1">
         <v>45971</v>
       </c>
       <c r="F315">
@@ -10150,14 +10102,14 @@
       <c r="D316">
         <v>104.02</v>
       </c>
-      <c r="E316" s="2">
+      <c r="E316" s="1">
         <v>45972</v>
       </c>
       <c r="F316">
         <v>4680.9</v>
       </c>
       <c r="G316">
-        <v>79575.3</v>
+        <v>79575.29999999999</v>
       </c>
       <c r="H316">
         <v>15915.06</v>
@@ -10176,7 +10128,7 @@
       <c r="D317">
         <v>98.73999999999999</v>
       </c>
-      <c r="E317" s="2">
+      <c r="E317" s="1">
         <v>45973</v>
       </c>
       <c r="F317">
@@ -10202,14 +10154,14 @@
       <c r="D318">
         <v>41.8</v>
       </c>
-      <c r="E318" s="2">
+      <c r="E318" s="1">
         <v>45974</v>
       </c>
       <c r="F318">
         <v>1881</v>
       </c>
       <c r="G318">
-        <v>9405</v>
+        <v>9404.999999999998</v>
       </c>
       <c r="H318">
         <v>1881</v>
@@ -10228,14 +10180,14 @@
       <c r="D319">
         <v>132.04</v>
       </c>
-      <c r="E319" s="2">
+      <c r="E319" s="1">
         <v>45975</v>
       </c>
       <c r="F319">
         <v>5941.799999999999</v>
       </c>
       <c r="G319">
-        <v>445635</v>
+        <v>445634.9999999999</v>
       </c>
       <c r="H319">
         <v>89127</v>
@@ -10254,14 +10206,14 @@
       <c r="D320">
         <v>5.04</v>
       </c>
-      <c r="E320" s="2">
+      <c r="E320" s="1">
         <v>45976</v>
       </c>
       <c r="F320">
         <v>226.8</v>
       </c>
       <c r="G320">
-        <v>9298.799999999999</v>
+        <v>9298.800000000001</v>
       </c>
       <c r="H320">
         <v>1859.76</v>
@@ -10280,7 +10232,7 @@
       <c r="D321">
         <v>9.49</v>
       </c>
-      <c r="E321" s="2">
+      <c r="E321" s="1">
         <v>45977</v>
       </c>
       <c r="F321">
@@ -10306,7 +10258,7 @@
       <c r="D322">
         <v>42.35</v>
       </c>
-      <c r="E322" s="2">
+      <c r="E322" s="1">
         <v>45978</v>
       </c>
       <c r="F322">
@@ -10332,7 +10284,7 @@
       <c r="D323">
         <v>122.31</v>
       </c>
-      <c r="E323" s="2">
+      <c r="E323" s="1">
         <v>45979</v>
       </c>
       <c r="F323">
@@ -10358,14 +10310,14 @@
       <c r="D324">
         <v>35.92</v>
       </c>
-      <c r="E324" s="2">
+      <c r="E324" s="1">
         <v>45980</v>
       </c>
       <c r="F324">
         <v>1616.4</v>
       </c>
       <c r="G324">
-        <v>82436.39999999999</v>
+        <v>82436.40000000001</v>
       </c>
       <c r="H324">
         <v>16487.28</v>
@@ -10384,7 +10336,7 @@
       <c r="D325">
         <v>147.7</v>
       </c>
-      <c r="E325" s="2">
+      <c r="E325" s="1">
         <v>45981</v>
       </c>
       <c r="F325">
@@ -10410,7 +10362,7 @@
       <c r="D326">
         <v>121.47</v>
       </c>
-      <c r="E326" s="2">
+      <c r="E326" s="1">
         <v>45982</v>
       </c>
       <c r="F326">
@@ -10436,7 +10388,7 @@
       <c r="D327">
         <v>57.03</v>
       </c>
-      <c r="E327" s="2">
+      <c r="E327" s="1">
         <v>45983</v>
       </c>
       <c r="F327">
@@ -10462,14 +10414,14 @@
       <c r="D328">
         <v>71.84999999999999</v>
       </c>
-      <c r="E328" s="2">
+      <c r="E328" s="1">
         <v>45984</v>
       </c>
       <c r="F328">
         <v>3233.25</v>
       </c>
       <c r="G328">
-        <v>58198.5</v>
+        <v>58198.49999999999</v>
       </c>
       <c r="H328">
         <v>11639.7</v>
@@ -10488,7 +10440,7 @@
       <c r="D329">
         <v>28.71</v>
       </c>
-      <c r="E329" s="2">
+      <c r="E329" s="1">
         <v>45985</v>
       </c>
       <c r="F329">
@@ -10514,7 +10466,7 @@
       <c r="D330">
         <v>82.59999999999999</v>
       </c>
-      <c r="E330" s="2">
+      <c r="E330" s="1">
         <v>45986</v>
       </c>
       <c r="F330">
@@ -10540,7 +10492,7 @@
       <c r="D331">
         <v>142.01</v>
       </c>
-      <c r="E331" s="2">
+      <c r="E331" s="1">
         <v>45987</v>
       </c>
       <c r="F331">
@@ -10566,7 +10518,7 @@
       <c r="D332">
         <v>26.09</v>
       </c>
-      <c r="E332" s="2">
+      <c r="E332" s="1">
         <v>45988</v>
       </c>
       <c r="F332">
@@ -10592,7 +10544,7 @@
       <c r="D333">
         <v>68.06</v>
       </c>
-      <c r="E333" s="2">
+      <c r="E333" s="1">
         <v>45989</v>
       </c>
       <c r="F333">
@@ -10618,14 +10570,14 @@
       <c r="D334">
         <v>51.99</v>
       </c>
-      <c r="E334" s="2">
+      <c r="E334" s="1">
         <v>45990</v>
       </c>
       <c r="F334">
         <v>2339.55</v>
       </c>
       <c r="G334">
-        <v>51470.1</v>
+        <v>51470.10000000001</v>
       </c>
       <c r="H334">
         <v>10294.02</v>
@@ -10644,7 +10596,7 @@
       <c r="D335">
         <v>71.16</v>
       </c>
-      <c r="E335" s="2">
+      <c r="E335" s="1">
         <v>45991</v>
       </c>
       <c r="F335">
@@ -10670,7 +10622,7 @@
       <c r="D336">
         <v>47.23</v>
       </c>
-      <c r="E336" s="2">
+      <c r="E336" s="1">
         <v>45992</v>
       </c>
       <c r="F336">
@@ -10696,7 +10648,7 @@
       <c r="D337">
         <v>125.36</v>
       </c>
-      <c r="E337" s="2">
+      <c r="E337" s="1">
         <v>45993</v>
       </c>
       <c r="F337">
@@ -10706,7 +10658,7 @@
         <v>406166.4</v>
       </c>
       <c r="H337">
-        <v>81233.28000000001</v>
+        <v>81233.28</v>
       </c>
     </row>
     <row r="338" spans="1:8">
@@ -10722,7 +10674,7 @@
       <c r="D338">
         <v>48.37</v>
       </c>
-      <c r="E338" s="2">
+      <c r="E338" s="1">
         <v>45994</v>
       </c>
       <c r="F338">
@@ -10748,7 +10700,7 @@
       <c r="D339">
         <v>139.58</v>
       </c>
-      <c r="E339" s="2">
+      <c r="E339" s="1">
         <v>45995</v>
       </c>
       <c r="F339">
@@ -10774,7 +10726,7 @@
       <c r="D340">
         <v>95.43000000000001</v>
       </c>
-      <c r="E340" s="2">
+      <c r="E340" s="1">
         <v>45996</v>
       </c>
       <c r="F340">
@@ -10800,7 +10752,7 @@
       <c r="D341">
         <v>149.27</v>
       </c>
-      <c r="E341" s="2">
+      <c r="E341" s="1">
         <v>45997</v>
       </c>
       <c r="F341">
@@ -10826,7 +10778,7 @@
       <c r="D342">
         <v>124.82</v>
       </c>
-      <c r="E342" s="2">
+      <c r="E342" s="1">
         <v>45998</v>
       </c>
       <c r="F342">
@@ -10852,7 +10804,7 @@
       <c r="D343">
         <v>115.78</v>
       </c>
-      <c r="E343" s="2">
+      <c r="E343" s="1">
         <v>45999</v>
       </c>
       <c r="F343">
@@ -10878,7 +10830,7 @@
       <c r="D344">
         <v>83.63</v>
       </c>
-      <c r="E344" s="2">
+      <c r="E344" s="1">
         <v>46000</v>
       </c>
       <c r="F344">
@@ -10888,7 +10840,7 @@
         <v>278487.9</v>
       </c>
       <c r="H344">
-        <v>55697.58000000001</v>
+        <v>55697.57999999999</v>
       </c>
     </row>
     <row r="345" spans="1:8">
@@ -10904,7 +10856,7 @@
       <c r="D345">
         <v>114.77</v>
       </c>
-      <c r="E345" s="2">
+      <c r="E345" s="1">
         <v>46001</v>
       </c>
       <c r="F345">
@@ -10930,7 +10882,7 @@
       <c r="D346">
         <v>91.16</v>
       </c>
-      <c r="E346" s="2">
+      <c r="E346" s="1">
         <v>46002</v>
       </c>
       <c r="F346">
@@ -10956,7 +10908,7 @@
       <c r="D347">
         <v>143.14</v>
       </c>
-      <c r="E347" s="2">
+      <c r="E347" s="1">
         <v>46003</v>
       </c>
       <c r="F347">
@@ -10966,7 +10918,7 @@
         <v>19323.9</v>
       </c>
       <c r="H347">
-        <v>3864.780000000001</v>
+        <v>3864.78</v>
       </c>
     </row>
     <row r="348" spans="1:8">
@@ -10982,7 +10934,7 @@
       <c r="D348">
         <v>61.14</v>
       </c>
-      <c r="E348" s="2">
+      <c r="E348" s="1">
         <v>46004</v>
       </c>
       <c r="F348">
@@ -11008,7 +10960,7 @@
       <c r="D349">
         <v>42.35</v>
       </c>
-      <c r="E349" s="2">
+      <c r="E349" s="1">
         <v>46005</v>
       </c>
       <c r="F349">
@@ -11034,7 +10986,7 @@
       <c r="D350">
         <v>72.39</v>
       </c>
-      <c r="E350" s="2">
+      <c r="E350" s="1">
         <v>46006</v>
       </c>
       <c r="F350">
@@ -11060,7 +11012,7 @@
       <c r="D351">
         <v>97.06</v>
       </c>
-      <c r="E351" s="2">
+      <c r="E351" s="1">
         <v>46007</v>
       </c>
       <c r="F351">
@@ -11086,7 +11038,7 @@
       <c r="D352">
         <v>77.18000000000001</v>
       </c>
-      <c r="E352" s="2">
+      <c r="E352" s="1">
         <v>46008</v>
       </c>
       <c r="F352">
@@ -11112,7 +11064,7 @@
       <c r="D353">
         <v>12.71</v>
       </c>
-      <c r="E353" s="2">
+      <c r="E353" s="1">
         <v>46009</v>
       </c>
       <c r="F353">
@@ -11138,7 +11090,7 @@
       <c r="D354">
         <v>31.45</v>
       </c>
-      <c r="E354" s="2">
+      <c r="E354" s="1">
         <v>46010</v>
       </c>
       <c r="F354">
@@ -11164,7 +11116,7 @@
       <c r="D355">
         <v>125.16</v>
       </c>
-      <c r="E355" s="2">
+      <c r="E355" s="1">
         <v>46011</v>
       </c>
       <c r="F355">
@@ -11190,7 +11142,7 @@
       <c r="D356">
         <v>104.9</v>
       </c>
-      <c r="E356" s="2">
+      <c r="E356" s="1">
         <v>46012</v>
       </c>
       <c r="F356">
@@ -11216,7 +11168,7 @@
       <c r="D357">
         <v>93.61</v>
       </c>
-      <c r="E357" s="2">
+      <c r="E357" s="1">
         <v>46013</v>
       </c>
       <c r="F357">
@@ -11242,7 +11194,7 @@
       <c r="D358">
         <v>110.29</v>
       </c>
-      <c r="E358" s="2">
+      <c r="E358" s="1">
         <v>46014</v>
       </c>
       <c r="F358">
@@ -11268,17 +11220,17 @@
       <c r="D359">
         <v>142.96</v>
       </c>
-      <c r="E359" s="2">
+      <c r="E359" s="1">
         <v>46015</v>
       </c>
       <c r="F359">
         <v>6433.200000000001</v>
       </c>
       <c r="G359">
-        <v>456757.2</v>
+        <v>456757.2000000001</v>
       </c>
       <c r="H359">
-        <v>91351.44</v>
+        <v>91351.44000000002</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -11294,7 +11246,7 @@
       <c r="D360">
         <v>75.04000000000001</v>
       </c>
-      <c r="E360" s="2">
+      <c r="E360" s="1">
         <v>46016</v>
       </c>
       <c r="F360">
@@ -11320,7 +11272,7 @@
       <c r="D361">
         <v>148.1</v>
       </c>
-      <c r="E361" s="2">
+      <c r="E361" s="1">
         <v>46017</v>
       </c>
       <c r="F361">
@@ -11346,7 +11298,7 @@
       <c r="D362">
         <v>148.27</v>
       </c>
-      <c r="E362" s="2">
+      <c r="E362" s="1">
         <v>46018</v>
       </c>
       <c r="F362">
@@ -11372,14 +11324,14 @@
       <c r="D363">
         <v>133.52</v>
       </c>
-      <c r="E363" s="2">
+      <c r="E363" s="1">
         <v>46019</v>
       </c>
       <c r="F363">
         <v>6008.400000000001</v>
       </c>
       <c r="G363">
-        <v>96134.39999999999</v>
+        <v>96134.40000000001</v>
       </c>
       <c r="H363">
         <v>19226.88</v>
@@ -11398,7 +11350,7 @@
       <c r="D364">
         <v>145.22</v>
       </c>
-      <c r="E364" s="2">
+      <c r="E364" s="1">
         <v>46020</v>
       </c>
       <c r="F364">
@@ -11424,7 +11376,7 @@
       <c r="D365">
         <v>39.07</v>
       </c>
-      <c r="E365" s="2">
+      <c r="E365" s="1">
         <v>46021</v>
       </c>
       <c r="F365">
@@ -11450,7 +11402,7 @@
       <c r="D366">
         <v>78.92</v>
       </c>
-      <c r="E366" s="2">
+      <c r="E366" s="1">
         <v>46022</v>
       </c>
       <c r="F366">
@@ -11476,7 +11428,7 @@
       <c r="D367">
         <v>125.85</v>
       </c>
-      <c r="E367" s="2">
+      <c r="E367" s="1">
         <v>46023</v>
       </c>
       <c r="F367">
@@ -11502,14 +11454,14 @@
       <c r="D368">
         <v>89.15000000000001</v>
       </c>
-      <c r="E368" s="2">
+      <c r="E368" s="1">
         <v>46024</v>
       </c>
       <c r="F368">
         <v>4011.75</v>
       </c>
       <c r="G368">
-        <v>36105.75</v>
+        <v>36105.75000000001</v>
       </c>
       <c r="H368">
         <v>7221.150000000001</v>
@@ -11528,7 +11480,7 @@
       <c r="D369">
         <v>79.11</v>
       </c>
-      <c r="E369" s="2">
+      <c r="E369" s="1">
         <v>46025</v>
       </c>
       <c r="F369">
@@ -11554,7 +11506,7 @@
       <c r="D370">
         <v>105.06</v>
       </c>
-      <c r="E370" s="2">
+      <c r="E370" s="1">
         <v>46026</v>
       </c>
       <c r="F370">
@@ -11564,7 +11516,7 @@
         <v>28366.2</v>
       </c>
       <c r="H370">
-        <v>5673.240000000001</v>
+        <v>5673.24</v>
       </c>
     </row>
     <row r="371" spans="1:8">
@@ -11580,7 +11532,7 @@
       <c r="D371">
         <v>121.86</v>
       </c>
-      <c r="E371" s="2">
+      <c r="E371" s="1">
         <v>46027</v>
       </c>
       <c r="F371">
@@ -11606,7 +11558,7 @@
       <c r="D372">
         <v>31.96</v>
       </c>
-      <c r="E372" s="2">
+      <c r="E372" s="1">
         <v>46028</v>
       </c>
       <c r="F372">
@@ -11632,7 +11584,7 @@
       <c r="D373">
         <v>73.34</v>
       </c>
-      <c r="E373" s="2">
+      <c r="E373" s="1">
         <v>46029</v>
       </c>
       <c r="F373">
@@ -11642,7 +11594,7 @@
         <v>174915.9</v>
       </c>
       <c r="H373">
-        <v>34983.18</v>
+        <v>34983.18000000001</v>
       </c>
     </row>
     <row r="374" spans="1:8">
@@ -11658,7 +11610,7 @@
       <c r="D374">
         <v>106.94</v>
       </c>
-      <c r="E374" s="2">
+      <c r="E374" s="1">
         <v>46030</v>
       </c>
       <c r="F374">
@@ -11684,7 +11636,7 @@
       <c r="D375">
         <v>26.35</v>
       </c>
-      <c r="E375" s="2">
+      <c r="E375" s="1">
         <v>46031</v>
       </c>
       <c r="F375">
@@ -11710,7 +11662,7 @@
       <c r="D376">
         <v>124.5</v>
       </c>
-      <c r="E376" s="2">
+      <c r="E376" s="1">
         <v>46032</v>
       </c>
       <c r="F376">
@@ -11736,7 +11688,7 @@
       <c r="D377">
         <v>100.18</v>
       </c>
-      <c r="E377" s="2">
+      <c r="E377" s="1">
         <v>46033</v>
       </c>
       <c r="F377">
@@ -11746,7 +11698,7 @@
         <v>329091.3</v>
       </c>
       <c r="H377">
-        <v>65818.25999999999</v>
+        <v>65818.26000000001</v>
       </c>
     </row>
     <row r="378" spans="1:8">
@@ -11762,7 +11714,7 @@
       <c r="D378">
         <v>13.37</v>
       </c>
-      <c r="E378" s="2">
+      <c r="E378" s="1">
         <v>46034</v>
       </c>
       <c r="F378">
@@ -11788,7 +11740,7 @@
       <c r="D379">
         <v>50.46</v>
       </c>
-      <c r="E379" s="2">
+      <c r="E379" s="1">
         <v>46035</v>
       </c>
       <c r="F379">
@@ -11814,7 +11766,7 @@
       <c r="D380">
         <v>100.25</v>
       </c>
-      <c r="E380" s="2">
+      <c r="E380" s="1">
         <v>46036</v>
       </c>
       <c r="F380">
@@ -11840,7 +11792,7 @@
       <c r="D381">
         <v>101.07</v>
       </c>
-      <c r="E381" s="2">
+      <c r="E381" s="1">
         <v>46037</v>
       </c>
       <c r="F381">
@@ -11866,7 +11818,7 @@
       <c r="D382">
         <v>108.38</v>
       </c>
-      <c r="E382" s="2">
+      <c r="E382" s="1">
         <v>46038</v>
       </c>
       <c r="F382">
@@ -11892,7 +11844,7 @@
       <c r="D383">
         <v>108.66</v>
       </c>
-      <c r="E383" s="2">
+      <c r="E383" s="1">
         <v>46039</v>
       </c>
       <c r="F383">
@@ -11918,7 +11870,7 @@
       <c r="D384">
         <v>40.14</v>
       </c>
-      <c r="E384" s="2">
+      <c r="E384" s="1">
         <v>46040</v>
       </c>
       <c r="F384">
@@ -11944,7 +11896,7 @@
       <c r="D385">
         <v>117.48</v>
       </c>
-      <c r="E385" s="2">
+      <c r="E385" s="1">
         <v>46041</v>
       </c>
       <c r="F385">
@@ -11970,7 +11922,7 @@
       <c r="D386">
         <v>101.2</v>
       </c>
-      <c r="E386" s="2">
+      <c r="E386" s="1">
         <v>46042</v>
       </c>
       <c r="F386">
@@ -11996,7 +11948,7 @@
       <c r="D387">
         <v>149.75</v>
       </c>
-      <c r="E387" s="2">
+      <c r="E387" s="1">
         <v>46043</v>
       </c>
       <c r="F387">
@@ -12022,7 +11974,7 @@
       <c r="D388">
         <v>85.40000000000001</v>
       </c>
-      <c r="E388" s="2">
+      <c r="E388" s="1">
         <v>46044</v>
       </c>
       <c r="F388">
@@ -12032,7 +11984,7 @@
         <v>11529</v>
       </c>
       <c r="H388">
-        <v>2305.8</v>
+        <v>2305.800000000001</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -12048,7 +12000,7 @@
       <c r="D389">
         <v>62.04</v>
       </c>
-      <c r="E389" s="2">
+      <c r="E389" s="1">
         <v>46045</v>
       </c>
       <c r="F389">
@@ -12074,7 +12026,7 @@
       <c r="D390">
         <v>143.34</v>
       </c>
-      <c r="E390" s="2">
+      <c r="E390" s="1">
         <v>46046</v>
       </c>
       <c r="F390">
@@ -12084,7 +12036,7 @@
         <v>199959.3</v>
       </c>
       <c r="H390">
-        <v>39991.86</v>
+        <v>39991.86000000001</v>
       </c>
     </row>
     <row r="391" spans="1:8">
@@ -12100,7 +12052,7 @@
       <c r="D391">
         <v>23.3</v>
       </c>
-      <c r="E391" s="2">
+      <c r="E391" s="1">
         <v>46047</v>
       </c>
       <c r="F391">
@@ -12126,7 +12078,7 @@
       <c r="D392">
         <v>51.95</v>
       </c>
-      <c r="E392" s="2">
+      <c r="E392" s="1">
         <v>46048</v>
       </c>
       <c r="F392">
@@ -12152,7 +12104,7 @@
       <c r="D393">
         <v>11.75</v>
       </c>
-      <c r="E393" s="2">
+      <c r="E393" s="1">
         <v>46049</v>
       </c>
       <c r="F393">
@@ -12178,7 +12130,7 @@
       <c r="D394">
         <v>48.75</v>
       </c>
-      <c r="E394" s="2">
+      <c r="E394" s="1">
         <v>46050</v>
       </c>
       <c r="F394">
@@ -12204,14 +12156,14 @@
       <c r="D395">
         <v>54.79</v>
       </c>
-      <c r="E395" s="2">
+      <c r="E395" s="1">
         <v>46051</v>
       </c>
       <c r="F395">
         <v>2465.55</v>
       </c>
       <c r="G395">
-        <v>7396.65</v>
+        <v>7396.650000000001</v>
       </c>
       <c r="H395">
         <v>1479.33</v>
@@ -12230,17 +12182,17 @@
       <c r="D396">
         <v>143.55</v>
       </c>
-      <c r="E396" s="2">
+      <c r="E396" s="1">
         <v>46052</v>
       </c>
       <c r="F396">
         <v>6459.750000000001</v>
       </c>
       <c r="G396">
-        <v>432803.25</v>
+        <v>432803.2500000001</v>
       </c>
       <c r="H396">
-        <v>86560.65000000001</v>
+        <v>86560.65000000002</v>
       </c>
     </row>
     <row r="397" spans="1:8">
@@ -12256,7 +12208,7 @@
       <c r="D397">
         <v>65.54000000000001</v>
       </c>
-      <c r="E397" s="2">
+      <c r="E397" s="1">
         <v>46053</v>
       </c>
       <c r="F397">
@@ -12282,14 +12234,14 @@
       <c r="D398">
         <v>23.66</v>
       </c>
-      <c r="E398" s="2">
+      <c r="E398" s="1">
         <v>46054</v>
       </c>
       <c r="F398">
         <v>1064.7</v>
       </c>
       <c r="G398">
-        <v>51105.6</v>
+        <v>51105.60000000001</v>
       </c>
       <c r="H398">
         <v>10221.12</v>
@@ -12308,7 +12260,7 @@
       <c r="D399">
         <v>88.39</v>
       </c>
-      <c r="E399" s="2">
+      <c r="E399" s="1">
         <v>46055</v>
       </c>
       <c r="F399">
@@ -12334,14 +12286,14 @@
       <c r="D400">
         <v>35.22</v>
       </c>
-      <c r="E400" s="2">
+      <c r="E400" s="1">
         <v>46056</v>
       </c>
       <c r="F400">
         <v>1584.9</v>
       </c>
       <c r="G400">
-        <v>55471.5</v>
+        <v>55471.49999999999</v>
       </c>
       <c r="H400">
         <v>11094.3</v>
@@ -12360,7 +12312,7 @@
       <c r="D401">
         <v>149.73</v>
       </c>
-      <c r="E401" s="2">
+      <c r="E401" s="1">
         <v>46057</v>
       </c>
       <c r="F401">
@@ -12386,7 +12338,7 @@
       <c r="D402">
         <v>102.84</v>
       </c>
-      <c r="E402" s="2">
+      <c r="E402" s="1">
         <v>46058</v>
       </c>
       <c r="F402">
@@ -12412,7 +12364,7 @@
       <c r="D403">
         <v>41.66</v>
       </c>
-      <c r="E403" s="2">
+      <c r="E403" s="1">
         <v>46059</v>
       </c>
       <c r="F403">
@@ -12438,7 +12390,7 @@
       <c r="D404">
         <v>113.69</v>
       </c>
-      <c r="E404" s="2">
+      <c r="E404" s="1">
         <v>46060</v>
       </c>
       <c r="F404">
@@ -12464,7 +12416,7 @@
       <c r="D405">
         <v>21.7</v>
       </c>
-      <c r="E405" s="2">
+      <c r="E405" s="1">
         <v>46061</v>
       </c>
       <c r="F405">
@@ -12490,7 +12442,7 @@
       <c r="D406">
         <v>45.7</v>
       </c>
-      <c r="E406" s="2">
+      <c r="E406" s="1">
         <v>46062</v>
       </c>
       <c r="F406">
@@ -12516,7 +12468,7 @@
       <c r="D407">
         <v>21.59</v>
       </c>
-      <c r="E407" s="2">
+      <c r="E407" s="1">
         <v>46063</v>
       </c>
       <c r="F407">
@@ -12542,7 +12494,7 @@
       <c r="D408">
         <v>99.44</v>
       </c>
-      <c r="E408" s="2">
+      <c r="E408" s="1">
         <v>46064</v>
       </c>
       <c r="F408">
@@ -12568,7 +12520,7 @@
       <c r="D409">
         <v>105.36</v>
       </c>
-      <c r="E409" s="2">
+      <c r="E409" s="1">
         <v>46065</v>
       </c>
       <c r="F409">
@@ -12578,7 +12530,7 @@
         <v>42670.8</v>
       </c>
       <c r="H409">
-        <v>8534.160000000002</v>
+        <v>8534.16</v>
       </c>
     </row>
     <row r="410" spans="1:8">
@@ -12594,7 +12546,7 @@
       <c r="D410">
         <v>65.29000000000001</v>
       </c>
-      <c r="E410" s="2">
+      <c r="E410" s="1">
         <v>46066</v>
       </c>
       <c r="F410">
@@ -12620,7 +12572,7 @@
       <c r="D411">
         <v>120.39</v>
       </c>
-      <c r="E411" s="2">
+      <c r="E411" s="1">
         <v>46067</v>
       </c>
       <c r="F411">
@@ -12646,7 +12598,7 @@
       <c r="D412">
         <v>98.45999999999999</v>
       </c>
-      <c r="E412" s="2">
+      <c r="E412" s="1">
         <v>46068</v>
       </c>
       <c r="F412">
@@ -12672,7 +12624,7 @@
       <c r="D413">
         <v>25.58</v>
       </c>
-      <c r="E413" s="2">
+      <c r="E413" s="1">
         <v>46069</v>
       </c>
       <c r="F413">
@@ -12698,7 +12650,7 @@
       <c r="D414">
         <v>149.88</v>
       </c>
-      <c r="E414" s="2">
+      <c r="E414" s="1">
         <v>46070</v>
       </c>
       <c r="F414">
@@ -12724,7 +12676,7 @@
       <c r="D415">
         <v>66.72</v>
       </c>
-      <c r="E415" s="2">
+      <c r="E415" s="1">
         <v>46071</v>
       </c>
       <c r="F415">
@@ -12750,7 +12702,7 @@
       <c r="D416">
         <v>7.19</v>
       </c>
-      <c r="E416" s="2">
+      <c r="E416" s="1">
         <v>46072</v>
       </c>
       <c r="F416">
@@ -12776,7 +12728,7 @@
       <c r="D417">
         <v>72.5</v>
       </c>
-      <c r="E417" s="2">
+      <c r="E417" s="1">
         <v>46073</v>
       </c>
       <c r="F417">
@@ -12802,7 +12754,7 @@
       <c r="D418">
         <v>98.77</v>
       </c>
-      <c r="E418" s="2">
+      <c r="E418" s="1">
         <v>46074</v>
       </c>
       <c r="F418">
@@ -12812,7 +12764,7 @@
         <v>217787.85</v>
       </c>
       <c r="H418">
-        <v>43557.57000000001</v>
+        <v>43557.57</v>
       </c>
     </row>
     <row r="419" spans="1:8">
@@ -12828,7 +12780,7 @@
       <c r="D419">
         <v>40.25</v>
       </c>
-      <c r="E419" s="2">
+      <c r="E419" s="1">
         <v>46075</v>
       </c>
       <c r="F419">
@@ -12854,7 +12806,7 @@
       <c r="D420">
         <v>122.62</v>
       </c>
-      <c r="E420" s="2">
+      <c r="E420" s="1">
         <v>46076</v>
       </c>
       <c r="F420">
@@ -12864,7 +12816,7 @@
         <v>220716</v>
       </c>
       <c r="H420">
-        <v>44143.2</v>
+        <v>44143.20000000001</v>
       </c>
     </row>
     <row r="421" spans="1:8">
@@ -12880,7 +12832,7 @@
       <c r="D421">
         <v>145.25</v>
       </c>
-      <c r="E421" s="2">
+      <c r="E421" s="1">
         <v>46077</v>
       </c>
       <c r="F421">
@@ -12906,7 +12858,7 @@
       <c r="D422">
         <v>99.52</v>
       </c>
-      <c r="E422" s="2">
+      <c r="E422" s="1">
         <v>46078</v>
       </c>
       <c r="F422">
@@ -12932,7 +12884,7 @@
       <c r="D423">
         <v>102.39</v>
       </c>
-      <c r="E423" s="2">
+      <c r="E423" s="1">
         <v>46079</v>
       </c>
       <c r="F423">
@@ -12958,7 +12910,7 @@
       <c r="D424">
         <v>23.59</v>
       </c>
-      <c r="E424" s="2">
+      <c r="E424" s="1">
         <v>46080</v>
       </c>
       <c r="F424">
@@ -12968,7 +12920,7 @@
         <v>30784.95</v>
       </c>
       <c r="H424">
-        <v>6156.990000000001</v>
+        <v>6156.99</v>
       </c>
     </row>
     <row r="425" spans="1:8">
@@ -12984,14 +12936,14 @@
       <c r="D425">
         <v>37.01</v>
       </c>
-      <c r="E425" s="2">
+      <c r="E425" s="1">
         <v>46081</v>
       </c>
       <c r="F425">
         <v>1665.45</v>
       </c>
       <c r="G425">
-        <v>6661.8</v>
+        <v>6661.799999999999</v>
       </c>
       <c r="H425">
         <v>1332.36</v>
@@ -13010,7 +12962,7 @@
       <c r="D426">
         <v>15.56</v>
       </c>
-      <c r="E426" s="2">
+      <c r="E426" s="1">
         <v>46082</v>
       </c>
       <c r="F426">
@@ -13020,7 +12972,7 @@
         <v>19605.6</v>
       </c>
       <c r="H426">
-        <v>3921.12</v>
+        <v>3921.120000000001</v>
       </c>
     </row>
     <row r="427" spans="1:8">
@@ -13036,7 +12988,7 @@
       <c r="D427">
         <v>50.06</v>
       </c>
-      <c r="E427" s="2">
+      <c r="E427" s="1">
         <v>46083</v>
       </c>
       <c r="F427">
@@ -13046,7 +12998,7 @@
         <v>110382.3</v>
       </c>
       <c r="H427">
-        <v>22076.46</v>
+        <v>22076.46000000001</v>
       </c>
     </row>
     <row r="428" spans="1:8">
@@ -13062,7 +13014,7 @@
       <c r="D428">
         <v>99.48</v>
       </c>
-      <c r="E428" s="2">
+      <c r="E428" s="1">
         <v>46084</v>
       </c>
       <c r="F428">
@@ -13088,7 +13040,7 @@
       <c r="D429">
         <v>76.47</v>
       </c>
-      <c r="E429" s="2">
+      <c r="E429" s="1">
         <v>46085</v>
       </c>
       <c r="F429">
@@ -13114,7 +13066,7 @@
       <c r="D430">
         <v>30.15</v>
       </c>
-      <c r="E430" s="2">
+      <c r="E430" s="1">
         <v>46086</v>
       </c>
       <c r="F430">
@@ -13140,7 +13092,7 @@
       <c r="D431">
         <v>99.66</v>
       </c>
-      <c r="E431" s="2">
+      <c r="E431" s="1">
         <v>46087</v>
       </c>
       <c r="F431">
@@ -13166,7 +13118,7 @@
       <c r="D432">
         <v>129.58</v>
       </c>
-      <c r="E432" s="2">
+      <c r="E432" s="1">
         <v>46088</v>
       </c>
       <c r="F432">
@@ -13192,7 +13144,7 @@
       <c r="D433">
         <v>92.90000000000001</v>
       </c>
-      <c r="E433" s="2">
+      <c r="E433" s="1">
         <v>46089</v>
       </c>
       <c r="F433">
@@ -13218,7 +13170,7 @@
       <c r="D434">
         <v>148.2</v>
       </c>
-      <c r="E434" s="2">
+      <c r="E434" s="1">
         <v>46090</v>
       </c>
       <c r="F434">
@@ -13244,7 +13196,7 @@
       <c r="D435">
         <v>131.57</v>
       </c>
-      <c r="E435" s="2">
+      <c r="E435" s="1">
         <v>46091</v>
       </c>
       <c r="F435">
@@ -13270,7 +13222,7 @@
       <c r="D436">
         <v>149.56</v>
       </c>
-      <c r="E436" s="2">
+      <c r="E436" s="1">
         <v>46092</v>
       </c>
       <c r="F436">
@@ -13296,7 +13248,7 @@
       <c r="D437">
         <v>114.85</v>
       </c>
-      <c r="E437" s="2">
+      <c r="E437" s="1">
         <v>46093</v>
       </c>
       <c r="F437">
@@ -13322,7 +13274,7 @@
       <c r="D438">
         <v>67.47</v>
       </c>
-      <c r="E438" s="2">
+      <c r="E438" s="1">
         <v>46094</v>
       </c>
       <c r="F438">
@@ -13348,7 +13300,7 @@
       <c r="D439">
         <v>105.54</v>
       </c>
-      <c r="E439" s="2">
+      <c r="E439" s="1">
         <v>46095</v>
       </c>
       <c r="F439">
@@ -13374,7 +13326,7 @@
       <c r="D440">
         <v>41.05</v>
       </c>
-      <c r="E440" s="2">
+      <c r="E440" s="1">
         <v>46096</v>
       </c>
       <c r="F440">
@@ -13400,7 +13352,7 @@
       <c r="D441">
         <v>6.98</v>
       </c>
-      <c r="E441" s="2">
+      <c r="E441" s="1">
         <v>46097</v>
       </c>
       <c r="F441">
@@ -13410,7 +13362,7 @@
         <v>28269</v>
       </c>
       <c r="H441">
-        <v>5653.8</v>
+        <v>5653.800000000001</v>
       </c>
     </row>
     <row r="442" spans="1:8">
@@ -13426,7 +13378,7 @@
       <c r="D442">
         <v>123.17</v>
       </c>
-      <c r="E442" s="2">
+      <c r="E442" s="1">
         <v>46098</v>
       </c>
       <c r="F442">
@@ -13452,7 +13404,7 @@
       <c r="D443">
         <v>16.55</v>
       </c>
-      <c r="E443" s="2">
+      <c r="E443" s="1">
         <v>46099</v>
       </c>
       <c r="F443">
@@ -13478,7 +13430,7 @@
       <c r="D444">
         <v>22.73</v>
       </c>
-      <c r="E444" s="2">
+      <c r="E444" s="1">
         <v>46100</v>
       </c>
       <c r="F444">
@@ -13504,7 +13456,7 @@
       <c r="D445">
         <v>31.22</v>
       </c>
-      <c r="E445" s="2">
+      <c r="E445" s="1">
         <v>46101</v>
       </c>
       <c r="F445">
@@ -13530,7 +13482,7 @@
       <c r="D446">
         <v>12.08</v>
       </c>
-      <c r="E446" s="2">
+      <c r="E446" s="1">
         <v>46102</v>
       </c>
       <c r="F446">
@@ -13556,7 +13508,7 @@
       <c r="D447">
         <v>89.5</v>
       </c>
-      <c r="E447" s="2">
+      <c r="E447" s="1">
         <v>46103</v>
       </c>
       <c r="F447">
@@ -13582,7 +13534,7 @@
       <c r="D448">
         <v>41.88</v>
       </c>
-      <c r="E448" s="2">
+      <c r="E448" s="1">
         <v>46104</v>
       </c>
       <c r="F448">
@@ -13608,7 +13560,7 @@
       <c r="D449">
         <v>112.7</v>
       </c>
-      <c r="E449" s="2">
+      <c r="E449" s="1">
         <v>46105</v>
       </c>
       <c r="F449">
@@ -13634,7 +13586,7 @@
       <c r="D450">
         <v>91.17</v>
       </c>
-      <c r="E450" s="2">
+      <c r="E450" s="1">
         <v>46106</v>
       </c>
       <c r="F450">
@@ -13660,7 +13612,7 @@
       <c r="D451">
         <v>48.48</v>
       </c>
-      <c r="E451" s="2">
+      <c r="E451" s="1">
         <v>46107</v>
       </c>
       <c r="F451">
@@ -13686,7 +13638,7 @@
       <c r="D452">
         <v>30.28</v>
       </c>
-      <c r="E452" s="2">
+      <c r="E452" s="1">
         <v>46108</v>
       </c>
       <c r="F452">
@@ -13712,7 +13664,7 @@
       <c r="D453">
         <v>45.68</v>
       </c>
-      <c r="E453" s="2">
+      <c r="E453" s="1">
         <v>46109</v>
       </c>
       <c r="F453">
@@ -13738,7 +13690,7 @@
       <c r="D454">
         <v>98.56</v>
       </c>
-      <c r="E454" s="2">
+      <c r="E454" s="1">
         <v>46110</v>
       </c>
       <c r="F454">
@@ -13764,7 +13716,7 @@
       <c r="D455">
         <v>84.54000000000001</v>
       </c>
-      <c r="E455" s="2">
+      <c r="E455" s="1">
         <v>46111</v>
       </c>
       <c r="F455">
@@ -13790,7 +13742,7 @@
       <c r="D456">
         <v>138.58</v>
       </c>
-      <c r="E456" s="2">
+      <c r="E456" s="1">
         <v>46112</v>
       </c>
       <c r="F456">
@@ -13816,7 +13768,7 @@
       <c r="D457">
         <v>98.16</v>
       </c>
-      <c r="E457" s="2">
+      <c r="E457" s="1">
         <v>46113</v>
       </c>
       <c r="F457">
@@ -13842,7 +13794,7 @@
       <c r="D458">
         <v>9.02</v>
       </c>
-      <c r="E458" s="2">
+      <c r="E458" s="1">
         <v>46114</v>
       </c>
       <c r="F458">
@@ -13868,17 +13820,17 @@
       <c r="D459">
         <v>129.88</v>
       </c>
-      <c r="E459" s="2">
+      <c r="E459" s="1">
         <v>46115</v>
       </c>
       <c r="F459">
         <v>5844.599999999999</v>
       </c>
       <c r="G459">
-        <v>409122</v>
+        <v>409121.9999999999</v>
       </c>
       <c r="H459">
-        <v>81824.40000000001</v>
+        <v>81824.39999999999</v>
       </c>
     </row>
     <row r="460" spans="1:8">
@@ -13894,7 +13846,7 @@
       <c r="D460">
         <v>96.16</v>
       </c>
-      <c r="E460" s="2">
+      <c r="E460" s="1">
         <v>46116</v>
       </c>
       <c r="F460">
@@ -13920,7 +13872,7 @@
       <c r="D461">
         <v>14.86</v>
       </c>
-      <c r="E461" s="2">
+      <c r="E461" s="1">
         <v>46117</v>
       </c>
       <c r="F461">
@@ -13930,7 +13882,7 @@
         <v>39453.3</v>
       </c>
       <c r="H461">
-        <v>7890.660000000001</v>
+        <v>7890.66</v>
       </c>
     </row>
     <row r="462" spans="1:8">
@@ -13946,7 +13898,7 @@
       <c r="D462">
         <v>67.06999999999999</v>
       </c>
-      <c r="E462" s="2">
+      <c r="E462" s="1">
         <v>46118</v>
       </c>
       <c r="F462">
@@ -13972,7 +13924,7 @@
       <c r="D463">
         <v>55.62</v>
       </c>
-      <c r="E463" s="2">
+      <c r="E463" s="1">
         <v>46119</v>
       </c>
       <c r="F463">
@@ -13998,7 +13950,7 @@
       <c r="D464">
         <v>42.55</v>
       </c>
-      <c r="E464" s="2">
+      <c r="E464" s="1">
         <v>46120</v>
       </c>
       <c r="F464">
@@ -14024,7 +13976,7 @@
       <c r="D465">
         <v>92.25</v>
       </c>
-      <c r="E465" s="2">
+      <c r="E465" s="1">
         <v>46121</v>
       </c>
       <c r="F465">
@@ -14050,7 +14002,7 @@
       <c r="D466">
         <v>122.17</v>
       </c>
-      <c r="E466" s="2">
+      <c r="E466" s="1">
         <v>46122</v>
       </c>
       <c r="F466">
@@ -14076,7 +14028,7 @@
       <c r="D467">
         <v>147.77</v>
       </c>
-      <c r="E467" s="2">
+      <c r="E467" s="1">
         <v>46123</v>
       </c>
       <c r="F467">
@@ -14102,7 +14054,7 @@
       <c r="D468">
         <v>94.06</v>
       </c>
-      <c r="E468" s="2">
+      <c r="E468" s="1">
         <v>46124</v>
       </c>
       <c r="F468">
@@ -14112,7 +14064,7 @@
         <v>325917.9</v>
       </c>
       <c r="H468">
-        <v>65183.58000000001</v>
+        <v>65183.57999999999</v>
       </c>
     </row>
     <row r="469" spans="1:8">
@@ -14128,7 +14080,7 @@
       <c r="D469">
         <v>41.75</v>
       </c>
-      <c r="E469" s="2">
+      <c r="E469" s="1">
         <v>46125</v>
       </c>
       <c r="F469">
@@ -14154,7 +14106,7 @@
       <c r="D470">
         <v>76.06</v>
       </c>
-      <c r="E470" s="2">
+      <c r="E470" s="1">
         <v>46126</v>
       </c>
       <c r="F470">
@@ -14180,7 +14132,7 @@
       <c r="D471">
         <v>95.64</v>
       </c>
-      <c r="E471" s="2">
+      <c r="E471" s="1">
         <v>46127</v>
       </c>
       <c r="F471">
@@ -14190,7 +14142,7 @@
         <v>197974.8</v>
       </c>
       <c r="H471">
-        <v>39594.96</v>
+        <v>39594.96000000001</v>
       </c>
     </row>
     <row r="472" spans="1:8">
@@ -14206,7 +14158,7 @@
       <c r="D472">
         <v>38.31</v>
       </c>
-      <c r="E472" s="2">
+      <c r="E472" s="1">
         <v>46128</v>
       </c>
       <c r="F472">
@@ -14232,7 +14184,7 @@
       <c r="D473">
         <v>86.14</v>
       </c>
-      <c r="E473" s="2">
+      <c r="E473" s="1">
         <v>46129</v>
       </c>
       <c r="F473">
@@ -14258,7 +14210,7 @@
       <c r="D474">
         <v>100.73</v>
       </c>
-      <c r="E474" s="2">
+      <c r="E474" s="1">
         <v>46130</v>
       </c>
       <c r="F474">
@@ -14284,7 +14236,7 @@
       <c r="D475">
         <v>135.47</v>
       </c>
-      <c r="E475" s="2">
+      <c r="E475" s="1">
         <v>46131</v>
       </c>
       <c r="F475">
@@ -14294,7 +14246,7 @@
         <v>353576.7</v>
       </c>
       <c r="H475">
-        <v>70715.34000000001</v>
+        <v>70715.34</v>
       </c>
     </row>
     <row r="476" spans="1:8">
@@ -14310,7 +14262,7 @@
       <c r="D476">
         <v>90.78</v>
       </c>
-      <c r="E476" s="2">
+      <c r="E476" s="1">
         <v>46132</v>
       </c>
       <c r="F476">
@@ -14336,7 +14288,7 @@
       <c r="D477">
         <v>117.42</v>
       </c>
-      <c r="E477" s="2">
+      <c r="E477" s="1">
         <v>46133</v>
       </c>
       <c r="F477">
@@ -14346,7 +14298,7 @@
         <v>359305.2</v>
       </c>
       <c r="H477">
-        <v>71861.04000000001</v>
+        <v>71861.03999999999</v>
       </c>
     </row>
     <row r="478" spans="1:8">
@@ -14362,7 +14314,7 @@
       <c r="D478">
         <v>106.71</v>
       </c>
-      <c r="E478" s="2">
+      <c r="E478" s="1">
         <v>46134</v>
       </c>
       <c r="F478">
@@ -14388,7 +14340,7 @@
       <c r="D479">
         <v>109.21</v>
       </c>
-      <c r="E479" s="2">
+      <c r="E479" s="1">
         <v>46135</v>
       </c>
       <c r="F479">
@@ -14414,7 +14366,7 @@
       <c r="D480">
         <v>16.21</v>
       </c>
-      <c r="E480" s="2">
+      <c r="E480" s="1">
         <v>46136</v>
       </c>
       <c r="F480">
@@ -14440,7 +14392,7 @@
       <c r="D481">
         <v>131.87</v>
       </c>
-      <c r="E481" s="2">
+      <c r="E481" s="1">
         <v>46137</v>
       </c>
       <c r="F481">
@@ -14466,7 +14418,7 @@
       <c r="D482">
         <v>22.22</v>
       </c>
-      <c r="E482" s="2">
+      <c r="E482" s="1">
         <v>46138</v>
       </c>
       <c r="F482">
@@ -14492,7 +14444,7 @@
       <c r="D483">
         <v>93.17</v>
       </c>
-      <c r="E483" s="2">
+      <c r="E483" s="1">
         <v>46139</v>
       </c>
       <c r="F483">
@@ -14518,14 +14470,14 @@
       <c r="D484">
         <v>129.01</v>
       </c>
-      <c r="E484" s="2">
+      <c r="E484" s="1">
         <v>46140</v>
       </c>
       <c r="F484">
         <v>5805.45</v>
       </c>
       <c r="G484">
-        <v>75470.85000000001</v>
+        <v>75470.84999999999</v>
       </c>
       <c r="H484">
         <v>15094.17</v>
@@ -14544,7 +14496,7 @@
       <c r="D485">
         <v>40.63</v>
       </c>
-      <c r="E485" s="2">
+      <c r="E485" s="1">
         <v>46141</v>
       </c>
       <c r="F485">
@@ -14554,7 +14506,7 @@
         <v>181006.65</v>
       </c>
       <c r="H485">
-        <v>36201.33</v>
+        <v>36201.33000000001</v>
       </c>
     </row>
     <row r="486" spans="1:8">
@@ -14570,7 +14522,7 @@
       <c r="D486">
         <v>89.97</v>
       </c>
-      <c r="E486" s="2">
+      <c r="E486" s="1">
         <v>46142</v>
       </c>
       <c r="F486">
@@ -14580,7 +14532,7 @@
         <v>210529.8</v>
       </c>
       <c r="H486">
-        <v>42105.96</v>
+        <v>42105.96000000001</v>
       </c>
     </row>
     <row r="487" spans="1:8">
@@ -14596,7 +14548,7 @@
       <c r="D487">
         <v>14.31</v>
       </c>
-      <c r="E487" s="2">
+      <c r="E487" s="1">
         <v>46143</v>
       </c>
       <c r="F487">
@@ -14622,7 +14574,7 @@
       <c r="D488">
         <v>52.81</v>
       </c>
-      <c r="E488" s="2">
+      <c r="E488" s="1">
         <v>46144</v>
       </c>
       <c r="F488">
@@ -14648,7 +14600,7 @@
       <c r="D489">
         <v>8.02</v>
       </c>
-      <c r="E489" s="2">
+      <c r="E489" s="1">
         <v>46145</v>
       </c>
       <c r="F489">
@@ -14674,7 +14626,7 @@
       <c r="D490">
         <v>142.46</v>
       </c>
-      <c r="E490" s="2">
+      <c r="E490" s="1">
         <v>46146</v>
       </c>
       <c r="F490">
@@ -14684,7 +14636,7 @@
         <v>211553.1</v>
       </c>
       <c r="H490">
-        <v>42310.62</v>
+        <v>42310.62000000001</v>
       </c>
     </row>
     <row r="491" spans="1:8">
@@ -14700,7 +14652,7 @@
       <c r="D491">
         <v>13.95</v>
       </c>
-      <c r="E491" s="2">
+      <c r="E491" s="1">
         <v>46147</v>
       </c>
       <c r="F491">
@@ -14726,7 +14678,7 @@
       <c r="D492">
         <v>122.32</v>
       </c>
-      <c r="E492" s="2">
+      <c r="E492" s="1">
         <v>46148</v>
       </c>
       <c r="F492">
@@ -14752,7 +14704,7 @@
       <c r="D493">
         <v>88.12</v>
       </c>
-      <c r="E493" s="2">
+      <c r="E493" s="1">
         <v>46149</v>
       </c>
       <c r="F493">
@@ -14778,7 +14730,7 @@
       <c r="D494">
         <v>139.15</v>
       </c>
-      <c r="E494" s="2">
+      <c r="E494" s="1">
         <v>46150</v>
       </c>
       <c r="F494">
@@ -14804,14 +14756,14 @@
       <c r="D495">
         <v>31.58</v>
       </c>
-      <c r="E495" s="2">
+      <c r="E495" s="1">
         <v>46151</v>
       </c>
       <c r="F495">
         <v>1421.1</v>
       </c>
       <c r="G495">
-        <v>63949.5</v>
+        <v>63949.49999999999</v>
       </c>
       <c r="H495">
         <v>12789.9</v>
@@ -14830,7 +14782,7 @@
       <c r="D496">
         <v>27.2</v>
       </c>
-      <c r="E496" s="2">
+      <c r="E496" s="1">
         <v>46152</v>
       </c>
       <c r="F496">
@@ -14856,7 +14808,7 @@
       <c r="D497">
         <v>134.14</v>
       </c>
-      <c r="E497" s="2">
+      <c r="E497" s="1">
         <v>46153</v>
       </c>
       <c r="F497">
@@ -14882,7 +14834,7 @@
       <c r="D498">
         <v>58.21</v>
       </c>
-      <c r="E498" s="2">
+      <c r="E498" s="1">
         <v>46154</v>
       </c>
       <c r="F498">
@@ -14908,7 +14860,7 @@
       <c r="D499">
         <v>42.83</v>
       </c>
-      <c r="E499" s="2">
+      <c r="E499" s="1">
         <v>46155</v>
       </c>
       <c r="F499">
@@ -14934,7 +14886,7 @@
       <c r="D500">
         <v>77.16</v>
       </c>
-      <c r="E500" s="2">
+      <c r="E500" s="1">
         <v>46156</v>
       </c>
       <c r="F500">
@@ -14960,7 +14912,7 @@
       <c r="D501">
         <v>78.47</v>
       </c>
-      <c r="E501" s="2">
+      <c r="E501" s="1">
         <v>46157</v>
       </c>
       <c r="F501">
@@ -14971,14 +14923,6 @@
       </c>
       <c r="H501">
         <v>0</v>
-      </c>
-    </row>
-    <row r="502" spans="1:8">
-      <c r="G502" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="H502" s="3">
-        <v>75230500.95</v>
       </c>
     </row>
   </sheetData>
@@ -14990,9 +14934,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="2" width="20.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
@@ -15001,8 +14942,8 @@
       <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>514</v>
+      <c r="D1" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -15013,7 +14954,7 @@
         <v>4578</v>
       </c>
       <c r="D2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="3" spans="1:4">

--- a/Professional_Report.xlsx
+++ b/Professional_Report.xlsx
@@ -7,15 +7,15 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Warehouse" sheetId="1" r:id="rId1"/>
-    <sheet name="Analytics" sheetId="2" r:id="rId2"/>
+    <sheet name="Весь Склад" sheetId="1" r:id="rId1"/>
+    <sheet name="Аналитика" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="516">
   <si>
     <t>Артикул</t>
   </si>
@@ -1556,21 +1556,24 @@
     <t>Платье</t>
   </si>
   <si>
-    <t>Рекомендация AI</t>
-  </si>
-  <si>
-    <t>Анализируя текущие остатки, **Юбка** имеет наименьшее количество (3801).
-**Рекомендация:** Рассмотрите приоритетную закупку **Юбок**, а также проведите сверку всех позиций с планом продаж и минимальными остатками для более точной оценки.</t>
+    <t>ОБЩИЙ ИТОГ:</t>
+  </si>
+  <si>
+    <t>СОВЕТ ОТ GEMINI 3:</t>
+  </si>
+  <si>
+    <t>AI сейчас отдыхает, но данные в порядке! 😴</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00 &quot;₴&quot;"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1578,16 +1581,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7E4BC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1595,13 +1618,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1896,32 +1936,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H501"/>
+  <dimension ref="A1:H502"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="8" width="16.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1938,7 +1986,7 @@
       <c r="D2">
         <v>32.32</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>45658</v>
       </c>
       <c r="F2">
@@ -1964,17 +2012,17 @@
       <c r="D3">
         <v>149.73</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>45659</v>
       </c>
       <c r="F3">
         <v>6737.849999999999</v>
       </c>
       <c r="G3">
-        <v>471649.4999999999</v>
+        <v>471649.5</v>
       </c>
       <c r="H3">
-        <v>94329.89999999999</v>
+        <v>94329.90000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1990,7 +2038,7 @@
       <c r="D4">
         <v>127.09</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>45660</v>
       </c>
       <c r="F4">
@@ -2016,7 +2064,7 @@
       <c r="D5">
         <v>59.14</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>45661</v>
       </c>
       <c r="F5">
@@ -2042,7 +2090,7 @@
       <c r="D6">
         <v>27.71</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="2">
         <v>45662</v>
       </c>
       <c r="F6">
@@ -2068,7 +2116,7 @@
       <c r="D7">
         <v>86.05</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>45663</v>
       </c>
       <c r="F7">
@@ -2094,7 +2142,7 @@
       <c r="D8">
         <v>55.78</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>45664</v>
       </c>
       <c r="F8">
@@ -2120,7 +2168,7 @@
       <c r="D9">
         <v>57.98</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="2">
         <v>45665</v>
       </c>
       <c r="F9">
@@ -2146,7 +2194,7 @@
       <c r="D10">
         <v>92.66</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="2">
         <v>45666</v>
       </c>
       <c r="F10">
@@ -2172,7 +2220,7 @@
       <c r="D11">
         <v>79.91</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="2">
         <v>45667</v>
       </c>
       <c r="F11">
@@ -2198,7 +2246,7 @@
       <c r="D12">
         <v>125.64</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="2">
         <v>45668</v>
       </c>
       <c r="F12">
@@ -2224,7 +2272,7 @@
       <c r="D13">
         <v>7.19</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>45669</v>
       </c>
       <c r="F13">
@@ -2250,7 +2298,7 @@
       <c r="D14">
         <v>96.13</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="2">
         <v>45670</v>
       </c>
       <c r="F14">
@@ -2276,7 +2324,7 @@
       <c r="D15">
         <v>113.11</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="2">
         <v>45671</v>
       </c>
       <c r="F15">
@@ -2302,7 +2350,7 @@
       <c r="D16">
         <v>74.73999999999999</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="2">
         <v>45672</v>
       </c>
       <c r="F16">
@@ -2328,7 +2376,7 @@
       <c r="D17">
         <v>34.61</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="2">
         <v>45673</v>
       </c>
       <c r="F17">
@@ -2354,7 +2402,7 @@
       <c r="D18">
         <v>32.98</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="2">
         <v>45674</v>
       </c>
       <c r="F18">
@@ -2380,7 +2428,7 @@
       <c r="D19">
         <v>106.48</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="2">
         <v>45675</v>
       </c>
       <c r="F19">
@@ -2406,7 +2454,7 @@
       <c r="D20">
         <v>38.7</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="2">
         <v>45676</v>
       </c>
       <c r="F20">
@@ -2432,7 +2480,7 @@
       <c r="D21">
         <v>136.08</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="2">
         <v>45677</v>
       </c>
       <c r="F21">
@@ -2458,7 +2506,7 @@
       <c r="D22">
         <v>120.1</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="2">
         <v>45678</v>
       </c>
       <c r="F22">
@@ -2484,7 +2532,7 @@
       <c r="D23">
         <v>40.06</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="2">
         <v>45679</v>
       </c>
       <c r="F23">
@@ -2510,7 +2558,7 @@
       <c r="D24">
         <v>49.92</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="2">
         <v>45680</v>
       </c>
       <c r="F24">
@@ -2520,7 +2568,7 @@
         <v>31449.6</v>
       </c>
       <c r="H24">
-        <v>6289.920000000001</v>
+        <v>6289.92</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2536,7 +2584,7 @@
       <c r="D25">
         <v>27.6</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="2">
         <v>45681</v>
       </c>
       <c r="F25">
@@ -2562,7 +2610,7 @@
       <c r="D26">
         <v>7.16</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="2">
         <v>45682</v>
       </c>
       <c r="F26">
@@ -2588,7 +2636,7 @@
       <c r="D27">
         <v>96.3</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="2">
         <v>45683</v>
       </c>
       <c r="F27">
@@ -2614,7 +2662,7 @@
       <c r="D28">
         <v>77.65000000000001</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28" s="2">
         <v>45684</v>
       </c>
       <c r="F28">
@@ -2624,7 +2672,7 @@
         <v>223632</v>
       </c>
       <c r="H28">
-        <v>44726.40000000001</v>
+        <v>44726.4</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2640,7 +2688,7 @@
       <c r="D29">
         <v>125.31</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="2">
         <v>45685</v>
       </c>
       <c r="F29">
@@ -2666,7 +2714,7 @@
       <c r="D30">
         <v>76.5</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="2">
         <v>45686</v>
       </c>
       <c r="F30">
@@ -2692,7 +2740,7 @@
       <c r="D31">
         <v>20.2</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="2">
         <v>45687</v>
       </c>
       <c r="F31">
@@ -2718,7 +2766,7 @@
       <c r="D32">
         <v>115.28</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="2">
         <v>45688</v>
       </c>
       <c r="F32">
@@ -2744,7 +2792,7 @@
       <c r="D33">
         <v>127.99</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="2">
         <v>45689</v>
       </c>
       <c r="F33">
@@ -2770,7 +2818,7 @@
       <c r="D34">
         <v>103.03</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="2">
         <v>45690</v>
       </c>
       <c r="F34">
@@ -2796,7 +2844,7 @@
       <c r="D35">
         <v>86.45</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="2">
         <v>45691</v>
       </c>
       <c r="F35">
@@ -2822,7 +2870,7 @@
       <c r="D36">
         <v>88.72</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="2">
         <v>45692</v>
       </c>
       <c r="F36">
@@ -2848,7 +2896,7 @@
       <c r="D37">
         <v>62.13</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37" s="2">
         <v>45693</v>
       </c>
       <c r="F37">
@@ -2874,14 +2922,14 @@
       <c r="D38">
         <v>77.18000000000001</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38" s="2">
         <v>45694</v>
       </c>
       <c r="F38">
         <v>3473.1</v>
       </c>
       <c r="G38">
-        <v>329944.5000000001</v>
+        <v>329944.5</v>
       </c>
       <c r="H38">
         <v>65988.90000000001</v>
@@ -2900,7 +2948,7 @@
       <c r="D39">
         <v>101.59</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="2">
         <v>45695</v>
       </c>
       <c r="F39">
@@ -2926,7 +2974,7 @@
       <c r="D40">
         <v>121.05</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40" s="2">
         <v>45696</v>
       </c>
       <c r="F40">
@@ -2952,7 +3000,7 @@
       <c r="D41">
         <v>22.8</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="2">
         <v>45697</v>
       </c>
       <c r="F41">
@@ -2978,7 +3026,7 @@
       <c r="D42">
         <v>64.28</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="2">
         <v>45698</v>
       </c>
       <c r="F42">
@@ -3004,7 +3052,7 @@
       <c r="D43">
         <v>13.9</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43" s="2">
         <v>45699</v>
       </c>
       <c r="F43">
@@ -3030,7 +3078,7 @@
       <c r="D44">
         <v>130.25</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="2">
         <v>45700</v>
       </c>
       <c r="F44">
@@ -3056,7 +3104,7 @@
       <c r="D45">
         <v>149.54</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45" s="2">
         <v>45701</v>
       </c>
       <c r="F45">
@@ -3082,7 +3130,7 @@
       <c r="D46">
         <v>115.93</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="2">
         <v>45702</v>
       </c>
       <c r="F46">
@@ -3092,7 +3140,7 @@
         <v>485167.05</v>
       </c>
       <c r="H46">
-        <v>97033.41000000002</v>
+        <v>97033.41</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -3108,7 +3156,7 @@
       <c r="D47">
         <v>60.1</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="2">
         <v>45703</v>
       </c>
       <c r="F47">
@@ -3134,7 +3182,7 @@
       <c r="D48">
         <v>131.66</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="2">
         <v>45704</v>
       </c>
       <c r="F48">
@@ -3160,7 +3208,7 @@
       <c r="D49">
         <v>97.65000000000001</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49" s="2">
         <v>45705</v>
       </c>
       <c r="F49">
@@ -3186,7 +3234,7 @@
       <c r="D50">
         <v>142.56</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50" s="2">
         <v>45706</v>
       </c>
       <c r="F50">
@@ -3212,7 +3260,7 @@
       <c r="D51">
         <v>118.46</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E51" s="2">
         <v>45707</v>
       </c>
       <c r="F51">
@@ -3238,7 +3286,7 @@
       <c r="D52">
         <v>84.45999999999999</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E52" s="2">
         <v>45708</v>
       </c>
       <c r="F52">
@@ -3264,7 +3312,7 @@
       <c r="D53">
         <v>21.28</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="2">
         <v>45709</v>
       </c>
       <c r="F53">
@@ -3290,7 +3338,7 @@
       <c r="D54">
         <v>112.69</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E54" s="2">
         <v>45710</v>
       </c>
       <c r="F54">
@@ -3316,7 +3364,7 @@
       <c r="D55">
         <v>47.3</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E55" s="2">
         <v>45711</v>
       </c>
       <c r="F55">
@@ -3342,7 +3390,7 @@
       <c r="D56">
         <v>118.7</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56" s="2">
         <v>45712</v>
       </c>
       <c r="F56">
@@ -3368,7 +3416,7 @@
       <c r="D57">
         <v>60.75</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E57" s="2">
         <v>45713</v>
       </c>
       <c r="F57">
@@ -3394,7 +3442,7 @@
       <c r="D58">
         <v>125.34</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E58" s="2">
         <v>45714</v>
       </c>
       <c r="F58">
@@ -3420,7 +3468,7 @@
       <c r="D59">
         <v>13.42</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59" s="2">
         <v>45715</v>
       </c>
       <c r="F59">
@@ -3446,7 +3494,7 @@
       <c r="D60">
         <v>53.96</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E60" s="2">
         <v>45716</v>
       </c>
       <c r="F60">
@@ -3472,7 +3520,7 @@
       <c r="D61">
         <v>91.37</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E61" s="2">
         <v>45717</v>
       </c>
       <c r="F61">
@@ -3498,7 +3546,7 @@
       <c r="D62">
         <v>14.34</v>
       </c>
-      <c r="E62" s="1">
+      <c r="E62" s="2">
         <v>45718</v>
       </c>
       <c r="F62">
@@ -3524,7 +3572,7 @@
       <c r="D63">
         <v>137.14</v>
       </c>
-      <c r="E63" s="1">
+      <c r="E63" s="2">
         <v>45719</v>
       </c>
       <c r="F63">
@@ -3550,7 +3598,7 @@
       <c r="D64">
         <v>100.77</v>
       </c>
-      <c r="E64" s="1">
+      <c r="E64" s="2">
         <v>45720</v>
       </c>
       <c r="F64">
@@ -3576,7 +3624,7 @@
       <c r="D65">
         <v>16.41</v>
       </c>
-      <c r="E65" s="1">
+      <c r="E65" s="2">
         <v>45721</v>
       </c>
       <c r="F65">
@@ -3586,7 +3634,7 @@
         <v>37660.95</v>
       </c>
       <c r="H65">
-        <v>7532.190000000001</v>
+        <v>7532.19</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -3602,7 +3650,7 @@
       <c r="D66">
         <v>48.35</v>
       </c>
-      <c r="E66" s="1">
+      <c r="E66" s="2">
         <v>45722</v>
       </c>
       <c r="F66">
@@ -3628,7 +3676,7 @@
       <c r="D67">
         <v>145.23</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E67" s="2">
         <v>45723</v>
       </c>
       <c r="F67">
@@ -3638,7 +3686,7 @@
         <v>209131.2</v>
       </c>
       <c r="H67">
-        <v>41826.24</v>
+        <v>41826.24000000001</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -3654,7 +3702,7 @@
       <c r="D68">
         <v>5.78</v>
       </c>
-      <c r="E68" s="1">
+      <c r="E68" s="2">
         <v>45724</v>
       </c>
       <c r="F68">
@@ -3680,7 +3728,7 @@
       <c r="D69">
         <v>87.38</v>
       </c>
-      <c r="E69" s="1">
+      <c r="E69" s="2">
         <v>45725</v>
       </c>
       <c r="F69">
@@ -3706,7 +3754,7 @@
       <c r="D70">
         <v>144.18</v>
       </c>
-      <c r="E70" s="1">
+      <c r="E70" s="2">
         <v>45726</v>
       </c>
       <c r="F70">
@@ -3732,7 +3780,7 @@
       <c r="D71">
         <v>111.26</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E71" s="2">
         <v>45727</v>
       </c>
       <c r="F71">
@@ -3758,7 +3806,7 @@
       <c r="D72">
         <v>21.22</v>
       </c>
-      <c r="E72" s="1">
+      <c r="E72" s="2">
         <v>45728</v>
       </c>
       <c r="F72">
@@ -3784,7 +3832,7 @@
       <c r="D73">
         <v>37.02</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E73" s="2">
         <v>45729</v>
       </c>
       <c r="F73">
@@ -3794,7 +3842,7 @@
         <v>46645.2</v>
       </c>
       <c r="H73">
-        <v>9329.040000000001</v>
+        <v>9329.039999999999</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -3810,7 +3858,7 @@
       <c r="D74">
         <v>122.36</v>
       </c>
-      <c r="E74" s="1">
+      <c r="E74" s="2">
         <v>45730</v>
       </c>
       <c r="F74">
@@ -3836,7 +3884,7 @@
       <c r="D75">
         <v>132.18</v>
       </c>
-      <c r="E75" s="1">
+      <c r="E75" s="2">
         <v>45731</v>
       </c>
       <c r="F75">
@@ -3862,7 +3910,7 @@
       <c r="D76">
         <v>120.18</v>
       </c>
-      <c r="E76" s="1">
+      <c r="E76" s="2">
         <v>45732</v>
       </c>
       <c r="F76">
@@ -3888,7 +3936,7 @@
       <c r="D77">
         <v>16.33</v>
       </c>
-      <c r="E77" s="1">
+      <c r="E77" s="2">
         <v>45733</v>
       </c>
       <c r="F77">
@@ -3914,7 +3962,7 @@
       <c r="D78">
         <v>62.08</v>
       </c>
-      <c r="E78" s="1">
+      <c r="E78" s="2">
         <v>45734</v>
       </c>
       <c r="F78">
@@ -3940,7 +3988,7 @@
       <c r="D79">
         <v>40.37</v>
       </c>
-      <c r="E79" s="1">
+      <c r="E79" s="2">
         <v>45735</v>
       </c>
       <c r="F79">
@@ -3966,7 +4014,7 @@
       <c r="D80">
         <v>33.12</v>
       </c>
-      <c r="E80" s="1">
+      <c r="E80" s="2">
         <v>45736</v>
       </c>
       <c r="F80">
@@ -3992,7 +4040,7 @@
       <c r="D81">
         <v>91.70999999999999</v>
       </c>
-      <c r="E81" s="1">
+      <c r="E81" s="2">
         <v>45737</v>
       </c>
       <c r="F81">
@@ -4018,7 +4066,7 @@
       <c r="D82">
         <v>145.25</v>
       </c>
-      <c r="E82" s="1">
+      <c r="E82" s="2">
         <v>45738</v>
       </c>
       <c r="F82">
@@ -4044,17 +4092,17 @@
       <c r="D83">
         <v>27.83</v>
       </c>
-      <c r="E83" s="1">
+      <c r="E83" s="2">
         <v>45739</v>
       </c>
       <c r="F83">
         <v>1252.35</v>
       </c>
       <c r="G83">
-        <v>42579.89999999999</v>
+        <v>42579.9</v>
       </c>
       <c r="H83">
-        <v>8515.98</v>
+        <v>8515.980000000001</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -4070,7 +4118,7 @@
       <c r="D84">
         <v>88.89</v>
       </c>
-      <c r="E84" s="1">
+      <c r="E84" s="2">
         <v>45740</v>
       </c>
       <c r="F84">
@@ -4096,7 +4144,7 @@
       <c r="D85">
         <v>64.8</v>
       </c>
-      <c r="E85" s="1">
+      <c r="E85" s="2">
         <v>45741</v>
       </c>
       <c r="F85">
@@ -4122,7 +4170,7 @@
       <c r="D86">
         <v>73.88</v>
       </c>
-      <c r="E86" s="1">
+      <c r="E86" s="2">
         <v>45742</v>
       </c>
       <c r="F86">
@@ -4148,7 +4196,7 @@
       <c r="D87">
         <v>64.66</v>
       </c>
-      <c r="E87" s="1">
+      <c r="E87" s="2">
         <v>45743</v>
       </c>
       <c r="F87">
@@ -4174,7 +4222,7 @@
       <c r="D88">
         <v>45.23</v>
       </c>
-      <c r="E88" s="1">
+      <c r="E88" s="2">
         <v>45744</v>
       </c>
       <c r="F88">
@@ -4200,7 +4248,7 @@
       <c r="D89">
         <v>136.53</v>
       </c>
-      <c r="E89" s="1">
+      <c r="E89" s="2">
         <v>45745</v>
       </c>
       <c r="F89">
@@ -4210,7 +4258,7 @@
         <v>313336.35</v>
       </c>
       <c r="H89">
-        <v>62667.27000000001</v>
+        <v>62667.27</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -4226,7 +4274,7 @@
       <c r="D90">
         <v>73.45999999999999</v>
       </c>
-      <c r="E90" s="1">
+      <c r="E90" s="2">
         <v>45746</v>
       </c>
       <c r="F90">
@@ -4252,7 +4300,7 @@
       <c r="D91">
         <v>91.5</v>
       </c>
-      <c r="E91" s="1">
+      <c r="E91" s="2">
         <v>45747</v>
       </c>
       <c r="F91">
@@ -4278,7 +4326,7 @@
       <c r="D92">
         <v>63.76</v>
       </c>
-      <c r="E92" s="1">
+      <c r="E92" s="2">
         <v>45748</v>
       </c>
       <c r="F92">
@@ -4304,7 +4352,7 @@
       <c r="D93">
         <v>125.94</v>
       </c>
-      <c r="E93" s="1">
+      <c r="E93" s="2">
         <v>45749</v>
       </c>
       <c r="F93">
@@ -4330,7 +4378,7 @@
       <c r="D94">
         <v>52.65</v>
       </c>
-      <c r="E94" s="1">
+      <c r="E94" s="2">
         <v>45750</v>
       </c>
       <c r="F94">
@@ -4356,7 +4404,7 @@
       <c r="D95">
         <v>112.3</v>
       </c>
-      <c r="E95" s="1">
+      <c r="E95" s="2">
         <v>45751</v>
       </c>
       <c r="F95">
@@ -4382,7 +4430,7 @@
       <c r="D96">
         <v>128.85</v>
       </c>
-      <c r="E96" s="1">
+      <c r="E96" s="2">
         <v>45752</v>
       </c>
       <c r="F96">
@@ -4408,7 +4456,7 @@
       <c r="D97">
         <v>92.63</v>
       </c>
-      <c r="E97" s="1">
+      <c r="E97" s="2">
         <v>45753</v>
       </c>
       <c r="F97">
@@ -4434,7 +4482,7 @@
       <c r="D98">
         <v>123.1</v>
       </c>
-      <c r="E98" s="1">
+      <c r="E98" s="2">
         <v>45754</v>
       </c>
       <c r="F98">
@@ -4460,7 +4508,7 @@
       <c r="D99">
         <v>36.15</v>
       </c>
-      <c r="E99" s="1">
+      <c r="E99" s="2">
         <v>45755</v>
       </c>
       <c r="F99">
@@ -4486,7 +4534,7 @@
       <c r="D100">
         <v>24.99</v>
       </c>
-      <c r="E100" s="1">
+      <c r="E100" s="2">
         <v>45756</v>
       </c>
       <c r="F100">
@@ -4512,7 +4560,7 @@
       <c r="D101">
         <v>53.9</v>
       </c>
-      <c r="E101" s="1">
+      <c r="E101" s="2">
         <v>45757</v>
       </c>
       <c r="F101">
@@ -4538,7 +4586,7 @@
       <c r="D102">
         <v>13.18</v>
       </c>
-      <c r="E102" s="1">
+      <c r="E102" s="2">
         <v>45758</v>
       </c>
       <c r="F102">
@@ -4564,7 +4612,7 @@
       <c r="D103">
         <v>40.17</v>
       </c>
-      <c r="E103" s="1">
+      <c r="E103" s="2">
         <v>45759</v>
       </c>
       <c r="F103">
@@ -4574,7 +4622,7 @@
         <v>21691.8</v>
       </c>
       <c r="H103">
-        <v>4338.360000000001</v>
+        <v>4338.36</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -4590,7 +4638,7 @@
       <c r="D104">
         <v>80.94</v>
       </c>
-      <c r="E104" s="1">
+      <c r="E104" s="2">
         <v>45760</v>
       </c>
       <c r="F104">
@@ -4616,7 +4664,7 @@
       <c r="D105">
         <v>105.2</v>
       </c>
-      <c r="E105" s="1">
+      <c r="E105" s="2">
         <v>45761</v>
       </c>
       <c r="F105">
@@ -4642,7 +4690,7 @@
       <c r="D106">
         <v>40.74</v>
       </c>
-      <c r="E106" s="1">
+      <c r="E106" s="2">
         <v>45762</v>
       </c>
       <c r="F106">
@@ -4668,7 +4716,7 @@
       <c r="D107">
         <v>118.81</v>
       </c>
-      <c r="E107" s="1">
+      <c r="E107" s="2">
         <v>45763</v>
       </c>
       <c r="F107">
@@ -4678,7 +4726,7 @@
         <v>278015.4</v>
       </c>
       <c r="H107">
-        <v>55603.07999999999</v>
+        <v>55603.08000000001</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -4694,7 +4742,7 @@
       <c r="D108">
         <v>95.27</v>
       </c>
-      <c r="E108" s="1">
+      <c r="E108" s="2">
         <v>45764</v>
       </c>
       <c r="F108">
@@ -4720,7 +4768,7 @@
       <c r="D109">
         <v>87.56</v>
       </c>
-      <c r="E109" s="1">
+      <c r="E109" s="2">
         <v>45765</v>
       </c>
       <c r="F109">
@@ -4746,7 +4794,7 @@
       <c r="D110">
         <v>69.87</v>
       </c>
-      <c r="E110" s="1">
+      <c r="E110" s="2">
         <v>45766</v>
       </c>
       <c r="F110">
@@ -4772,7 +4820,7 @@
       <c r="D111">
         <v>93.78</v>
       </c>
-      <c r="E111" s="1">
+      <c r="E111" s="2">
         <v>45767</v>
       </c>
       <c r="F111">
@@ -4798,7 +4846,7 @@
       <c r="D112">
         <v>39.01</v>
       </c>
-      <c r="E112" s="1">
+      <c r="E112" s="2">
         <v>45768</v>
       </c>
       <c r="F112">
@@ -4824,7 +4872,7 @@
       <c r="D113">
         <v>107.45</v>
       </c>
-      <c r="E113" s="1">
+      <c r="E113" s="2">
         <v>45769</v>
       </c>
       <c r="F113">
@@ -4850,7 +4898,7 @@
       <c r="D114">
         <v>62.41</v>
       </c>
-      <c r="E114" s="1">
+      <c r="E114" s="2">
         <v>45770</v>
       </c>
       <c r="F114">
@@ -4876,7 +4924,7 @@
       <c r="D115">
         <v>85.19</v>
       </c>
-      <c r="E115" s="1">
+      <c r="E115" s="2">
         <v>45771</v>
       </c>
       <c r="F115">
@@ -4902,7 +4950,7 @@
       <c r="D116">
         <v>104.52</v>
       </c>
-      <c r="E116" s="1">
+      <c r="E116" s="2">
         <v>45772</v>
       </c>
       <c r="F116">
@@ -4928,7 +4976,7 @@
       <c r="D117">
         <v>45.93</v>
       </c>
-      <c r="E117" s="1">
+      <c r="E117" s="2">
         <v>45773</v>
       </c>
       <c r="F117">
@@ -4954,7 +5002,7 @@
       <c r="D118">
         <v>131.84</v>
       </c>
-      <c r="E118" s="1">
+      <c r="E118" s="2">
         <v>45774</v>
       </c>
       <c r="F118">
@@ -4980,7 +5028,7 @@
       <c r="D119">
         <v>136.94</v>
       </c>
-      <c r="E119" s="1">
+      <c r="E119" s="2">
         <v>45775</v>
       </c>
       <c r="F119">
@@ -5006,7 +5054,7 @@
       <c r="D120">
         <v>92.28</v>
       </c>
-      <c r="E120" s="1">
+      <c r="E120" s="2">
         <v>45776</v>
       </c>
       <c r="F120">
@@ -5032,7 +5080,7 @@
       <c r="D121">
         <v>13.11</v>
       </c>
-      <c r="E121" s="1">
+      <c r="E121" s="2">
         <v>45777</v>
       </c>
       <c r="F121">
@@ -5042,7 +5090,7 @@
         <v>24187.95</v>
       </c>
       <c r="H121">
-        <v>4837.589999999999</v>
+        <v>4837.59</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -5058,7 +5106,7 @@
       <c r="D122">
         <v>88.02</v>
       </c>
-      <c r="E122" s="1">
+      <c r="E122" s="2">
         <v>45778</v>
       </c>
       <c r="F122">
@@ -5084,7 +5132,7 @@
       <c r="D123">
         <v>137.36</v>
       </c>
-      <c r="E123" s="1">
+      <c r="E123" s="2">
         <v>45779</v>
       </c>
       <c r="F123">
@@ -5094,7 +5142,7 @@
         <v>302878.8</v>
       </c>
       <c r="H123">
-        <v>60575.76000000001</v>
+        <v>60575.76</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -5110,7 +5158,7 @@
       <c r="D124">
         <v>21.7</v>
       </c>
-      <c r="E124" s="1">
+      <c r="E124" s="2">
         <v>45780</v>
       </c>
       <c r="F124">
@@ -5136,7 +5184,7 @@
       <c r="D125">
         <v>103.09</v>
       </c>
-      <c r="E125" s="1">
+      <c r="E125" s="2">
         <v>45781</v>
       </c>
       <c r="F125">
@@ -5162,17 +5210,17 @@
       <c r="D126">
         <v>77.65000000000001</v>
       </c>
-      <c r="E126" s="1">
+      <c r="E126" s="2">
         <v>45782</v>
       </c>
       <c r="F126">
         <v>3494.25</v>
       </c>
       <c r="G126">
-        <v>83862.00000000001</v>
+        <v>83862</v>
       </c>
       <c r="H126">
-        <v>16772.40000000001</v>
+        <v>16772.4</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -5188,14 +5236,14 @@
       <c r="D127">
         <v>35.2</v>
       </c>
-      <c r="E127" s="1">
+      <c r="E127" s="2">
         <v>45783</v>
       </c>
       <c r="F127">
         <v>1584</v>
       </c>
       <c r="G127">
-        <v>64944.00000000001</v>
+        <v>64944</v>
       </c>
       <c r="H127">
         <v>12988.8</v>
@@ -5214,7 +5262,7 @@
       <c r="D128">
         <v>11.97</v>
       </c>
-      <c r="E128" s="1">
+      <c r="E128" s="2">
         <v>45784</v>
       </c>
       <c r="F128">
@@ -5240,7 +5288,7 @@
       <c r="D129">
         <v>94.09</v>
       </c>
-      <c r="E129" s="1">
+      <c r="E129" s="2">
         <v>45785</v>
       </c>
       <c r="F129">
@@ -5266,7 +5314,7 @@
       <c r="D130">
         <v>48.18</v>
       </c>
-      <c r="E130" s="1">
+      <c r="E130" s="2">
         <v>45786</v>
       </c>
       <c r="F130">
@@ -5292,7 +5340,7 @@
       <c r="D131">
         <v>116.4</v>
       </c>
-      <c r="E131" s="1">
+      <c r="E131" s="2">
         <v>45787</v>
       </c>
       <c r="F131">
@@ -5318,7 +5366,7 @@
       <c r="D132">
         <v>28.73</v>
       </c>
-      <c r="E132" s="1">
+      <c r="E132" s="2">
         <v>45788</v>
       </c>
       <c r="F132">
@@ -5344,7 +5392,7 @@
       <c r="D133">
         <v>131.79</v>
       </c>
-      <c r="E133" s="1">
+      <c r="E133" s="2">
         <v>45789</v>
       </c>
       <c r="F133">
@@ -5370,7 +5418,7 @@
       <c r="D134">
         <v>47.63</v>
       </c>
-      <c r="E134" s="1">
+      <c r="E134" s="2">
         <v>45790</v>
       </c>
       <c r="F134">
@@ -5396,7 +5444,7 @@
       <c r="D135">
         <v>133.25</v>
       </c>
-      <c r="E135" s="1">
+      <c r="E135" s="2">
         <v>45791</v>
       </c>
       <c r="F135">
@@ -5422,7 +5470,7 @@
       <c r="D136">
         <v>85.52</v>
       </c>
-      <c r="E136" s="1">
+      <c r="E136" s="2">
         <v>45792</v>
       </c>
       <c r="F136">
@@ -5448,7 +5496,7 @@
       <c r="D137">
         <v>102.45</v>
       </c>
-      <c r="E137" s="1">
+      <c r="E137" s="2">
         <v>45793</v>
       </c>
       <c r="F137">
@@ -5474,7 +5522,7 @@
       <c r="D138">
         <v>67.69</v>
       </c>
-      <c r="E138" s="1">
+      <c r="E138" s="2">
         <v>45794</v>
       </c>
       <c r="F138">
@@ -5500,7 +5548,7 @@
       <c r="D139">
         <v>107.01</v>
       </c>
-      <c r="E139" s="1">
+      <c r="E139" s="2">
         <v>45795</v>
       </c>
       <c r="F139">
@@ -5526,7 +5574,7 @@
       <c r="D140">
         <v>16.41</v>
       </c>
-      <c r="E140" s="1">
+      <c r="E140" s="2">
         <v>45796</v>
       </c>
       <c r="F140">
@@ -5552,7 +5600,7 @@
       <c r="D141">
         <v>17.27</v>
       </c>
-      <c r="E141" s="1">
+      <c r="E141" s="2">
         <v>45797</v>
       </c>
       <c r="F141">
@@ -5578,7 +5626,7 @@
       <c r="D142">
         <v>103.05</v>
       </c>
-      <c r="E142" s="1">
+      <c r="E142" s="2">
         <v>45798</v>
       </c>
       <c r="F142">
@@ -5604,7 +5652,7 @@
       <c r="D143">
         <v>6.39</v>
       </c>
-      <c r="E143" s="1">
+      <c r="E143" s="2">
         <v>45799</v>
       </c>
       <c r="F143">
@@ -5630,7 +5678,7 @@
       <c r="D144">
         <v>50.57</v>
       </c>
-      <c r="E144" s="1">
+      <c r="E144" s="2">
         <v>45800</v>
       </c>
       <c r="F144">
@@ -5656,7 +5704,7 @@
       <c r="D145">
         <v>117.22</v>
       </c>
-      <c r="E145" s="1">
+      <c r="E145" s="2">
         <v>45801</v>
       </c>
       <c r="F145">
@@ -5682,7 +5730,7 @@
       <c r="D146">
         <v>149.35</v>
       </c>
-      <c r="E146" s="1">
+      <c r="E146" s="2">
         <v>45802</v>
       </c>
       <c r="F146">
@@ -5708,7 +5756,7 @@
       <c r="D147">
         <v>104.14</v>
       </c>
-      <c r="E147" s="1">
+      <c r="E147" s="2">
         <v>45803</v>
       </c>
       <c r="F147">
@@ -5734,7 +5782,7 @@
       <c r="D148">
         <v>87.65000000000001</v>
       </c>
-      <c r="E148" s="1">
+      <c r="E148" s="2">
         <v>45804</v>
       </c>
       <c r="F148">
@@ -5744,7 +5792,7 @@
         <v>114383.25</v>
       </c>
       <c r="H148">
-        <v>22876.65000000001</v>
+        <v>22876.65</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -5760,7 +5808,7 @@
       <c r="D149">
         <v>45.32</v>
       </c>
-      <c r="E149" s="1">
+      <c r="E149" s="2">
         <v>45805</v>
       </c>
       <c r="F149">
@@ -5786,7 +5834,7 @@
       <c r="D150">
         <v>92.05</v>
       </c>
-      <c r="E150" s="1">
+      <c r="E150" s="2">
         <v>45806</v>
       </c>
       <c r="F150">
@@ -5812,7 +5860,7 @@
       <c r="D151">
         <v>148.34</v>
       </c>
-      <c r="E151" s="1">
+      <c r="E151" s="2">
         <v>45807</v>
       </c>
       <c r="F151">
@@ -5838,7 +5886,7 @@
       <c r="D152">
         <v>122.03</v>
       </c>
-      <c r="E152" s="1">
+      <c r="E152" s="2">
         <v>45808</v>
       </c>
       <c r="F152">
@@ -5864,7 +5912,7 @@
       <c r="D153">
         <v>5.59</v>
       </c>
-      <c r="E153" s="1">
+      <c r="E153" s="2">
         <v>45809</v>
       </c>
       <c r="F153">
@@ -5874,7 +5922,7 @@
         <v>12325.95</v>
       </c>
       <c r="H153">
-        <v>2465.19</v>
+        <v>2465.190000000001</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -5890,7 +5938,7 @@
       <c r="D154">
         <v>111.48</v>
       </c>
-      <c r="E154" s="1">
+      <c r="E154" s="2">
         <v>45810</v>
       </c>
       <c r="F154">
@@ -5900,7 +5948,7 @@
         <v>381261.6</v>
       </c>
       <c r="H154">
-        <v>76252.32000000001</v>
+        <v>76252.31999999999</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -5916,7 +5964,7 @@
       <c r="D155">
         <v>121.62</v>
       </c>
-      <c r="E155" s="1">
+      <c r="E155" s="2">
         <v>45811</v>
       </c>
       <c r="F155">
@@ -5942,7 +5990,7 @@
       <c r="D156">
         <v>80.2</v>
       </c>
-      <c r="E156" s="1">
+      <c r="E156" s="2">
         <v>45812</v>
       </c>
       <c r="F156">
@@ -5968,7 +6016,7 @@
       <c r="D157">
         <v>20.83</v>
       </c>
-      <c r="E157" s="1">
+      <c r="E157" s="2">
         <v>45813</v>
       </c>
       <c r="F157">
@@ -5978,7 +6026,7 @@
         <v>30932.55</v>
       </c>
       <c r="H157">
-        <v>6186.509999999999</v>
+        <v>6186.51</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -5994,7 +6042,7 @@
       <c r="D158">
         <v>129.4</v>
       </c>
-      <c r="E158" s="1">
+      <c r="E158" s="2">
         <v>45814</v>
       </c>
       <c r="F158">
@@ -6020,7 +6068,7 @@
       <c r="D159">
         <v>108.7</v>
       </c>
-      <c r="E159" s="1">
+      <c r="E159" s="2">
         <v>45815</v>
       </c>
       <c r="F159">
@@ -6046,7 +6094,7 @@
       <c r="D160">
         <v>114.18</v>
       </c>
-      <c r="E160" s="1">
+      <c r="E160" s="2">
         <v>45816</v>
       </c>
       <c r="F160">
@@ -6056,7 +6104,7 @@
         <v>493257.6</v>
       </c>
       <c r="H160">
-        <v>98651.52000000002</v>
+        <v>98651.52</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -6072,7 +6120,7 @@
       <c r="D161">
         <v>25.26</v>
       </c>
-      <c r="E161" s="1">
+      <c r="E161" s="2">
         <v>45817</v>
       </c>
       <c r="F161">
@@ -6098,7 +6146,7 @@
       <c r="D162">
         <v>130.06</v>
       </c>
-      <c r="E162" s="1">
+      <c r="E162" s="2">
         <v>45818</v>
       </c>
       <c r="F162">
@@ -6124,7 +6172,7 @@
       <c r="D163">
         <v>18.57</v>
       </c>
-      <c r="E163" s="1">
+      <c r="E163" s="2">
         <v>45819</v>
       </c>
       <c r="F163">
@@ -6150,7 +6198,7 @@
       <c r="D164">
         <v>144.33</v>
       </c>
-      <c r="E164" s="1">
+      <c r="E164" s="2">
         <v>45820</v>
       </c>
       <c r="F164">
@@ -6160,7 +6208,7 @@
         <v>409175.55</v>
       </c>
       <c r="H164">
-        <v>81835.11000000002</v>
+        <v>81835.11</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -6176,7 +6224,7 @@
       <c r="D165">
         <v>99.65000000000001</v>
       </c>
-      <c r="E165" s="1">
+      <c r="E165" s="2">
         <v>45821</v>
       </c>
       <c r="F165">
@@ -6202,7 +6250,7 @@
       <c r="D166">
         <v>71.63</v>
       </c>
-      <c r="E166" s="1">
+      <c r="E166" s="2">
         <v>45822</v>
       </c>
       <c r="F166">
@@ -6228,7 +6276,7 @@
       <c r="D167">
         <v>32.67</v>
       </c>
-      <c r="E167" s="1">
+      <c r="E167" s="2">
         <v>45823</v>
       </c>
       <c r="F167">
@@ -6254,7 +6302,7 @@
       <c r="D168">
         <v>13.52</v>
       </c>
-      <c r="E168" s="1">
+      <c r="E168" s="2">
         <v>45824</v>
       </c>
       <c r="F168">
@@ -6264,7 +6312,7 @@
         <v>37720.8</v>
       </c>
       <c r="H168">
-        <v>7544.16</v>
+        <v>7544.160000000001</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -6280,7 +6328,7 @@
       <c r="D169">
         <v>12.34</v>
       </c>
-      <c r="E169" s="1">
+      <c r="E169" s="2">
         <v>45825</v>
       </c>
       <c r="F169">
@@ -6306,17 +6354,17 @@
       <c r="D170">
         <v>12.04</v>
       </c>
-      <c r="E170" s="1">
+      <c r="E170" s="2">
         <v>45826</v>
       </c>
       <c r="F170">
         <v>541.8</v>
       </c>
       <c r="G170">
-        <v>39551.39999999999</v>
+        <v>39551.4</v>
       </c>
       <c r="H170">
-        <v>7910.279999999999</v>
+        <v>7910.280000000001</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -6332,17 +6380,17 @@
       <c r="D171">
         <v>130.87</v>
       </c>
-      <c r="E171" s="1">
+      <c r="E171" s="2">
         <v>45827</v>
       </c>
       <c r="F171">
         <v>5889.150000000001</v>
       </c>
       <c r="G171">
-        <v>323903.2500000001</v>
+        <v>323903.25</v>
       </c>
       <c r="H171">
-        <v>64780.65000000002</v>
+        <v>64780.65</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -6358,7 +6406,7 @@
       <c r="D172">
         <v>54.01</v>
       </c>
-      <c r="E172" s="1">
+      <c r="E172" s="2">
         <v>45828</v>
       </c>
       <c r="F172">
@@ -6384,7 +6432,7 @@
       <c r="D173">
         <v>71.75</v>
       </c>
-      <c r="E173" s="1">
+      <c r="E173" s="2">
         <v>45829</v>
       </c>
       <c r="F173">
@@ -6410,7 +6458,7 @@
       <c r="D174">
         <v>60.44</v>
       </c>
-      <c r="E174" s="1">
+      <c r="E174" s="2">
         <v>45830</v>
       </c>
       <c r="F174">
@@ -6436,7 +6484,7 @@
       <c r="D175">
         <v>85.94</v>
       </c>
-      <c r="E175" s="1">
+      <c r="E175" s="2">
         <v>45831</v>
       </c>
       <c r="F175">
@@ -6462,17 +6510,17 @@
       <c r="D176">
         <v>132.71</v>
       </c>
-      <c r="E176" s="1">
+      <c r="E176" s="2">
         <v>45832</v>
       </c>
       <c r="F176">
         <v>5971.950000000001</v>
       </c>
       <c r="G176">
-        <v>424008.4500000001</v>
+        <v>424008.45</v>
       </c>
       <c r="H176">
-        <v>84801.69000000002</v>
+        <v>84801.69</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -6488,7 +6536,7 @@
       <c r="D177">
         <v>5.42</v>
       </c>
-      <c r="E177" s="1">
+      <c r="E177" s="2">
         <v>45833</v>
       </c>
       <c r="F177">
@@ -6498,7 +6546,7 @@
         <v>21707.1</v>
       </c>
       <c r="H177">
-        <v>4341.420000000001</v>
+        <v>4341.42</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -6514,7 +6562,7 @@
       <c r="D178">
         <v>55.66</v>
       </c>
-      <c r="E178" s="1">
+      <c r="E178" s="2">
         <v>45834</v>
       </c>
       <c r="F178">
@@ -6540,7 +6588,7 @@
       <c r="D179">
         <v>30.1</v>
       </c>
-      <c r="E179" s="1">
+      <c r="E179" s="2">
         <v>45835</v>
       </c>
       <c r="F179">
@@ -6566,7 +6614,7 @@
       <c r="D180">
         <v>120.86</v>
       </c>
-      <c r="E180" s="1">
+      <c r="E180" s="2">
         <v>45836</v>
       </c>
       <c r="F180">
@@ -6592,14 +6640,14 @@
       <c r="D181">
         <v>21.35</v>
       </c>
-      <c r="E181" s="1">
+      <c r="E181" s="2">
         <v>45837</v>
       </c>
       <c r="F181">
         <v>960.7500000000001</v>
       </c>
       <c r="G181">
-        <v>9607.500000000002</v>
+        <v>9607.5</v>
       </c>
       <c r="H181">
         <v>1921.5</v>
@@ -6618,7 +6666,7 @@
       <c r="D182">
         <v>105.99</v>
       </c>
-      <c r="E182" s="1">
+      <c r="E182" s="2">
         <v>45838</v>
       </c>
       <c r="F182">
@@ -6644,14 +6692,14 @@
       <c r="D183">
         <v>5.89</v>
       </c>
-      <c r="E183" s="1">
+      <c r="E183" s="2">
         <v>45839</v>
       </c>
       <c r="F183">
         <v>265.05</v>
       </c>
       <c r="G183">
-        <v>7686.450000000001</v>
+        <v>7686.45</v>
       </c>
       <c r="H183">
         <v>1537.29</v>
@@ -6670,7 +6718,7 @@
       <c r="D184">
         <v>8.51</v>
       </c>
-      <c r="E184" s="1">
+      <c r="E184" s="2">
         <v>45840</v>
       </c>
       <c r="F184">
@@ -6696,7 +6744,7 @@
       <c r="D185">
         <v>123.09</v>
       </c>
-      <c r="E185" s="1">
+      <c r="E185" s="2">
         <v>45841</v>
       </c>
       <c r="F185">
@@ -6722,7 +6770,7 @@
       <c r="D186">
         <v>97.53</v>
       </c>
-      <c r="E186" s="1">
+      <c r="E186" s="2">
         <v>45842</v>
       </c>
       <c r="F186">
@@ -6748,7 +6796,7 @@
       <c r="D187">
         <v>137.59</v>
       </c>
-      <c r="E187" s="1">
+      <c r="E187" s="2">
         <v>45843</v>
       </c>
       <c r="F187">
@@ -6774,7 +6822,7 @@
       <c r="D188">
         <v>120.15</v>
       </c>
-      <c r="E188" s="1">
+      <c r="E188" s="2">
         <v>45844</v>
       </c>
       <c r="F188">
@@ -6800,17 +6848,17 @@
       <c r="D189">
         <v>82.15000000000001</v>
       </c>
-      <c r="E189" s="1">
+      <c r="E189" s="2">
         <v>45845</v>
       </c>
       <c r="F189">
         <v>3696.75</v>
       </c>
       <c r="G189">
-        <v>351191.2500000001</v>
+        <v>351191.25</v>
       </c>
       <c r="H189">
-        <v>70238.25000000001</v>
+        <v>70238.25</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -6826,7 +6874,7 @@
       <c r="D190">
         <v>42.92</v>
       </c>
-      <c r="E190" s="1">
+      <c r="E190" s="2">
         <v>45846</v>
       </c>
       <c r="F190">
@@ -6852,7 +6900,7 @@
       <c r="D191">
         <v>142.71</v>
       </c>
-      <c r="E191" s="1">
+      <c r="E191" s="2">
         <v>45847</v>
       </c>
       <c r="F191">
@@ -6862,7 +6910,7 @@
         <v>308253.6</v>
       </c>
       <c r="H191">
-        <v>61650.72000000001</v>
+        <v>61650.72</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -6878,7 +6926,7 @@
       <c r="D192">
         <v>22.85</v>
       </c>
-      <c r="E192" s="1">
+      <c r="E192" s="2">
         <v>45848</v>
       </c>
       <c r="F192">
@@ -6904,7 +6952,7 @@
       <c r="D193">
         <v>7.4</v>
       </c>
-      <c r="E193" s="1">
+      <c r="E193" s="2">
         <v>45849</v>
       </c>
       <c r="F193">
@@ -6930,7 +6978,7 @@
       <c r="D194">
         <v>44.58</v>
       </c>
-      <c r="E194" s="1">
+      <c r="E194" s="2">
         <v>45850</v>
       </c>
       <c r="F194">
@@ -6956,7 +7004,7 @@
       <c r="D195">
         <v>18.97</v>
       </c>
-      <c r="E195" s="1">
+      <c r="E195" s="2">
         <v>45851</v>
       </c>
       <c r="F195">
@@ -6982,17 +7030,17 @@
       <c r="D196">
         <v>108.13</v>
       </c>
-      <c r="E196" s="1">
+      <c r="E196" s="2">
         <v>45852</v>
       </c>
       <c r="F196">
         <v>4865.849999999999</v>
       </c>
       <c r="G196">
-        <v>403865.5499999999</v>
+        <v>403865.55</v>
       </c>
       <c r="H196">
-        <v>80773.10999999999</v>
+        <v>80773.11</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -7008,7 +7056,7 @@
       <c r="D197">
         <v>34.04</v>
       </c>
-      <c r="E197" s="1">
+      <c r="E197" s="2">
         <v>45853</v>
       </c>
       <c r="F197">
@@ -7034,7 +7082,7 @@
       <c r="D198">
         <v>106.69</v>
       </c>
-      <c r="E198" s="1">
+      <c r="E198" s="2">
         <v>45854</v>
       </c>
       <c r="F198">
@@ -7060,7 +7108,7 @@
       <c r="D199">
         <v>14.62</v>
       </c>
-      <c r="E199" s="1">
+      <c r="E199" s="2">
         <v>45855</v>
       </c>
       <c r="F199">
@@ -7086,7 +7134,7 @@
       <c r="D200">
         <v>8.039999999999999</v>
       </c>
-      <c r="E200" s="1">
+      <c r="E200" s="2">
         <v>45856</v>
       </c>
       <c r="F200">
@@ -7096,7 +7144,7 @@
         <v>27496.8</v>
       </c>
       <c r="H200">
-        <v>5499.36</v>
+        <v>5499.360000000001</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -7112,7 +7160,7 @@
       <c r="D201">
         <v>15.83</v>
       </c>
-      <c r="E201" s="1">
+      <c r="E201" s="2">
         <v>45857</v>
       </c>
       <c r="F201">
@@ -7138,7 +7186,7 @@
       <c r="D202">
         <v>24.09</v>
       </c>
-      <c r="E202" s="1">
+      <c r="E202" s="2">
         <v>45858</v>
       </c>
       <c r="F202">
@@ -7164,7 +7212,7 @@
       <c r="D203">
         <v>95.58</v>
       </c>
-      <c r="E203" s="1">
+      <c r="E203" s="2">
         <v>45859</v>
       </c>
       <c r="F203">
@@ -7190,7 +7238,7 @@
       <c r="D204">
         <v>20.76</v>
       </c>
-      <c r="E204" s="1">
+      <c r="E204" s="2">
         <v>45860</v>
       </c>
       <c r="F204">
@@ -7216,7 +7264,7 @@
       <c r="D205">
         <v>122.98</v>
       </c>
-      <c r="E205" s="1">
+      <c r="E205" s="2">
         <v>45861</v>
       </c>
       <c r="F205">
@@ -7242,7 +7290,7 @@
       <c r="D206">
         <v>136.82</v>
       </c>
-      <c r="E206" s="1">
+      <c r="E206" s="2">
         <v>45862</v>
       </c>
       <c r="F206">
@@ -7268,14 +7316,14 @@
       <c r="D207">
         <v>140.93</v>
       </c>
-      <c r="E207" s="1">
+      <c r="E207" s="2">
         <v>45863</v>
       </c>
       <c r="F207">
         <v>6341.85</v>
       </c>
       <c r="G207">
-        <v>615159.4500000001</v>
+        <v>615159.45</v>
       </c>
       <c r="H207">
         <v>123031.89</v>
@@ -7294,7 +7342,7 @@
       <c r="D208">
         <v>47.13</v>
       </c>
-      <c r="E208" s="1">
+      <c r="E208" s="2">
         <v>45864</v>
       </c>
       <c r="F208">
@@ -7320,7 +7368,7 @@
       <c r="D209">
         <v>74.62</v>
       </c>
-      <c r="E209" s="1">
+      <c r="E209" s="2">
         <v>45865</v>
       </c>
       <c r="F209">
@@ -7346,7 +7394,7 @@
       <c r="D210">
         <v>56.91</v>
       </c>
-      <c r="E210" s="1">
+      <c r="E210" s="2">
         <v>45866</v>
       </c>
       <c r="F210">
@@ -7356,7 +7404,7 @@
         <v>217680.75</v>
       </c>
       <c r="H210">
-        <v>43536.14999999999</v>
+        <v>43536.15</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -7372,14 +7420,14 @@
       <c r="D211">
         <v>33.34</v>
       </c>
-      <c r="E211" s="1">
+      <c r="E211" s="2">
         <v>45867</v>
       </c>
       <c r="F211">
         <v>1500.3</v>
       </c>
       <c r="G211">
-        <v>57011.40000000001</v>
+        <v>57011.4</v>
       </c>
       <c r="H211">
         <v>11402.28</v>
@@ -7398,7 +7446,7 @@
       <c r="D212">
         <v>77.8</v>
       </c>
-      <c r="E212" s="1">
+      <c r="E212" s="2">
         <v>45868</v>
       </c>
       <c r="F212">
@@ -7424,7 +7472,7 @@
       <c r="D213">
         <v>110.41</v>
       </c>
-      <c r="E213" s="1">
+      <c r="E213" s="2">
         <v>45869</v>
       </c>
       <c r="F213">
@@ -7450,14 +7498,14 @@
       <c r="D214">
         <v>142.95</v>
       </c>
-      <c r="E214" s="1">
+      <c r="E214" s="2">
         <v>45870</v>
       </c>
       <c r="F214">
         <v>6432.749999999999</v>
       </c>
       <c r="G214">
-        <v>598245.7499999999</v>
+        <v>598245.75</v>
       </c>
       <c r="H214">
         <v>119649.15</v>
@@ -7476,7 +7524,7 @@
       <c r="D215">
         <v>116.3</v>
       </c>
-      <c r="E215" s="1">
+      <c r="E215" s="2">
         <v>45871</v>
       </c>
       <c r="F215">
@@ -7502,7 +7550,7 @@
       <c r="D216">
         <v>115.65</v>
       </c>
-      <c r="E216" s="1">
+      <c r="E216" s="2">
         <v>45872</v>
       </c>
       <c r="F216">
@@ -7528,7 +7576,7 @@
       <c r="D217">
         <v>45.25</v>
       </c>
-      <c r="E217" s="1">
+      <c r="E217" s="2">
         <v>45873</v>
       </c>
       <c r="F217">
@@ -7554,7 +7602,7 @@
       <c r="D218">
         <v>31.62</v>
       </c>
-      <c r="E218" s="1">
+      <c r="E218" s="2">
         <v>45874</v>
       </c>
       <c r="F218">
@@ -7580,7 +7628,7 @@
       <c r="D219">
         <v>8.18</v>
       </c>
-      <c r="E219" s="1">
+      <c r="E219" s="2">
         <v>45875</v>
       </c>
       <c r="F219">
@@ -7606,7 +7654,7 @@
       <c r="D220">
         <v>39.04</v>
       </c>
-      <c r="E220" s="1">
+      <c r="E220" s="2">
         <v>45876</v>
       </c>
       <c r="F220">
@@ -7632,14 +7680,14 @@
       <c r="D221">
         <v>78.77</v>
       </c>
-      <c r="E221" s="1">
+      <c r="E221" s="2">
         <v>45877</v>
       </c>
       <c r="F221">
         <v>3544.65</v>
       </c>
       <c r="G221">
-        <v>38991.14999999999</v>
+        <v>38991.15</v>
       </c>
       <c r="H221">
         <v>7798.23</v>
@@ -7658,7 +7706,7 @@
       <c r="D222">
         <v>130.43</v>
       </c>
-      <c r="E222" s="1">
+      <c r="E222" s="2">
         <v>45878</v>
       </c>
       <c r="F222">
@@ -7684,7 +7732,7 @@
       <c r="D223">
         <v>39.59</v>
       </c>
-      <c r="E223" s="1">
+      <c r="E223" s="2">
         <v>45879</v>
       </c>
       <c r="F223">
@@ -7710,7 +7758,7 @@
       <c r="D224">
         <v>7</v>
       </c>
-      <c r="E224" s="1">
+      <c r="E224" s="2">
         <v>45880</v>
       </c>
       <c r="F224">
@@ -7736,7 +7784,7 @@
       <c r="D225">
         <v>125.94</v>
       </c>
-      <c r="E225" s="1">
+      <c r="E225" s="2">
         <v>45881</v>
       </c>
       <c r="F225">
@@ -7762,7 +7810,7 @@
       <c r="D226">
         <v>124.2</v>
       </c>
-      <c r="E226" s="1">
+      <c r="E226" s="2">
         <v>45882</v>
       </c>
       <c r="F226">
@@ -7788,7 +7836,7 @@
       <c r="D227">
         <v>111.05</v>
       </c>
-      <c r="E227" s="1">
+      <c r="E227" s="2">
         <v>45883</v>
       </c>
       <c r="F227">
@@ -7814,14 +7862,14 @@
       <c r="D228">
         <v>51.27</v>
       </c>
-      <c r="E228" s="1">
+      <c r="E228" s="2">
         <v>45884</v>
       </c>
       <c r="F228">
         <v>2307.15</v>
       </c>
       <c r="G228">
-        <v>83057.40000000001</v>
+        <v>83057.39999999999</v>
       </c>
       <c r="H228">
         <v>16611.48</v>
@@ -7840,14 +7888,14 @@
       <c r="D229">
         <v>138.84</v>
       </c>
-      <c r="E229" s="1">
+      <c r="E229" s="2">
         <v>45885</v>
       </c>
       <c r="F229">
         <v>6247.8</v>
       </c>
       <c r="G229">
-        <v>81221.40000000001</v>
+        <v>81221.39999999999</v>
       </c>
       <c r="H229">
         <v>16244.28</v>
@@ -7866,7 +7914,7 @@
       <c r="D230">
         <v>32.93</v>
       </c>
-      <c r="E230" s="1">
+      <c r="E230" s="2">
         <v>45886</v>
       </c>
       <c r="F230">
@@ -7892,7 +7940,7 @@
       <c r="D231">
         <v>21.87</v>
       </c>
-      <c r="E231" s="1">
+      <c r="E231" s="2">
         <v>45887</v>
       </c>
       <c r="F231">
@@ -7918,7 +7966,7 @@
       <c r="D232">
         <v>26.86</v>
       </c>
-      <c r="E232" s="1">
+      <c r="E232" s="2">
         <v>45888</v>
       </c>
       <c r="F232">
@@ -7944,7 +7992,7 @@
       <c r="D233">
         <v>55.67</v>
       </c>
-      <c r="E233" s="1">
+      <c r="E233" s="2">
         <v>45889</v>
       </c>
       <c r="F233">
@@ -7970,7 +8018,7 @@
       <c r="D234">
         <v>103.15</v>
       </c>
-      <c r="E234" s="1">
+      <c r="E234" s="2">
         <v>45890</v>
       </c>
       <c r="F234">
@@ -7996,7 +8044,7 @@
       <c r="D235">
         <v>99.12</v>
       </c>
-      <c r="E235" s="1">
+      <c r="E235" s="2">
         <v>45891</v>
       </c>
       <c r="F235">
@@ -8022,7 +8070,7 @@
       <c r="D236">
         <v>34.49</v>
       </c>
-      <c r="E236" s="1">
+      <c r="E236" s="2">
         <v>45892</v>
       </c>
       <c r="F236">
@@ -8048,7 +8096,7 @@
       <c r="D237">
         <v>61.01</v>
       </c>
-      <c r="E237" s="1">
+      <c r="E237" s="2">
         <v>45893</v>
       </c>
       <c r="F237">
@@ -8074,7 +8122,7 @@
       <c r="D238">
         <v>58.8</v>
       </c>
-      <c r="E238" s="1">
+      <c r="E238" s="2">
         <v>45894</v>
       </c>
       <c r="F238">
@@ -8100,7 +8148,7 @@
       <c r="D239">
         <v>11.46</v>
       </c>
-      <c r="E239" s="1">
+      <c r="E239" s="2">
         <v>45895</v>
       </c>
       <c r="F239">
@@ -8126,7 +8174,7 @@
       <c r="D240">
         <v>141.47</v>
       </c>
-      <c r="E240" s="1">
+      <c r="E240" s="2">
         <v>45896</v>
       </c>
       <c r="F240">
@@ -8152,7 +8200,7 @@
       <c r="D241">
         <v>27</v>
       </c>
-      <c r="E241" s="1">
+      <c r="E241" s="2">
         <v>45897</v>
       </c>
       <c r="F241">
@@ -8178,7 +8226,7 @@
       <c r="D242">
         <v>8.890000000000001</v>
       </c>
-      <c r="E242" s="1">
+      <c r="E242" s="2">
         <v>45898</v>
       </c>
       <c r="F242">
@@ -8204,7 +8252,7 @@
       <c r="D243">
         <v>123.98</v>
       </c>
-      <c r="E243" s="1">
+      <c r="E243" s="2">
         <v>45899</v>
       </c>
       <c r="F243">
@@ -8214,7 +8262,7 @@
         <v>133898.4</v>
       </c>
       <c r="H243">
-        <v>26779.68000000001</v>
+        <v>26779.68</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -8230,14 +8278,14 @@
       <c r="D244">
         <v>6.98</v>
       </c>
-      <c r="E244" s="1">
+      <c r="E244" s="2">
         <v>45900</v>
       </c>
       <c r="F244">
         <v>314.1</v>
       </c>
       <c r="G244">
-        <v>9108.900000000001</v>
+        <v>9108.9</v>
       </c>
       <c r="H244">
         <v>1821.78</v>
@@ -8256,7 +8304,7 @@
       <c r="D245">
         <v>12.06</v>
       </c>
-      <c r="E245" s="1">
+      <c r="E245" s="2">
         <v>45901</v>
       </c>
       <c r="F245">
@@ -8282,7 +8330,7 @@
       <c r="D246">
         <v>37.31</v>
       </c>
-      <c r="E246" s="1">
+      <c r="E246" s="2">
         <v>45902</v>
       </c>
       <c r="F246">
@@ -8308,7 +8356,7 @@
       <c r="D247">
         <v>11.1</v>
       </c>
-      <c r="E247" s="1">
+      <c r="E247" s="2">
         <v>45903</v>
       </c>
       <c r="F247">
@@ -8334,7 +8382,7 @@
       <c r="D248">
         <v>21.3</v>
       </c>
-      <c r="E248" s="1">
+      <c r="E248" s="2">
         <v>45904</v>
       </c>
       <c r="F248">
@@ -8360,7 +8408,7 @@
       <c r="D249">
         <v>58.54</v>
       </c>
-      <c r="E249" s="1">
+      <c r="E249" s="2">
         <v>45905</v>
       </c>
       <c r="F249">
@@ -8386,7 +8434,7 @@
       <c r="D250">
         <v>113.57</v>
       </c>
-      <c r="E250" s="1">
+      <c r="E250" s="2">
         <v>45906</v>
       </c>
       <c r="F250">
@@ -8396,7 +8444,7 @@
         <v>373077.45</v>
       </c>
       <c r="H250">
-        <v>74615.48999999999</v>
+        <v>74615.49000000001</v>
       </c>
     </row>
     <row r="251" spans="1:8">
@@ -8412,7 +8460,7 @@
       <c r="D251">
         <v>141.75</v>
       </c>
-      <c r="E251" s="1">
+      <c r="E251" s="2">
         <v>45907</v>
       </c>
       <c r="F251">
@@ -8438,7 +8486,7 @@
       <c r="D252">
         <v>129.75</v>
       </c>
-      <c r="E252" s="1">
+      <c r="E252" s="2">
         <v>45908</v>
       </c>
       <c r="F252">
@@ -8464,17 +8512,17 @@
       <c r="D253">
         <v>131.7</v>
       </c>
-      <c r="E253" s="1">
+      <c r="E253" s="2">
         <v>45909</v>
       </c>
       <c r="F253">
         <v>5926.499999999999</v>
       </c>
       <c r="G253">
-        <v>325957.4999999999</v>
+        <v>325957.5</v>
       </c>
       <c r="H253">
-        <v>65191.49999999999</v>
+        <v>65191.5</v>
       </c>
     </row>
     <row r="254" spans="1:8">
@@ -8490,7 +8538,7 @@
       <c r="D254">
         <v>79.08</v>
       </c>
-      <c r="E254" s="1">
+      <c r="E254" s="2">
         <v>45910</v>
       </c>
       <c r="F254">
@@ -8516,7 +8564,7 @@
       <c r="D255">
         <v>134.12</v>
       </c>
-      <c r="E255" s="1">
+      <c r="E255" s="2">
         <v>45911</v>
       </c>
       <c r="F255">
@@ -8542,7 +8590,7 @@
       <c r="D256">
         <v>63.35</v>
       </c>
-      <c r="E256" s="1">
+      <c r="E256" s="2">
         <v>45912</v>
       </c>
       <c r="F256">
@@ -8568,7 +8616,7 @@
       <c r="D257">
         <v>78.19</v>
       </c>
-      <c r="E257" s="1">
+      <c r="E257" s="2">
         <v>45913</v>
       </c>
       <c r="F257">
@@ -8594,7 +8642,7 @@
       <c r="D258">
         <v>119.83</v>
       </c>
-      <c r="E258" s="1">
+      <c r="E258" s="2">
         <v>45914</v>
       </c>
       <c r="F258">
@@ -8620,7 +8668,7 @@
       <c r="D259">
         <v>126.17</v>
       </c>
-      <c r="E259" s="1">
+      <c r="E259" s="2">
         <v>45915</v>
       </c>
       <c r="F259">
@@ -8630,7 +8678,7 @@
         <v>39743.55</v>
       </c>
       <c r="H259">
-        <v>7948.709999999999</v>
+        <v>7948.710000000001</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -8646,7 +8694,7 @@
       <c r="D260">
         <v>96.25</v>
       </c>
-      <c r="E260" s="1">
+      <c r="E260" s="2">
         <v>45916</v>
       </c>
       <c r="F260">
@@ -8672,7 +8720,7 @@
       <c r="D261">
         <v>53.02</v>
       </c>
-      <c r="E261" s="1">
+      <c r="E261" s="2">
         <v>45917</v>
       </c>
       <c r="F261">
@@ -8698,7 +8746,7 @@
       <c r="D262">
         <v>6.74</v>
       </c>
-      <c r="E262" s="1">
+      <c r="E262" s="2">
         <v>45918</v>
       </c>
       <c r="F262">
@@ -8724,7 +8772,7 @@
       <c r="D263">
         <v>64.38</v>
       </c>
-      <c r="E263" s="1">
+      <c r="E263" s="2">
         <v>45919</v>
       </c>
       <c r="F263">
@@ -8750,7 +8798,7 @@
       <c r="D264">
         <v>86.38</v>
       </c>
-      <c r="E264" s="1">
+      <c r="E264" s="2">
         <v>45920</v>
       </c>
       <c r="F264">
@@ -8776,7 +8824,7 @@
       <c r="D265">
         <v>89</v>
       </c>
-      <c r="E265" s="1">
+      <c r="E265" s="2">
         <v>45921</v>
       </c>
       <c r="F265">
@@ -8802,7 +8850,7 @@
       <c r="D266">
         <v>74.84</v>
       </c>
-      <c r="E266" s="1">
+      <c r="E266" s="2">
         <v>45922</v>
       </c>
       <c r="F266">
@@ -8812,7 +8860,7 @@
         <v>188596.8</v>
       </c>
       <c r="H266">
-        <v>37719.36000000001</v>
+        <v>37719.36</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -8828,7 +8876,7 @@
       <c r="D267">
         <v>13.81</v>
       </c>
-      <c r="E267" s="1">
+      <c r="E267" s="2">
         <v>45923</v>
       </c>
       <c r="F267">
@@ -8854,7 +8902,7 @@
       <c r="D268">
         <v>118.99</v>
       </c>
-      <c r="E268" s="1">
+      <c r="E268" s="2">
         <v>45924</v>
       </c>
       <c r="F268">
@@ -8880,14 +8928,14 @@
       <c r="D269">
         <v>94.86</v>
       </c>
-      <c r="E269" s="1">
+      <c r="E269" s="2">
         <v>45925</v>
       </c>
       <c r="F269">
         <v>4268.7</v>
       </c>
       <c r="G269">
-        <v>98180.09999999999</v>
+        <v>98180.10000000001</v>
       </c>
       <c r="H269">
         <v>19636.02</v>
@@ -8906,7 +8954,7 @@
       <c r="D270">
         <v>79.33</v>
       </c>
-      <c r="E270" s="1">
+      <c r="E270" s="2">
         <v>45926</v>
       </c>
       <c r="F270">
@@ -8916,7 +8964,7 @@
         <v>239179.95</v>
       </c>
       <c r="H270">
-        <v>47835.99</v>
+        <v>47835.99000000001</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -8932,7 +8980,7 @@
       <c r="D271">
         <v>42.67</v>
       </c>
-      <c r="E271" s="1">
+      <c r="E271" s="2">
         <v>45927</v>
       </c>
       <c r="F271">
@@ -8958,7 +9006,7 @@
       <c r="D272">
         <v>123.08</v>
       </c>
-      <c r="E272" s="1">
+      <c r="E272" s="2">
         <v>45928</v>
       </c>
       <c r="F272">
@@ -8984,7 +9032,7 @@
       <c r="D273">
         <v>47.97</v>
       </c>
-      <c r="E273" s="1">
+      <c r="E273" s="2">
         <v>45929</v>
       </c>
       <c r="F273">
@@ -9010,7 +9058,7 @@
       <c r="D274">
         <v>73.75</v>
       </c>
-      <c r="E274" s="1">
+      <c r="E274" s="2">
         <v>45930</v>
       </c>
       <c r="F274">
@@ -9036,7 +9084,7 @@
       <c r="D275">
         <v>142.17</v>
       </c>
-      <c r="E275" s="1">
+      <c r="E275" s="2">
         <v>45931</v>
       </c>
       <c r="F275">
@@ -9062,7 +9110,7 @@
       <c r="D276">
         <v>9.279999999999999</v>
       </c>
-      <c r="E276" s="1">
+      <c r="E276" s="2">
         <v>45932</v>
       </c>
       <c r="F276">
@@ -9088,7 +9136,7 @@
       <c r="D277">
         <v>128.14</v>
       </c>
-      <c r="E277" s="1">
+      <c r="E277" s="2">
         <v>45933</v>
       </c>
       <c r="F277">
@@ -9114,7 +9162,7 @@
       <c r="D278">
         <v>131.42</v>
       </c>
-      <c r="E278" s="1">
+      <c r="E278" s="2">
         <v>45934</v>
       </c>
       <c r="F278">
@@ -9140,7 +9188,7 @@
       <c r="D279">
         <v>106.67</v>
       </c>
-      <c r="E279" s="1">
+      <c r="E279" s="2">
         <v>45935</v>
       </c>
       <c r="F279">
@@ -9150,7 +9198,7 @@
         <v>206406.45</v>
       </c>
       <c r="H279">
-        <v>41281.29</v>
+        <v>41281.29000000001</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -9166,7 +9214,7 @@
       <c r="D280">
         <v>139.78</v>
       </c>
-      <c r="E280" s="1">
+      <c r="E280" s="2">
         <v>45936</v>
       </c>
       <c r="F280">
@@ -9192,14 +9240,14 @@
       <c r="D281">
         <v>67.98</v>
       </c>
-      <c r="E281" s="1">
+      <c r="E281" s="2">
         <v>45937</v>
       </c>
       <c r="F281">
         <v>3059.1</v>
       </c>
       <c r="G281">
-        <v>6118.200000000001</v>
+        <v>6118.2</v>
       </c>
       <c r="H281">
         <v>1223.64</v>
@@ -9218,7 +9266,7 @@
       <c r="D282">
         <v>95.36</v>
       </c>
-      <c r="E282" s="1">
+      <c r="E282" s="2">
         <v>45938</v>
       </c>
       <c r="F282">
@@ -9244,7 +9292,7 @@
       <c r="D283">
         <v>7.54</v>
       </c>
-      <c r="E283" s="1">
+      <c r="E283" s="2">
         <v>45939</v>
       </c>
       <c r="F283">
@@ -9254,7 +9302,7 @@
         <v>26126.1</v>
       </c>
       <c r="H283">
-        <v>5225.220000000001</v>
+        <v>5225.22</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -9270,7 +9318,7 @@
       <c r="D284">
         <v>55.2</v>
       </c>
-      <c r="E284" s="1">
+      <c r="E284" s="2">
         <v>45940</v>
       </c>
       <c r="F284">
@@ -9296,7 +9344,7 @@
       <c r="D285">
         <v>11.6</v>
       </c>
-      <c r="E285" s="1">
+      <c r="E285" s="2">
         <v>45941</v>
       </c>
       <c r="F285">
@@ -9322,7 +9370,7 @@
       <c r="D286">
         <v>59.09</v>
       </c>
-      <c r="E286" s="1">
+      <c r="E286" s="2">
         <v>45942</v>
       </c>
       <c r="F286">
@@ -9332,7 +9380,7 @@
         <v>255268.8</v>
       </c>
       <c r="H286">
-        <v>51053.76000000001</v>
+        <v>51053.76</v>
       </c>
     </row>
     <row r="287" spans="1:8">
@@ -9348,7 +9396,7 @@
       <c r="D287">
         <v>11.84</v>
       </c>
-      <c r="E287" s="1">
+      <c r="E287" s="2">
         <v>45943</v>
       </c>
       <c r="F287">
@@ -9358,7 +9406,7 @@
         <v>35164.8</v>
       </c>
       <c r="H287">
-        <v>7032.959999999999</v>
+        <v>7032.960000000001</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -9374,7 +9422,7 @@
       <c r="D288">
         <v>132.16</v>
       </c>
-      <c r="E288" s="1">
+      <c r="E288" s="2">
         <v>45944</v>
       </c>
       <c r="F288">
@@ -9400,7 +9448,7 @@
       <c r="D289">
         <v>17.72</v>
       </c>
-      <c r="E289" s="1">
+      <c r="E289" s="2">
         <v>45945</v>
       </c>
       <c r="F289">
@@ -9426,7 +9474,7 @@
       <c r="D290">
         <v>145.18</v>
       </c>
-      <c r="E290" s="1">
+      <c r="E290" s="2">
         <v>45946</v>
       </c>
       <c r="F290">
@@ -9452,7 +9500,7 @@
       <c r="D291">
         <v>12.34</v>
       </c>
-      <c r="E291" s="1">
+      <c r="E291" s="2">
         <v>45947</v>
       </c>
       <c r="F291">
@@ -9478,7 +9526,7 @@
       <c r="D292">
         <v>66.09999999999999</v>
       </c>
-      <c r="E292" s="1">
+      <c r="E292" s="2">
         <v>45948</v>
       </c>
       <c r="F292">
@@ -9504,7 +9552,7 @@
       <c r="D293">
         <v>29.03</v>
       </c>
-      <c r="E293" s="1">
+      <c r="E293" s="2">
         <v>45949</v>
       </c>
       <c r="F293">
@@ -9530,7 +9578,7 @@
       <c r="D294">
         <v>19.39</v>
       </c>
-      <c r="E294" s="1">
+      <c r="E294" s="2">
         <v>45950</v>
       </c>
       <c r="F294">
@@ -9540,7 +9588,7 @@
         <v>34029.45</v>
       </c>
       <c r="H294">
-        <v>6805.890000000001</v>
+        <v>6805.889999999999</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -9556,7 +9604,7 @@
       <c r="D295">
         <v>145.16</v>
       </c>
-      <c r="E295" s="1">
+      <c r="E295" s="2">
         <v>45951</v>
       </c>
       <c r="F295">
@@ -9582,7 +9630,7 @@
       <c r="D296">
         <v>112.56</v>
       </c>
-      <c r="E296" s="1">
+      <c r="E296" s="2">
         <v>45952</v>
       </c>
       <c r="F296">
@@ -9608,7 +9656,7 @@
       <c r="D297">
         <v>12.34</v>
       </c>
-      <c r="E297" s="1">
+      <c r="E297" s="2">
         <v>45953</v>
       </c>
       <c r="F297">
@@ -9634,7 +9682,7 @@
       <c r="D298">
         <v>70.56999999999999</v>
       </c>
-      <c r="E298" s="1">
+      <c r="E298" s="2">
         <v>45954</v>
       </c>
       <c r="F298">
@@ -9644,7 +9692,7 @@
         <v>22229.55</v>
       </c>
       <c r="H298">
-        <v>4445.909999999999</v>
+        <v>4445.91</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -9660,7 +9708,7 @@
       <c r="D299">
         <v>87.34999999999999</v>
       </c>
-      <c r="E299" s="1">
+      <c r="E299" s="2">
         <v>45955</v>
       </c>
       <c r="F299">
@@ -9670,7 +9718,7 @@
         <v>196537.5</v>
       </c>
       <c r="H299">
-        <v>39307.49999999999</v>
+        <v>39307.5</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -9686,7 +9734,7 @@
       <c r="D300">
         <v>128.63</v>
       </c>
-      <c r="E300" s="1">
+      <c r="E300" s="2">
         <v>45956</v>
       </c>
       <c r="F300">
@@ -9712,7 +9760,7 @@
       <c r="D301">
         <v>16.94</v>
       </c>
-      <c r="E301" s="1">
+      <c r="E301" s="2">
         <v>45957</v>
       </c>
       <c r="F301">
@@ -9738,7 +9786,7 @@
       <c r="D302">
         <v>5.54</v>
       </c>
-      <c r="E302" s="1">
+      <c r="E302" s="2">
         <v>45958</v>
       </c>
       <c r="F302">
@@ -9764,7 +9812,7 @@
       <c r="D303">
         <v>94.11</v>
       </c>
-      <c r="E303" s="1">
+      <c r="E303" s="2">
         <v>45959</v>
       </c>
       <c r="F303">
@@ -9790,7 +9838,7 @@
       <c r="D304">
         <v>99.05</v>
       </c>
-      <c r="E304" s="1">
+      <c r="E304" s="2">
         <v>45960</v>
       </c>
       <c r="F304">
@@ -9816,7 +9864,7 @@
       <c r="D305">
         <v>113.73</v>
       </c>
-      <c r="E305" s="1">
+      <c r="E305" s="2">
         <v>45961</v>
       </c>
       <c r="F305">
@@ -9842,7 +9890,7 @@
       <c r="D306">
         <v>136.84</v>
       </c>
-      <c r="E306" s="1">
+      <c r="E306" s="2">
         <v>45962</v>
       </c>
       <c r="F306">
@@ -9868,7 +9916,7 @@
       <c r="D307">
         <v>78.98</v>
       </c>
-      <c r="E307" s="1">
+      <c r="E307" s="2">
         <v>45963</v>
       </c>
       <c r="F307">
@@ -9894,7 +9942,7 @@
       <c r="D308">
         <v>134.93</v>
       </c>
-      <c r="E308" s="1">
+      <c r="E308" s="2">
         <v>45964</v>
       </c>
       <c r="F308">
@@ -9920,7 +9968,7 @@
       <c r="D309">
         <v>129.62</v>
       </c>
-      <c r="E309" s="1">
+      <c r="E309" s="2">
         <v>45965</v>
       </c>
       <c r="F309">
@@ -9946,17 +9994,17 @@
       <c r="D310">
         <v>146.3</v>
       </c>
-      <c r="E310" s="1">
+      <c r="E310" s="2">
         <v>45966</v>
       </c>
       <c r="F310">
         <v>6583.500000000001</v>
       </c>
       <c r="G310">
-        <v>322591.5000000001</v>
+        <v>322591.5</v>
       </c>
       <c r="H310">
-        <v>64518.30000000002</v>
+        <v>64518.3</v>
       </c>
     </row>
     <row r="311" spans="1:8">
@@ -9972,7 +10020,7 @@
       <c r="D311">
         <v>91.01000000000001</v>
       </c>
-      <c r="E311" s="1">
+      <c r="E311" s="2">
         <v>45967</v>
       </c>
       <c r="F311">
@@ -9998,7 +10046,7 @@
       <c r="D312">
         <v>6.18</v>
       </c>
-      <c r="E312" s="1">
+      <c r="E312" s="2">
         <v>45968</v>
       </c>
       <c r="F312">
@@ -10024,7 +10072,7 @@
       <c r="D313">
         <v>128.59</v>
       </c>
-      <c r="E313" s="1">
+      <c r="E313" s="2">
         <v>45969</v>
       </c>
       <c r="F313">
@@ -10034,7 +10082,7 @@
         <v>474497.1</v>
       </c>
       <c r="H313">
-        <v>94899.42000000001</v>
+        <v>94899.42</v>
       </c>
     </row>
     <row r="314" spans="1:8">
@@ -10050,7 +10098,7 @@
       <c r="D314">
         <v>40.72</v>
       </c>
-      <c r="E314" s="1">
+      <c r="E314" s="2">
         <v>45970</v>
       </c>
       <c r="F314">
@@ -10076,7 +10124,7 @@
       <c r="D315">
         <v>86.3</v>
       </c>
-      <c r="E315" s="1">
+      <c r="E315" s="2">
         <v>45971</v>
       </c>
       <c r="F315">
@@ -10102,14 +10150,14 @@
       <c r="D316">
         <v>104.02</v>
       </c>
-      <c r="E316" s="1">
+      <c r="E316" s="2">
         <v>45972</v>
       </c>
       <c r="F316">
         <v>4680.9</v>
       </c>
       <c r="G316">
-        <v>79575.29999999999</v>
+        <v>79575.3</v>
       </c>
       <c r="H316">
         <v>15915.06</v>
@@ -10128,7 +10176,7 @@
       <c r="D317">
         <v>98.73999999999999</v>
       </c>
-      <c r="E317" s="1">
+      <c r="E317" s="2">
         <v>45973</v>
       </c>
       <c r="F317">
@@ -10154,14 +10202,14 @@
       <c r="D318">
         <v>41.8</v>
       </c>
-      <c r="E318" s="1">
+      <c r="E318" s="2">
         <v>45974</v>
       </c>
       <c r="F318">
         <v>1881</v>
       </c>
       <c r="G318">
-        <v>9404.999999999998</v>
+        <v>9405</v>
       </c>
       <c r="H318">
         <v>1881</v>
@@ -10180,14 +10228,14 @@
       <c r="D319">
         <v>132.04</v>
       </c>
-      <c r="E319" s="1">
+      <c r="E319" s="2">
         <v>45975</v>
       </c>
       <c r="F319">
         <v>5941.799999999999</v>
       </c>
       <c r="G319">
-        <v>445634.9999999999</v>
+        <v>445635</v>
       </c>
       <c r="H319">
         <v>89127</v>
@@ -10206,14 +10254,14 @@
       <c r="D320">
         <v>5.04</v>
       </c>
-      <c r="E320" s="1">
+      <c r="E320" s="2">
         <v>45976</v>
       </c>
       <c r="F320">
         <v>226.8</v>
       </c>
       <c r="G320">
-        <v>9298.800000000001</v>
+        <v>9298.799999999999</v>
       </c>
       <c r="H320">
         <v>1859.76</v>
@@ -10232,7 +10280,7 @@
       <c r="D321">
         <v>9.49</v>
       </c>
-      <c r="E321" s="1">
+      <c r="E321" s="2">
         <v>45977</v>
       </c>
       <c r="F321">
@@ -10258,7 +10306,7 @@
       <c r="D322">
         <v>42.35</v>
       </c>
-      <c r="E322" s="1">
+      <c r="E322" s="2">
         <v>45978</v>
       </c>
       <c r="F322">
@@ -10284,7 +10332,7 @@
       <c r="D323">
         <v>122.31</v>
       </c>
-      <c r="E323" s="1">
+      <c r="E323" s="2">
         <v>45979</v>
       </c>
       <c r="F323">
@@ -10310,14 +10358,14 @@
       <c r="D324">
         <v>35.92</v>
       </c>
-      <c r="E324" s="1">
+      <c r="E324" s="2">
         <v>45980</v>
       </c>
       <c r="F324">
         <v>1616.4</v>
       </c>
       <c r="G324">
-        <v>82436.40000000001</v>
+        <v>82436.39999999999</v>
       </c>
       <c r="H324">
         <v>16487.28</v>
@@ -10336,7 +10384,7 @@
       <c r="D325">
         <v>147.7</v>
       </c>
-      <c r="E325" s="1">
+      <c r="E325" s="2">
         <v>45981</v>
       </c>
       <c r="F325">
@@ -10362,7 +10410,7 @@
       <c r="D326">
         <v>121.47</v>
       </c>
-      <c r="E326" s="1">
+      <c r="E326" s="2">
         <v>45982</v>
       </c>
       <c r="F326">
@@ -10388,7 +10436,7 @@
       <c r="D327">
         <v>57.03</v>
       </c>
-      <c r="E327" s="1">
+      <c r="E327" s="2">
         <v>45983</v>
       </c>
       <c r="F327">
@@ -10414,14 +10462,14 @@
       <c r="D328">
         <v>71.84999999999999</v>
       </c>
-      <c r="E328" s="1">
+      <c r="E328" s="2">
         <v>45984</v>
       </c>
       <c r="F328">
         <v>3233.25</v>
       </c>
       <c r="G328">
-        <v>58198.49999999999</v>
+        <v>58198.5</v>
       </c>
       <c r="H328">
         <v>11639.7</v>
@@ -10440,7 +10488,7 @@
       <c r="D329">
         <v>28.71</v>
       </c>
-      <c r="E329" s="1">
+      <c r="E329" s="2">
         <v>45985</v>
       </c>
       <c r="F329">
@@ -10466,7 +10514,7 @@
       <c r="D330">
         <v>82.59999999999999</v>
       </c>
-      <c r="E330" s="1">
+      <c r="E330" s="2">
         <v>45986</v>
       </c>
       <c r="F330">
@@ -10492,7 +10540,7 @@
       <c r="D331">
         <v>142.01</v>
       </c>
-      <c r="E331" s="1">
+      <c r="E331" s="2">
         <v>45987</v>
       </c>
       <c r="F331">
@@ -10518,7 +10566,7 @@
       <c r="D332">
         <v>26.09</v>
       </c>
-      <c r="E332" s="1">
+      <c r="E332" s="2">
         <v>45988</v>
       </c>
       <c r="F332">
@@ -10544,7 +10592,7 @@
       <c r="D333">
         <v>68.06</v>
       </c>
-      <c r="E333" s="1">
+      <c r="E333" s="2">
         <v>45989</v>
       </c>
       <c r="F333">
@@ -10570,14 +10618,14 @@
       <c r="D334">
         <v>51.99</v>
       </c>
-      <c r="E334" s="1">
+      <c r="E334" s="2">
         <v>45990</v>
       </c>
       <c r="F334">
         <v>2339.55</v>
       </c>
       <c r="G334">
-        <v>51470.10000000001</v>
+        <v>51470.1</v>
       </c>
       <c r="H334">
         <v>10294.02</v>
@@ -10596,7 +10644,7 @@
       <c r="D335">
         <v>71.16</v>
       </c>
-      <c r="E335" s="1">
+      <c r="E335" s="2">
         <v>45991</v>
       </c>
       <c r="F335">
@@ -10622,7 +10670,7 @@
       <c r="D336">
         <v>47.23</v>
       </c>
-      <c r="E336" s="1">
+      <c r="E336" s="2">
         <v>45992</v>
       </c>
       <c r="F336">
@@ -10648,7 +10696,7 @@
       <c r="D337">
         <v>125.36</v>
       </c>
-      <c r="E337" s="1">
+      <c r="E337" s="2">
         <v>45993</v>
       </c>
       <c r="F337">
@@ -10658,7 +10706,7 @@
         <v>406166.4</v>
       </c>
       <c r="H337">
-        <v>81233.28</v>
+        <v>81233.28000000001</v>
       </c>
     </row>
     <row r="338" spans="1:8">
@@ -10674,7 +10722,7 @@
       <c r="D338">
         <v>48.37</v>
       </c>
-      <c r="E338" s="1">
+      <c r="E338" s="2">
         <v>45994</v>
       </c>
       <c r="F338">
@@ -10700,7 +10748,7 @@
       <c r="D339">
         <v>139.58</v>
       </c>
-      <c r="E339" s="1">
+      <c r="E339" s="2">
         <v>45995</v>
       </c>
       <c r="F339">
@@ -10726,7 +10774,7 @@
       <c r="D340">
         <v>95.43000000000001</v>
       </c>
-      <c r="E340" s="1">
+      <c r="E340" s="2">
         <v>45996</v>
       </c>
       <c r="F340">
@@ -10752,7 +10800,7 @@
       <c r="D341">
         <v>149.27</v>
       </c>
-      <c r="E341" s="1">
+      <c r="E341" s="2">
         <v>45997</v>
       </c>
       <c r="F341">
@@ -10778,7 +10826,7 @@
       <c r="D342">
         <v>124.82</v>
       </c>
-      <c r="E342" s="1">
+      <c r="E342" s="2">
         <v>45998</v>
       </c>
       <c r="F342">
@@ -10804,7 +10852,7 @@
       <c r="D343">
         <v>115.78</v>
       </c>
-      <c r="E343" s="1">
+      <c r="E343" s="2">
         <v>45999</v>
       </c>
       <c r="F343">
@@ -10830,7 +10878,7 @@
       <c r="D344">
         <v>83.63</v>
       </c>
-      <c r="E344" s="1">
+      <c r="E344" s="2">
         <v>46000</v>
       </c>
       <c r="F344">
@@ -10840,7 +10888,7 @@
         <v>278487.9</v>
       </c>
       <c r="H344">
-        <v>55697.57999999999</v>
+        <v>55697.58000000001</v>
       </c>
     </row>
     <row r="345" spans="1:8">
@@ -10856,7 +10904,7 @@
       <c r="D345">
         <v>114.77</v>
       </c>
-      <c r="E345" s="1">
+      <c r="E345" s="2">
         <v>46001</v>
       </c>
       <c r="F345">
@@ -10882,7 +10930,7 @@
       <c r="D346">
         <v>91.16</v>
       </c>
-      <c r="E346" s="1">
+      <c r="E346" s="2">
         <v>46002</v>
       </c>
       <c r="F346">
@@ -10908,7 +10956,7 @@
       <c r="D347">
         <v>143.14</v>
       </c>
-      <c r="E347" s="1">
+      <c r="E347" s="2">
         <v>46003</v>
       </c>
       <c r="F347">
@@ -10918,7 +10966,7 @@
         <v>19323.9</v>
       </c>
       <c r="H347">
-        <v>3864.78</v>
+        <v>3864.780000000001</v>
       </c>
     </row>
     <row r="348" spans="1:8">
@@ -10934,7 +10982,7 @@
       <c r="D348">
         <v>61.14</v>
       </c>
-      <c r="E348" s="1">
+      <c r="E348" s="2">
         <v>46004</v>
       </c>
       <c r="F348">
@@ -10960,7 +11008,7 @@
       <c r="D349">
         <v>42.35</v>
       </c>
-      <c r="E349" s="1">
+      <c r="E349" s="2">
         <v>46005</v>
       </c>
       <c r="F349">
@@ -10986,7 +11034,7 @@
       <c r="D350">
         <v>72.39</v>
       </c>
-      <c r="E350" s="1">
+      <c r="E350" s="2">
         <v>46006</v>
       </c>
       <c r="F350">
@@ -11012,7 +11060,7 @@
       <c r="D351">
         <v>97.06</v>
       </c>
-      <c r="E351" s="1">
+      <c r="E351" s="2">
         <v>46007</v>
       </c>
       <c r="F351">
@@ -11038,7 +11086,7 @@
       <c r="D352">
         <v>77.18000000000001</v>
       </c>
-      <c r="E352" s="1">
+      <c r="E352" s="2">
         <v>46008</v>
       </c>
       <c r="F352">
@@ -11064,7 +11112,7 @@
       <c r="D353">
         <v>12.71</v>
       </c>
-      <c r="E353" s="1">
+      <c r="E353" s="2">
         <v>46009</v>
       </c>
       <c r="F353">
@@ -11090,7 +11138,7 @@
       <c r="D354">
         <v>31.45</v>
       </c>
-      <c r="E354" s="1">
+      <c r="E354" s="2">
         <v>46010</v>
       </c>
       <c r="F354">
@@ -11116,7 +11164,7 @@
       <c r="D355">
         <v>125.16</v>
       </c>
-      <c r="E355" s="1">
+      <c r="E355" s="2">
         <v>46011</v>
       </c>
       <c r="F355">
@@ -11142,7 +11190,7 @@
       <c r="D356">
         <v>104.9</v>
       </c>
-      <c r="E356" s="1">
+      <c r="E356" s="2">
         <v>46012</v>
       </c>
       <c r="F356">
@@ -11168,7 +11216,7 @@
       <c r="D357">
         <v>93.61</v>
       </c>
-      <c r="E357" s="1">
+      <c r="E357" s="2">
         <v>46013</v>
       </c>
       <c r="F357">
@@ -11194,7 +11242,7 @@
       <c r="D358">
         <v>110.29</v>
       </c>
-      <c r="E358" s="1">
+      <c r="E358" s="2">
         <v>46014</v>
       </c>
       <c r="F358">
@@ -11220,17 +11268,17 @@
       <c r="D359">
         <v>142.96</v>
       </c>
-      <c r="E359" s="1">
+      <c r="E359" s="2">
         <v>46015</v>
       </c>
       <c r="F359">
         <v>6433.200000000001</v>
       </c>
       <c r="G359">
-        <v>456757.2000000001</v>
+        <v>456757.2</v>
       </c>
       <c r="H359">
-        <v>91351.44000000002</v>
+        <v>91351.44</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -11246,7 +11294,7 @@
       <c r="D360">
         <v>75.04000000000001</v>
       </c>
-      <c r="E360" s="1">
+      <c r="E360" s="2">
         <v>46016</v>
       </c>
       <c r="F360">
@@ -11272,7 +11320,7 @@
       <c r="D361">
         <v>148.1</v>
       </c>
-      <c r="E361" s="1">
+      <c r="E361" s="2">
         <v>46017</v>
       </c>
       <c r="F361">
@@ -11298,7 +11346,7 @@
       <c r="D362">
         <v>148.27</v>
       </c>
-      <c r="E362" s="1">
+      <c r="E362" s="2">
         <v>46018</v>
       </c>
       <c r="F362">
@@ -11324,14 +11372,14 @@
       <c r="D363">
         <v>133.52</v>
       </c>
-      <c r="E363" s="1">
+      <c r="E363" s="2">
         <v>46019</v>
       </c>
       <c r="F363">
         <v>6008.400000000001</v>
       </c>
       <c r="G363">
-        <v>96134.40000000001</v>
+        <v>96134.39999999999</v>
       </c>
       <c r="H363">
         <v>19226.88</v>
@@ -11350,7 +11398,7 @@
       <c r="D364">
         <v>145.22</v>
       </c>
-      <c r="E364" s="1">
+      <c r="E364" s="2">
         <v>46020</v>
       </c>
       <c r="F364">
@@ -11376,7 +11424,7 @@
       <c r="D365">
         <v>39.07</v>
       </c>
-      <c r="E365" s="1">
+      <c r="E365" s="2">
         <v>46021</v>
       </c>
       <c r="F365">
@@ -11402,7 +11450,7 @@
       <c r="D366">
         <v>78.92</v>
       </c>
-      <c r="E366" s="1">
+      <c r="E366" s="2">
         <v>46022</v>
       </c>
       <c r="F366">
@@ -11428,7 +11476,7 @@
       <c r="D367">
         <v>125.85</v>
       </c>
-      <c r="E367" s="1">
+      <c r="E367" s="2">
         <v>46023</v>
       </c>
       <c r="F367">
@@ -11454,14 +11502,14 @@
       <c r="D368">
         <v>89.15000000000001</v>
       </c>
-      <c r="E368" s="1">
+      <c r="E368" s="2">
         <v>46024</v>
       </c>
       <c r="F368">
         <v>4011.75</v>
       </c>
       <c r="G368">
-        <v>36105.75000000001</v>
+        <v>36105.75</v>
       </c>
       <c r="H368">
         <v>7221.150000000001</v>
@@ -11480,7 +11528,7 @@
       <c r="D369">
         <v>79.11</v>
       </c>
-      <c r="E369" s="1">
+      <c r="E369" s="2">
         <v>46025</v>
       </c>
       <c r="F369">
@@ -11506,7 +11554,7 @@
       <c r="D370">
         <v>105.06</v>
       </c>
-      <c r="E370" s="1">
+      <c r="E370" s="2">
         <v>46026</v>
       </c>
       <c r="F370">
@@ -11516,7 +11564,7 @@
         <v>28366.2</v>
       </c>
       <c r="H370">
-        <v>5673.24</v>
+        <v>5673.240000000001</v>
       </c>
     </row>
     <row r="371" spans="1:8">
@@ -11532,7 +11580,7 @@
       <c r="D371">
         <v>121.86</v>
       </c>
-      <c r="E371" s="1">
+      <c r="E371" s="2">
         <v>46027</v>
       </c>
       <c r="F371">
@@ -11558,7 +11606,7 @@
       <c r="D372">
         <v>31.96</v>
       </c>
-      <c r="E372" s="1">
+      <c r="E372" s="2">
         <v>46028</v>
       </c>
       <c r="F372">
@@ -11584,7 +11632,7 @@
       <c r="D373">
         <v>73.34</v>
       </c>
-      <c r="E373" s="1">
+      <c r="E373" s="2">
         <v>46029</v>
       </c>
       <c r="F373">
@@ -11594,7 +11642,7 @@
         <v>174915.9</v>
       </c>
       <c r="H373">
-        <v>34983.18000000001</v>
+        <v>34983.18</v>
       </c>
     </row>
     <row r="374" spans="1:8">
@@ -11610,7 +11658,7 @@
       <c r="D374">
         <v>106.94</v>
       </c>
-      <c r="E374" s="1">
+      <c r="E374" s="2">
         <v>46030</v>
       </c>
       <c r="F374">
@@ -11636,7 +11684,7 @@
       <c r="D375">
         <v>26.35</v>
       </c>
-      <c r="E375" s="1">
+      <c r="E375" s="2">
         <v>46031</v>
       </c>
       <c r="F375">
@@ -11662,7 +11710,7 @@
       <c r="D376">
         <v>124.5</v>
       </c>
-      <c r="E376" s="1">
+      <c r="E376" s="2">
         <v>46032</v>
       </c>
       <c r="F376">
@@ -11688,7 +11736,7 @@
       <c r="D377">
         <v>100.18</v>
       </c>
-      <c r="E377" s="1">
+      <c r="E377" s="2">
         <v>46033</v>
       </c>
       <c r="F377">
@@ -11698,7 +11746,7 @@
         <v>329091.3</v>
       </c>
       <c r="H377">
-        <v>65818.26000000001</v>
+        <v>65818.25999999999</v>
       </c>
     </row>
     <row r="378" spans="1:8">
@@ -11714,7 +11762,7 @@
       <c r="D378">
         <v>13.37</v>
       </c>
-      <c r="E378" s="1">
+      <c r="E378" s="2">
         <v>46034</v>
       </c>
       <c r="F378">
@@ -11740,7 +11788,7 @@
       <c r="D379">
         <v>50.46</v>
       </c>
-      <c r="E379" s="1">
+      <c r="E379" s="2">
         <v>46035</v>
       </c>
       <c r="F379">
@@ -11766,7 +11814,7 @@
       <c r="D380">
         <v>100.25</v>
       </c>
-      <c r="E380" s="1">
+      <c r="E380" s="2">
         <v>46036</v>
       </c>
       <c r="F380">
@@ -11792,7 +11840,7 @@
       <c r="D381">
         <v>101.07</v>
       </c>
-      <c r="E381" s="1">
+      <c r="E381" s="2">
         <v>46037</v>
       </c>
       <c r="F381">
@@ -11818,7 +11866,7 @@
       <c r="D382">
         <v>108.38</v>
       </c>
-      <c r="E382" s="1">
+      <c r="E382" s="2">
         <v>46038</v>
       </c>
       <c r="F382">
@@ -11844,7 +11892,7 @@
       <c r="D383">
         <v>108.66</v>
       </c>
-      <c r="E383" s="1">
+      <c r="E383" s="2">
         <v>46039</v>
       </c>
       <c r="F383">
@@ -11870,7 +11918,7 @@
       <c r="D384">
         <v>40.14</v>
       </c>
-      <c r="E384" s="1">
+      <c r="E384" s="2">
         <v>46040</v>
       </c>
       <c r="F384">
@@ -11896,7 +11944,7 @@
       <c r="D385">
         <v>117.48</v>
       </c>
-      <c r="E385" s="1">
+      <c r="E385" s="2">
         <v>46041</v>
       </c>
       <c r="F385">
@@ -11922,7 +11970,7 @@
       <c r="D386">
         <v>101.2</v>
       </c>
-      <c r="E386" s="1">
+      <c r="E386" s="2">
         <v>46042</v>
       </c>
       <c r="F386">
@@ -11948,7 +11996,7 @@
       <c r="D387">
         <v>149.75</v>
       </c>
-      <c r="E387" s="1">
+      <c r="E387" s="2">
         <v>46043</v>
       </c>
       <c r="F387">
@@ -11974,7 +12022,7 @@
       <c r="D388">
         <v>85.40000000000001</v>
       </c>
-      <c r="E388" s="1">
+      <c r="E388" s="2">
         <v>46044</v>
       </c>
       <c r="F388">
@@ -11984,7 +12032,7 @@
         <v>11529</v>
       </c>
       <c r="H388">
-        <v>2305.800000000001</v>
+        <v>2305.8</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -12000,7 +12048,7 @@
       <c r="D389">
         <v>62.04</v>
       </c>
-      <c r="E389" s="1">
+      <c r="E389" s="2">
         <v>46045</v>
       </c>
       <c r="F389">
@@ -12026,7 +12074,7 @@
       <c r="D390">
         <v>143.34</v>
       </c>
-      <c r="E390" s="1">
+      <c r="E390" s="2">
         <v>46046</v>
       </c>
       <c r="F390">
@@ -12036,7 +12084,7 @@
         <v>199959.3</v>
       </c>
       <c r="H390">
-        <v>39991.86000000001</v>
+        <v>39991.86</v>
       </c>
     </row>
     <row r="391" spans="1:8">
@@ -12052,7 +12100,7 @@
       <c r="D391">
         <v>23.3</v>
       </c>
-      <c r="E391" s="1">
+      <c r="E391" s="2">
         <v>46047</v>
       </c>
       <c r="F391">
@@ -12078,7 +12126,7 @@
       <c r="D392">
         <v>51.95</v>
       </c>
-      <c r="E392" s="1">
+      <c r="E392" s="2">
         <v>46048</v>
       </c>
       <c r="F392">
@@ -12104,7 +12152,7 @@
       <c r="D393">
         <v>11.75</v>
       </c>
-      <c r="E393" s="1">
+      <c r="E393" s="2">
         <v>46049</v>
       </c>
       <c r="F393">
@@ -12130,7 +12178,7 @@
       <c r="D394">
         <v>48.75</v>
       </c>
-      <c r="E394" s="1">
+      <c r="E394" s="2">
         <v>46050</v>
       </c>
       <c r="F394">
@@ -12156,14 +12204,14 @@
       <c r="D395">
         <v>54.79</v>
       </c>
-      <c r="E395" s="1">
+      <c r="E395" s="2">
         <v>46051</v>
       </c>
       <c r="F395">
         <v>2465.55</v>
       </c>
       <c r="G395">
-        <v>7396.650000000001</v>
+        <v>7396.65</v>
       </c>
       <c r="H395">
         <v>1479.33</v>
@@ -12182,17 +12230,17 @@
       <c r="D396">
         <v>143.55</v>
       </c>
-      <c r="E396" s="1">
+      <c r="E396" s="2">
         <v>46052</v>
       </c>
       <c r="F396">
         <v>6459.750000000001</v>
       </c>
       <c r="G396">
-        <v>432803.2500000001</v>
+        <v>432803.25</v>
       </c>
       <c r="H396">
-        <v>86560.65000000002</v>
+        <v>86560.65000000001</v>
       </c>
     </row>
     <row r="397" spans="1:8">
@@ -12208,7 +12256,7 @@
       <c r="D397">
         <v>65.54000000000001</v>
       </c>
-      <c r="E397" s="1">
+      <c r="E397" s="2">
         <v>46053</v>
       </c>
       <c r="F397">
@@ -12234,14 +12282,14 @@
       <c r="D398">
         <v>23.66</v>
       </c>
-      <c r="E398" s="1">
+      <c r="E398" s="2">
         <v>46054</v>
       </c>
       <c r="F398">
         <v>1064.7</v>
       </c>
       <c r="G398">
-        <v>51105.60000000001</v>
+        <v>51105.6</v>
       </c>
       <c r="H398">
         <v>10221.12</v>
@@ -12260,7 +12308,7 @@
       <c r="D399">
         <v>88.39</v>
       </c>
-      <c r="E399" s="1">
+      <c r="E399" s="2">
         <v>46055</v>
       </c>
       <c r="F399">
@@ -12286,14 +12334,14 @@
       <c r="D400">
         <v>35.22</v>
       </c>
-      <c r="E400" s="1">
+      <c r="E400" s="2">
         <v>46056</v>
       </c>
       <c r="F400">
         <v>1584.9</v>
       </c>
       <c r="G400">
-        <v>55471.49999999999</v>
+        <v>55471.5</v>
       </c>
       <c r="H400">
         <v>11094.3</v>
@@ -12312,7 +12360,7 @@
       <c r="D401">
         <v>149.73</v>
       </c>
-      <c r="E401" s="1">
+      <c r="E401" s="2">
         <v>46057</v>
       </c>
       <c r="F401">
@@ -12338,7 +12386,7 @@
       <c r="D402">
         <v>102.84</v>
       </c>
-      <c r="E402" s="1">
+      <c r="E402" s="2">
         <v>46058</v>
       </c>
       <c r="F402">
@@ -12364,7 +12412,7 @@
       <c r="D403">
         <v>41.66</v>
       </c>
-      <c r="E403" s="1">
+      <c r="E403" s="2">
         <v>46059</v>
       </c>
       <c r="F403">
@@ -12390,7 +12438,7 @@
       <c r="D404">
         <v>113.69</v>
       </c>
-      <c r="E404" s="1">
+      <c r="E404" s="2">
         <v>46060</v>
       </c>
       <c r="F404">
@@ -12416,7 +12464,7 @@
       <c r="D405">
         <v>21.7</v>
       </c>
-      <c r="E405" s="1">
+      <c r="E405" s="2">
         <v>46061</v>
       </c>
       <c r="F405">
@@ -12442,7 +12490,7 @@
       <c r="D406">
         <v>45.7</v>
       </c>
-      <c r="E406" s="1">
+      <c r="E406" s="2">
         <v>46062</v>
       </c>
       <c r="F406">
@@ -12468,7 +12516,7 @@
       <c r="D407">
         <v>21.59</v>
       </c>
-      <c r="E407" s="1">
+      <c r="E407" s="2">
         <v>46063</v>
       </c>
       <c r="F407">
@@ -12494,7 +12542,7 @@
       <c r="D408">
         <v>99.44</v>
       </c>
-      <c r="E408" s="1">
+      <c r="E408" s="2">
         <v>46064</v>
       </c>
       <c r="F408">
@@ -12520,7 +12568,7 @@
       <c r="D409">
         <v>105.36</v>
       </c>
-      <c r="E409" s="1">
+      <c r="E409" s="2">
         <v>46065</v>
       </c>
       <c r="F409">
@@ -12530,7 +12578,7 @@
         <v>42670.8</v>
       </c>
       <c r="H409">
-        <v>8534.16</v>
+        <v>8534.160000000002</v>
       </c>
     </row>
     <row r="410" spans="1:8">
@@ -12546,7 +12594,7 @@
       <c r="D410">
         <v>65.29000000000001</v>
       </c>
-      <c r="E410" s="1">
+      <c r="E410" s="2">
         <v>46066</v>
       </c>
       <c r="F410">
@@ -12572,7 +12620,7 @@
       <c r="D411">
         <v>120.39</v>
       </c>
-      <c r="E411" s="1">
+      <c r="E411" s="2">
         <v>46067</v>
       </c>
       <c r="F411">
@@ -12598,7 +12646,7 @@
       <c r="D412">
         <v>98.45999999999999</v>
       </c>
-      <c r="E412" s="1">
+      <c r="E412" s="2">
         <v>46068</v>
       </c>
       <c r="F412">
@@ -12624,7 +12672,7 @@
       <c r="D413">
         <v>25.58</v>
       </c>
-      <c r="E413" s="1">
+      <c r="E413" s="2">
         <v>46069</v>
       </c>
       <c r="F413">
@@ -12650,7 +12698,7 @@
       <c r="D414">
         <v>149.88</v>
       </c>
-      <c r="E414" s="1">
+      <c r="E414" s="2">
         <v>46070</v>
       </c>
       <c r="F414">
@@ -12676,7 +12724,7 @@
       <c r="D415">
         <v>66.72</v>
       </c>
-      <c r="E415" s="1">
+      <c r="E415" s="2">
         <v>46071</v>
       </c>
       <c r="F415">
@@ -12702,7 +12750,7 @@
       <c r="D416">
         <v>7.19</v>
       </c>
-      <c r="E416" s="1">
+      <c r="E416" s="2">
         <v>46072</v>
       </c>
       <c r="F416">
@@ -12728,7 +12776,7 @@
       <c r="D417">
         <v>72.5</v>
       </c>
-      <c r="E417" s="1">
+      <c r="E417" s="2">
         <v>46073</v>
       </c>
       <c r="F417">
@@ -12754,7 +12802,7 @@
       <c r="D418">
         <v>98.77</v>
       </c>
-      <c r="E418" s="1">
+      <c r="E418" s="2">
         <v>46074</v>
       </c>
       <c r="F418">
@@ -12764,7 +12812,7 @@
         <v>217787.85</v>
       </c>
       <c r="H418">
-        <v>43557.57</v>
+        <v>43557.57000000001</v>
       </c>
     </row>
     <row r="419" spans="1:8">
@@ -12780,7 +12828,7 @@
       <c r="D419">
         <v>40.25</v>
       </c>
-      <c r="E419" s="1">
+      <c r="E419" s="2">
         <v>46075</v>
       </c>
       <c r="F419">
@@ -12806,7 +12854,7 @@
       <c r="D420">
         <v>122.62</v>
       </c>
-      <c r="E420" s="1">
+      <c r="E420" s="2">
         <v>46076</v>
       </c>
       <c r="F420">
@@ -12816,7 +12864,7 @@
         <v>220716</v>
       </c>
       <c r="H420">
-        <v>44143.20000000001</v>
+        <v>44143.2</v>
       </c>
     </row>
     <row r="421" spans="1:8">
@@ -12832,7 +12880,7 @@
       <c r="D421">
         <v>145.25</v>
       </c>
-      <c r="E421" s="1">
+      <c r="E421" s="2">
         <v>46077</v>
       </c>
       <c r="F421">
@@ -12858,7 +12906,7 @@
       <c r="D422">
         <v>99.52</v>
       </c>
-      <c r="E422" s="1">
+      <c r="E422" s="2">
         <v>46078</v>
       </c>
       <c r="F422">
@@ -12884,7 +12932,7 @@
       <c r="D423">
         <v>102.39</v>
       </c>
-      <c r="E423" s="1">
+      <c r="E423" s="2">
         <v>46079</v>
       </c>
       <c r="F423">
@@ -12910,7 +12958,7 @@
       <c r="D424">
         <v>23.59</v>
       </c>
-      <c r="E424" s="1">
+      <c r="E424" s="2">
         <v>46080</v>
       </c>
       <c r="F424">
@@ -12920,7 +12968,7 @@
         <v>30784.95</v>
       </c>
       <c r="H424">
-        <v>6156.99</v>
+        <v>6156.990000000001</v>
       </c>
     </row>
     <row r="425" spans="1:8">
@@ -12936,14 +12984,14 @@
       <c r="D425">
         <v>37.01</v>
       </c>
-      <c r="E425" s="1">
+      <c r="E425" s="2">
         <v>46081</v>
       </c>
       <c r="F425">
         <v>1665.45</v>
       </c>
       <c r="G425">
-        <v>6661.799999999999</v>
+        <v>6661.8</v>
       </c>
       <c r="H425">
         <v>1332.36</v>
@@ -12962,7 +13010,7 @@
       <c r="D426">
         <v>15.56</v>
       </c>
-      <c r="E426" s="1">
+      <c r="E426" s="2">
         <v>46082</v>
       </c>
       <c r="F426">
@@ -12972,7 +13020,7 @@
         <v>19605.6</v>
       </c>
       <c r="H426">
-        <v>3921.120000000001</v>
+        <v>3921.12</v>
       </c>
     </row>
     <row r="427" spans="1:8">
@@ -12988,7 +13036,7 @@
       <c r="D427">
         <v>50.06</v>
       </c>
-      <c r="E427" s="1">
+      <c r="E427" s="2">
         <v>46083</v>
       </c>
       <c r="F427">
@@ -12998,7 +13046,7 @@
         <v>110382.3</v>
       </c>
       <c r="H427">
-        <v>22076.46000000001</v>
+        <v>22076.46</v>
       </c>
     </row>
     <row r="428" spans="1:8">
@@ -13014,7 +13062,7 @@
       <c r="D428">
         <v>99.48</v>
       </c>
-      <c r="E428" s="1">
+      <c r="E428" s="2">
         <v>46084</v>
       </c>
       <c r="F428">
@@ -13040,7 +13088,7 @@
       <c r="D429">
         <v>76.47</v>
       </c>
-      <c r="E429" s="1">
+      <c r="E429" s="2">
         <v>46085</v>
       </c>
       <c r="F429">
@@ -13066,7 +13114,7 @@
       <c r="D430">
         <v>30.15</v>
       </c>
-      <c r="E430" s="1">
+      <c r="E430" s="2">
         <v>46086</v>
       </c>
       <c r="F430">
@@ -13092,7 +13140,7 @@
       <c r="D431">
         <v>99.66</v>
       </c>
-      <c r="E431" s="1">
+      <c r="E431" s="2">
         <v>46087</v>
       </c>
       <c r="F431">
@@ -13118,7 +13166,7 @@
       <c r="D432">
         <v>129.58</v>
       </c>
-      <c r="E432" s="1">
+      <c r="E432" s="2">
         <v>46088</v>
       </c>
       <c r="F432">
@@ -13144,7 +13192,7 @@
       <c r="D433">
         <v>92.90000000000001</v>
       </c>
-      <c r="E433" s="1">
+      <c r="E433" s="2">
         <v>46089</v>
       </c>
       <c r="F433">
@@ -13170,7 +13218,7 @@
       <c r="D434">
         <v>148.2</v>
       </c>
-      <c r="E434" s="1">
+      <c r="E434" s="2">
         <v>46090</v>
       </c>
       <c r="F434">
@@ -13196,7 +13244,7 @@
       <c r="D435">
         <v>131.57</v>
       </c>
-      <c r="E435" s="1">
+      <c r="E435" s="2">
         <v>46091</v>
       </c>
       <c r="F435">
@@ -13222,7 +13270,7 @@
       <c r="D436">
         <v>149.56</v>
       </c>
-      <c r="E436" s="1">
+      <c r="E436" s="2">
         <v>46092</v>
       </c>
       <c r="F436">
@@ -13248,7 +13296,7 @@
       <c r="D437">
         <v>114.85</v>
       </c>
-      <c r="E437" s="1">
+      <c r="E437" s="2">
         <v>46093</v>
       </c>
       <c r="F437">
@@ -13274,7 +13322,7 @@
       <c r="D438">
         <v>67.47</v>
       </c>
-      <c r="E438" s="1">
+      <c r="E438" s="2">
         <v>46094</v>
       </c>
       <c r="F438">
@@ -13300,7 +13348,7 @@
       <c r="D439">
         <v>105.54</v>
       </c>
-      <c r="E439" s="1">
+      <c r="E439" s="2">
         <v>46095</v>
       </c>
       <c r="F439">
@@ -13326,7 +13374,7 @@
       <c r="D440">
         <v>41.05</v>
       </c>
-      <c r="E440" s="1">
+      <c r="E440" s="2">
         <v>46096</v>
       </c>
       <c r="F440">
@@ -13352,7 +13400,7 @@
       <c r="D441">
         <v>6.98</v>
       </c>
-      <c r="E441" s="1">
+      <c r="E441" s="2">
         <v>46097</v>
       </c>
       <c r="F441">
@@ -13362,7 +13410,7 @@
         <v>28269</v>
       </c>
       <c r="H441">
-        <v>5653.800000000001</v>
+        <v>5653.8</v>
       </c>
     </row>
     <row r="442" spans="1:8">
@@ -13378,7 +13426,7 @@
       <c r="D442">
         <v>123.17</v>
       </c>
-      <c r="E442" s="1">
+      <c r="E442" s="2">
         <v>46098</v>
       </c>
       <c r="F442">
@@ -13404,7 +13452,7 @@
       <c r="D443">
         <v>16.55</v>
       </c>
-      <c r="E443" s="1">
+      <c r="E443" s="2">
         <v>46099</v>
       </c>
       <c r="F443">
@@ -13430,7 +13478,7 @@
       <c r="D444">
         <v>22.73</v>
       </c>
-      <c r="E444" s="1">
+      <c r="E444" s="2">
         <v>46100</v>
       </c>
       <c r="F444">
@@ -13456,7 +13504,7 @@
       <c r="D445">
         <v>31.22</v>
       </c>
-      <c r="E445" s="1">
+      <c r="E445" s="2">
         <v>46101</v>
       </c>
       <c r="F445">
@@ -13482,7 +13530,7 @@
       <c r="D446">
         <v>12.08</v>
       </c>
-      <c r="E446" s="1">
+      <c r="E446" s="2">
         <v>46102</v>
       </c>
       <c r="F446">
@@ -13508,7 +13556,7 @@
       <c r="D447">
         <v>89.5</v>
       </c>
-      <c r="E447" s="1">
+      <c r="E447" s="2">
         <v>46103</v>
       </c>
       <c r="F447">
@@ -13534,7 +13582,7 @@
       <c r="D448">
         <v>41.88</v>
       </c>
-      <c r="E448" s="1">
+      <c r="E448" s="2">
         <v>46104</v>
       </c>
       <c r="F448">
@@ -13560,7 +13608,7 @@
       <c r="D449">
         <v>112.7</v>
       </c>
-      <c r="E449" s="1">
+      <c r="E449" s="2">
         <v>46105</v>
       </c>
       <c r="F449">
@@ -13586,7 +13634,7 @@
       <c r="D450">
         <v>91.17</v>
       </c>
-      <c r="E450" s="1">
+      <c r="E450" s="2">
         <v>46106</v>
       </c>
       <c r="F450">
@@ -13612,7 +13660,7 @@
       <c r="D451">
         <v>48.48</v>
       </c>
-      <c r="E451" s="1">
+      <c r="E451" s="2">
         <v>46107</v>
       </c>
       <c r="F451">
@@ -13638,7 +13686,7 @@
       <c r="D452">
         <v>30.28</v>
       </c>
-      <c r="E452" s="1">
+      <c r="E452" s="2">
         <v>46108</v>
       </c>
       <c r="F452">
@@ -13664,7 +13712,7 @@
       <c r="D453">
         <v>45.68</v>
       </c>
-      <c r="E453" s="1">
+      <c r="E453" s="2">
         <v>46109</v>
       </c>
       <c r="F453">
@@ -13690,7 +13738,7 @@
       <c r="D454">
         <v>98.56</v>
       </c>
-      <c r="E454" s="1">
+      <c r="E454" s="2">
         <v>46110</v>
       </c>
       <c r="F454">
@@ -13716,7 +13764,7 @@
       <c r="D455">
         <v>84.54000000000001</v>
       </c>
-      <c r="E455" s="1">
+      <c r="E455" s="2">
         <v>46111</v>
       </c>
       <c r="F455">
@@ -13742,7 +13790,7 @@
       <c r="D456">
         <v>138.58</v>
       </c>
-      <c r="E456" s="1">
+      <c r="E456" s="2">
         <v>46112</v>
       </c>
       <c r="F456">
@@ -13768,7 +13816,7 @@
       <c r="D457">
         <v>98.16</v>
       </c>
-      <c r="E457" s="1">
+      <c r="E457" s="2">
         <v>46113</v>
       </c>
       <c r="F457">
@@ -13794,7 +13842,7 @@
       <c r="D458">
         <v>9.02</v>
       </c>
-      <c r="E458" s="1">
+      <c r="E458" s="2">
         <v>46114</v>
       </c>
       <c r="F458">
@@ -13820,17 +13868,17 @@
       <c r="D459">
         <v>129.88</v>
       </c>
-      <c r="E459" s="1">
+      <c r="E459" s="2">
         <v>46115</v>
       </c>
       <c r="F459">
         <v>5844.599999999999</v>
       </c>
       <c r="G459">
-        <v>409121.9999999999</v>
+        <v>409122</v>
       </c>
       <c r="H459">
-        <v>81824.39999999999</v>
+        <v>81824.40000000001</v>
       </c>
     </row>
     <row r="460" spans="1:8">
@@ -13846,7 +13894,7 @@
       <c r="D460">
         <v>96.16</v>
       </c>
-      <c r="E460" s="1">
+      <c r="E460" s="2">
         <v>46116</v>
       </c>
       <c r="F460">
@@ -13872,7 +13920,7 @@
       <c r="D461">
         <v>14.86</v>
       </c>
-      <c r="E461" s="1">
+      <c r="E461" s="2">
         <v>46117</v>
       </c>
       <c r="F461">
@@ -13882,7 +13930,7 @@
         <v>39453.3</v>
       </c>
       <c r="H461">
-        <v>7890.66</v>
+        <v>7890.660000000001</v>
       </c>
     </row>
     <row r="462" spans="1:8">
@@ -13898,7 +13946,7 @@
       <c r="D462">
         <v>67.06999999999999</v>
       </c>
-      <c r="E462" s="1">
+      <c r="E462" s="2">
         <v>46118</v>
       </c>
       <c r="F462">
@@ -13924,7 +13972,7 @@
       <c r="D463">
         <v>55.62</v>
       </c>
-      <c r="E463" s="1">
+      <c r="E463" s="2">
         <v>46119</v>
       </c>
       <c r="F463">
@@ -13950,7 +13998,7 @@
       <c r="D464">
         <v>42.55</v>
       </c>
-      <c r="E464" s="1">
+      <c r="E464" s="2">
         <v>46120</v>
       </c>
       <c r="F464">
@@ -13976,7 +14024,7 @@
       <c r="D465">
         <v>92.25</v>
       </c>
-      <c r="E465" s="1">
+      <c r="E465" s="2">
         <v>46121</v>
       </c>
       <c r="F465">
@@ -14002,7 +14050,7 @@
       <c r="D466">
         <v>122.17</v>
       </c>
-      <c r="E466" s="1">
+      <c r="E466" s="2">
         <v>46122</v>
       </c>
       <c r="F466">
@@ -14028,7 +14076,7 @@
       <c r="D467">
         <v>147.77</v>
       </c>
-      <c r="E467" s="1">
+      <c r="E467" s="2">
         <v>46123</v>
       </c>
       <c r="F467">
@@ -14054,7 +14102,7 @@
       <c r="D468">
         <v>94.06</v>
       </c>
-      <c r="E468" s="1">
+      <c r="E468" s="2">
         <v>46124</v>
       </c>
       <c r="F468">
@@ -14064,7 +14112,7 @@
         <v>325917.9</v>
       </c>
       <c r="H468">
-        <v>65183.57999999999</v>
+        <v>65183.58000000001</v>
       </c>
     </row>
     <row r="469" spans="1:8">
@@ -14080,7 +14128,7 @@
       <c r="D469">
         <v>41.75</v>
       </c>
-      <c r="E469" s="1">
+      <c r="E469" s="2">
         <v>46125</v>
       </c>
       <c r="F469">
@@ -14106,7 +14154,7 @@
       <c r="D470">
         <v>76.06</v>
       </c>
-      <c r="E470" s="1">
+      <c r="E470" s="2">
         <v>46126</v>
       </c>
       <c r="F470">
@@ -14132,7 +14180,7 @@
       <c r="D471">
         <v>95.64</v>
       </c>
-      <c r="E471" s="1">
+      <c r="E471" s="2">
         <v>46127</v>
       </c>
       <c r="F471">
@@ -14142,7 +14190,7 @@
         <v>197974.8</v>
       </c>
       <c r="H471">
-        <v>39594.96000000001</v>
+        <v>39594.96</v>
       </c>
     </row>
     <row r="472" spans="1:8">
@@ -14158,7 +14206,7 @@
       <c r="D472">
         <v>38.31</v>
       </c>
-      <c r="E472" s="1">
+      <c r="E472" s="2">
         <v>46128</v>
       </c>
       <c r="F472">
@@ -14184,7 +14232,7 @@
       <c r="D473">
         <v>86.14</v>
       </c>
-      <c r="E473" s="1">
+      <c r="E473" s="2">
         <v>46129</v>
       </c>
       <c r="F473">
@@ -14210,7 +14258,7 @@
       <c r="D474">
         <v>100.73</v>
       </c>
-      <c r="E474" s="1">
+      <c r="E474" s="2">
         <v>46130</v>
       </c>
       <c r="F474">
@@ -14236,7 +14284,7 @@
       <c r="D475">
         <v>135.47</v>
       </c>
-      <c r="E475" s="1">
+      <c r="E475" s="2">
         <v>46131</v>
       </c>
       <c r="F475">
@@ -14246,7 +14294,7 @@
         <v>353576.7</v>
       </c>
       <c r="H475">
-        <v>70715.34</v>
+        <v>70715.34000000001</v>
       </c>
     </row>
     <row r="476" spans="1:8">
@@ -14262,7 +14310,7 @@
       <c r="D476">
         <v>90.78</v>
       </c>
-      <c r="E476" s="1">
+      <c r="E476" s="2">
         <v>46132</v>
       </c>
       <c r="F476">
@@ -14288,7 +14336,7 @@
       <c r="D477">
         <v>117.42</v>
       </c>
-      <c r="E477" s="1">
+      <c r="E477" s="2">
         <v>46133</v>
       </c>
       <c r="F477">
@@ -14298,7 +14346,7 @@
         <v>359305.2</v>
       </c>
       <c r="H477">
-        <v>71861.03999999999</v>
+        <v>71861.04000000001</v>
       </c>
     </row>
     <row r="478" spans="1:8">
@@ -14314,7 +14362,7 @@
       <c r="D478">
         <v>106.71</v>
       </c>
-      <c r="E478" s="1">
+      <c r="E478" s="2">
         <v>46134</v>
       </c>
       <c r="F478">
@@ -14340,7 +14388,7 @@
       <c r="D479">
         <v>109.21</v>
       </c>
-      <c r="E479" s="1">
+      <c r="E479" s="2">
         <v>46135</v>
       </c>
       <c r="F479">
@@ -14366,7 +14414,7 @@
       <c r="D480">
         <v>16.21</v>
       </c>
-      <c r="E480" s="1">
+      <c r="E480" s="2">
         <v>46136</v>
       </c>
       <c r="F480">
@@ -14392,7 +14440,7 @@
       <c r="D481">
         <v>131.87</v>
       </c>
-      <c r="E481" s="1">
+      <c r="E481" s="2">
         <v>46137</v>
       </c>
       <c r="F481">
@@ -14418,7 +14466,7 @@
       <c r="D482">
         <v>22.22</v>
       </c>
-      <c r="E482" s="1">
+      <c r="E482" s="2">
         <v>46138</v>
       </c>
       <c r="F482">
@@ -14444,7 +14492,7 @@
       <c r="D483">
         <v>93.17</v>
       </c>
-      <c r="E483" s="1">
+      <c r="E483" s="2">
         <v>46139</v>
       </c>
       <c r="F483">
@@ -14470,14 +14518,14 @@
       <c r="D484">
         <v>129.01</v>
       </c>
-      <c r="E484" s="1">
+      <c r="E484" s="2">
         <v>46140</v>
       </c>
       <c r="F484">
         <v>5805.45</v>
       </c>
       <c r="G484">
-        <v>75470.84999999999</v>
+        <v>75470.85000000001</v>
       </c>
       <c r="H484">
         <v>15094.17</v>
@@ -14496,7 +14544,7 @@
       <c r="D485">
         <v>40.63</v>
       </c>
-      <c r="E485" s="1">
+      <c r="E485" s="2">
         <v>46141</v>
       </c>
       <c r="F485">
@@ -14506,7 +14554,7 @@
         <v>181006.65</v>
       </c>
       <c r="H485">
-        <v>36201.33000000001</v>
+        <v>36201.33</v>
       </c>
     </row>
     <row r="486" spans="1:8">
@@ -14522,7 +14570,7 @@
       <c r="D486">
         <v>89.97</v>
       </c>
-      <c r="E486" s="1">
+      <c r="E486" s="2">
         <v>46142</v>
       </c>
       <c r="F486">
@@ -14532,7 +14580,7 @@
         <v>210529.8</v>
       </c>
       <c r="H486">
-        <v>42105.96000000001</v>
+        <v>42105.96</v>
       </c>
     </row>
     <row r="487" spans="1:8">
@@ -14548,7 +14596,7 @@
       <c r="D487">
         <v>14.31</v>
       </c>
-      <c r="E487" s="1">
+      <c r="E487" s="2">
         <v>46143</v>
       </c>
       <c r="F487">
@@ -14574,7 +14622,7 @@
       <c r="D488">
         <v>52.81</v>
       </c>
-      <c r="E488" s="1">
+      <c r="E488" s="2">
         <v>46144</v>
       </c>
       <c r="F488">
@@ -14600,7 +14648,7 @@
       <c r="D489">
         <v>8.02</v>
       </c>
-      <c r="E489" s="1">
+      <c r="E489" s="2">
         <v>46145</v>
       </c>
       <c r="F489">
@@ -14626,7 +14674,7 @@
       <c r="D490">
         <v>142.46</v>
       </c>
-      <c r="E490" s="1">
+      <c r="E490" s="2">
         <v>46146</v>
       </c>
       <c r="F490">
@@ -14636,7 +14684,7 @@
         <v>211553.1</v>
       </c>
       <c r="H490">
-        <v>42310.62000000001</v>
+        <v>42310.62</v>
       </c>
     </row>
     <row r="491" spans="1:8">
@@ -14652,7 +14700,7 @@
       <c r="D491">
         <v>13.95</v>
       </c>
-      <c r="E491" s="1">
+      <c r="E491" s="2">
         <v>46147</v>
       </c>
       <c r="F491">
@@ -14678,7 +14726,7 @@
       <c r="D492">
         <v>122.32</v>
       </c>
-      <c r="E492" s="1">
+      <c r="E492" s="2">
         <v>46148</v>
       </c>
       <c r="F492">
@@ -14704,7 +14752,7 @@
       <c r="D493">
         <v>88.12</v>
       </c>
-      <c r="E493" s="1">
+      <c r="E493" s="2">
         <v>46149</v>
       </c>
       <c r="F493">
@@ -14730,7 +14778,7 @@
       <c r="D494">
         <v>139.15</v>
       </c>
-      <c r="E494" s="1">
+      <c r="E494" s="2">
         <v>46150</v>
       </c>
       <c r="F494">
@@ -14756,14 +14804,14 @@
       <c r="D495">
         <v>31.58</v>
       </c>
-      <c r="E495" s="1">
+      <c r="E495" s="2">
         <v>46151</v>
       </c>
       <c r="F495">
         <v>1421.1</v>
       </c>
       <c r="G495">
-        <v>63949.49999999999</v>
+        <v>63949.5</v>
       </c>
       <c r="H495">
         <v>12789.9</v>
@@ -14782,7 +14830,7 @@
       <c r="D496">
         <v>27.2</v>
       </c>
-      <c r="E496" s="1">
+      <c r="E496" s="2">
         <v>46152</v>
       </c>
       <c r="F496">
@@ -14808,7 +14856,7 @@
       <c r="D497">
         <v>134.14</v>
       </c>
-      <c r="E497" s="1">
+      <c r="E497" s="2">
         <v>46153</v>
       </c>
       <c r="F497">
@@ -14834,7 +14882,7 @@
       <c r="D498">
         <v>58.21</v>
       </c>
-      <c r="E498" s="1">
+      <c r="E498" s="2">
         <v>46154</v>
       </c>
       <c r="F498">
@@ -14860,7 +14908,7 @@
       <c r="D499">
         <v>42.83</v>
       </c>
-      <c r="E499" s="1">
+      <c r="E499" s="2">
         <v>46155</v>
       </c>
       <c r="F499">
@@ -14886,7 +14934,7 @@
       <c r="D500">
         <v>77.16</v>
       </c>
-      <c r="E500" s="1">
+      <c r="E500" s="2">
         <v>46156</v>
       </c>
       <c r="F500">
@@ -14912,7 +14960,7 @@
       <c r="D501">
         <v>78.47</v>
       </c>
-      <c r="E501" s="1">
+      <c r="E501" s="2">
         <v>46157</v>
       </c>
       <c r="F501">
@@ -14923,6 +14971,14 @@
       </c>
       <c r="H501">
         <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="1:8">
+      <c r="G502" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="H502" s="3">
+        <v>75230500.95</v>
       </c>
     </row>
   </sheetData>
@@ -14934,6 +14990,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="20.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
@@ -14942,8 +15001,8 @@
       <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>513</v>
+      <c r="D1" s="1" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -14954,7 +15013,7 @@
         <v>4578</v>
       </c>
       <c r="D2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="3" spans="1:4">
